--- a/Outcome/Appendix/figure_data/fig7.xlsx
+++ b/Outcome/Appendix/figure_data/fig7.xlsx
@@ -2600,19 +2600,19 @@
         <v>43831</v>
       </c>
       <c r="B50" t="n">
-        <v>34715.3924121989</v>
+        <v>41685.4756532966</v>
       </c>
       <c r="C50" t="n">
-        <v>22234.8098950027</v>
+        <v>25452.9035288269</v>
       </c>
       <c r="D50" t="n">
-        <v>17699.4030509549</v>
+        <v>19923.4375178871</v>
       </c>
       <c r="E50" t="n">
-        <v>55284.0343513093</v>
+        <v>68753.7598653036</v>
       </c>
       <c r="F50" t="n">
-        <v>71314.7062457275</v>
+        <v>87312.3935926241</v>
       </c>
       <c r="G50" t="s">
         <v>65</v>
@@ -2621,13 +2621,13 @@
         <v>52472</v>
       </c>
       <c r="I50" t="n">
-        <v>-17757</v>
+        <v>-10787</v>
       </c>
       <c r="J50" t="s">
         <v>14</v>
       </c>
       <c r="K50" t="n">
-        <v>0.662</v>
+        <v>0.794</v>
       </c>
       <c r="L50" t="s">
         <v>15</v>
@@ -2641,19 +2641,19 @@
         <v>43862</v>
       </c>
       <c r="B51" t="n">
-        <v>38756.1558959228</v>
+        <v>57347.541924127</v>
       </c>
       <c r="C51" t="n">
-        <v>17630.1226670063</v>
+        <v>21316.4672374808</v>
       </c>
       <c r="D51" t="n">
-        <v>11901.1503587034</v>
+        <v>12172.9982511043</v>
       </c>
       <c r="E51" t="n">
-        <v>90762.8160228715</v>
+        <v>163299.54614068</v>
       </c>
       <c r="F51" t="n">
-        <v>146357.239316268</v>
+        <v>279667.431542176</v>
       </c>
       <c r="G51" t="s">
         <v>65</v>
@@ -2662,13 +2662,13 @@
         <v>33663</v>
       </c>
       <c r="I51" t="n">
-        <v>5093</v>
+        <v>23685</v>
       </c>
       <c r="J51" t="s">
         <v>17</v>
       </c>
       <c r="K51" t="n">
-        <v>1.151</v>
+        <v>1.704</v>
       </c>
       <c r="L51" t="s">
         <v>15</v>
@@ -2682,19 +2682,19 @@
         <v>43891</v>
       </c>
       <c r="B52" t="n">
-        <v>36358.2878372278</v>
+        <v>51965.7702393486</v>
       </c>
       <c r="C52" t="n">
-        <v>13956.4582256792</v>
+        <v>9955.13025303357</v>
       </c>
       <c r="D52" t="n">
-        <v>8713.37327868881</v>
+        <v>4286.61745918162</v>
       </c>
       <c r="E52" t="n">
-        <v>104239.234641943</v>
+        <v>293601.487312683</v>
       </c>
       <c r="F52" t="n">
-        <v>189853.464190753</v>
+        <v>805694.104079984</v>
       </c>
       <c r="G52" t="s">
         <v>65</v>
@@ -2703,13 +2703,13 @@
         <v>13157</v>
       </c>
       <c r="I52" t="n">
-        <v>23201</v>
+        <v>38809</v>
       </c>
       <c r="J52" t="s">
         <v>17</v>
       </c>
       <c r="K52" t="n">
-        <v>2.763</v>
+        <v>3.95</v>
       </c>
       <c r="L52" t="s">
         <v>15</v>
@@ -2723,19 +2723,19 @@
         <v>43922</v>
       </c>
       <c r="B53" t="n">
-        <v>20619.7773656365</v>
+        <v>30401.4332684134</v>
       </c>
       <c r="C53" t="n">
-        <v>7800.97579638222</v>
+        <v>2803.9305242179</v>
       </c>
       <c r="D53" t="n">
-        <v>4848.74591897067</v>
+        <v>764.013293705953</v>
       </c>
       <c r="E53" t="n">
-        <v>60544.0844108682</v>
+        <v>409232.485874124</v>
       </c>
       <c r="F53" t="n">
-        <v>112161.384205514</v>
+        <v>1411379.38132254</v>
       </c>
       <c r="G53" t="s">
         <v>65</v>
@@ -2744,16 +2744,16 @@
         <v>2095</v>
       </c>
       <c r="I53" t="n">
-        <v>18525</v>
+        <v>28306</v>
       </c>
       <c r="J53" t="s">
         <v>17</v>
       </c>
       <c r="K53" t="n">
-        <v>9.842</v>
+        <v>14.511</v>
       </c>
       <c r="L53" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="M53" t="s">
         <v>20</v>
@@ -2764,19 +2764,19 @@
         <v>43952</v>
       </c>
       <c r="B54" t="n">
-        <v>17959.6015472862</v>
+        <v>33012.1429284319</v>
       </c>
       <c r="C54" t="n">
-        <v>6755.39541449738</v>
+        <v>1338.07836101767</v>
       </c>
       <c r="D54" t="n">
-        <v>4190.36475282834</v>
+        <v>227.791001129807</v>
       </c>
       <c r="E54" t="n">
-        <v>53197.7982235453</v>
+        <v>1000417.53330378</v>
       </c>
       <c r="F54" t="n">
-        <v>99149.8870097676</v>
+        <v>4359357.76060126</v>
       </c>
       <c r="G54" t="s">
         <v>65</v>
@@ -2785,13 +2785,13 @@
         <v>1335</v>
       </c>
       <c r="I54" t="n">
-        <v>16625</v>
+        <v>31677</v>
       </c>
       <c r="J54" t="s">
         <v>17</v>
       </c>
       <c r="K54" t="n">
-        <v>13.453</v>
+        <v>24.728</v>
       </c>
       <c r="L54" t="s">
         <v>66</v>
@@ -2805,19 +2805,19 @@
         <v>43983</v>
       </c>
       <c r="B55" t="n">
-        <v>26245.3755056329</v>
+        <v>65046.4400595071</v>
       </c>
       <c r="C55" t="n">
-        <v>9448.19233078021</v>
+        <v>1060.08029057791</v>
       </c>
       <c r="D55" t="n">
-        <v>5737.87636552601</v>
+        <v>117.162704973494</v>
       </c>
       <c r="E55" t="n">
-        <v>81684.1906584493</v>
+        <v>5465080.45105092</v>
       </c>
       <c r="F55" t="n">
-        <v>156674.276778116</v>
+        <v>34647046.1017051</v>
       </c>
       <c r="G55" t="s">
         <v>65</v>
@@ -2826,13 +2826,13 @@
         <v>1531</v>
       </c>
       <c r="I55" t="n">
-        <v>24714</v>
+        <v>63515</v>
       </c>
       <c r="J55" t="s">
         <v>17</v>
       </c>
       <c r="K55" t="n">
-        <v>17.143</v>
+        <v>42.486</v>
       </c>
       <c r="L55" t="s">
         <v>66</v>
@@ -2846,19 +2846,19 @@
         <v>44013</v>
       </c>
       <c r="B56" t="n">
-        <v>31253.0728944432</v>
+        <v>111172.113031118</v>
       </c>
       <c r="C56" t="n">
-        <v>11003.5048425757</v>
+        <v>841.746944830536</v>
       </c>
       <c r="D56" t="n">
-        <v>6611.57699411874</v>
+        <v>44.3821984717264</v>
       </c>
       <c r="E56" t="n">
-        <v>99761.8075741998</v>
+        <v>20316658.1257381</v>
       </c>
       <c r="F56" t="n">
-        <v>194194.450769525</v>
+        <v>255047430.212067</v>
       </c>
       <c r="G56" t="s">
         <v>65</v>
@@ -2867,13 +2867,13 @@
         <v>2624</v>
       </c>
       <c r="I56" t="n">
-        <v>28629</v>
+        <v>108548</v>
       </c>
       <c r="J56" t="s">
         <v>17</v>
       </c>
       <c r="K56" t="n">
-        <v>11.91</v>
+        <v>42.367</v>
       </c>
       <c r="L56" t="s">
         <v>66</v>
@@ -2887,19 +2887,19 @@
         <v>44044</v>
       </c>
       <c r="B57" t="n">
-        <v>33654.6080673684</v>
+        <v>165158.761006484</v>
       </c>
       <c r="C57" t="n">
-        <v>11676.322201054</v>
+        <v>452.810074807181</v>
       </c>
       <c r="D57" t="n">
-        <v>6967.89019270923</v>
+        <v>10.602189801356</v>
       </c>
       <c r="E57" t="n">
-        <v>109294.646198769</v>
+        <v>91852213.7778851</v>
       </c>
       <c r="F57" t="n">
-        <v>214949.520924567</v>
+        <v>2058050303.65451</v>
       </c>
       <c r="G57" t="s">
         <v>65</v>
@@ -2908,13 +2908,13 @@
         <v>3232</v>
       </c>
       <c r="I57" t="n">
-        <v>30423</v>
+        <v>161927</v>
       </c>
       <c r="J57" t="s">
         <v>17</v>
       </c>
       <c r="K57" t="n">
-        <v>10.413</v>
+        <v>51.101</v>
       </c>
       <c r="L57" t="s">
         <v>66</v>
@@ -2928,19 +2928,19 @@
         <v>44075</v>
       </c>
       <c r="B58" t="n">
-        <v>47914.908691227</v>
+        <v>217206.762483883</v>
       </c>
       <c r="C58" t="n">
-        <v>15874.9671452561</v>
+        <v>221.908071074659</v>
       </c>
       <c r="D58" t="n">
-        <v>9266.91179445075</v>
+        <v>2.24944913659607</v>
       </c>
       <c r="E58" t="n">
-        <v>164007.276183751</v>
+        <v>333868572.586499</v>
       </c>
       <c r="F58" t="n">
-        <v>332628.504847078</v>
+        <v>12467982150.6099</v>
       </c>
       <c r="G58" t="s">
         <v>65</v>
@@ -2949,13 +2949,13 @@
         <v>2462</v>
       </c>
       <c r="I58" t="n">
-        <v>45453</v>
+        <v>214745</v>
       </c>
       <c r="J58" t="s">
         <v>17</v>
       </c>
       <c r="K58" t="n">
-        <v>19.462</v>
+        <v>88.223</v>
       </c>
       <c r="L58" t="s">
         <v>66</v>
@@ -2969,19 +2969,19 @@
         <v>44105</v>
       </c>
       <c r="B59" t="n">
-        <v>35264.9052883476</v>
+        <v>168881.326490214</v>
       </c>
       <c r="C59" t="n">
-        <v>11932.0916320813</v>
+        <v>45.3348510599911</v>
       </c>
       <c r="D59" t="n">
-        <v>7040.17835288114</v>
+        <v>0.263491228433019</v>
       </c>
       <c r="E59" t="n">
-        <v>118070.765033109</v>
+        <v>837977290.249468</v>
       </c>
       <c r="F59" t="n">
-        <v>236580.202122951</v>
+        <v>47947356166.3796</v>
       </c>
       <c r="G59" t="s">
         <v>65</v>
@@ -2990,16 +2990,16 @@
         <v>3824</v>
       </c>
       <c r="I59" t="n">
-        <v>31441</v>
+        <v>165057</v>
       </c>
       <c r="J59" t="s">
         <v>17</v>
       </c>
       <c r="K59" t="n">
-        <v>9.222</v>
+        <v>44.163</v>
       </c>
       <c r="L59" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="M59" t="s">
         <v>26</v>
@@ -3010,19 +3010,19 @@
         <v>44136</v>
       </c>
       <c r="B60" t="n">
-        <v>28473.0905646969</v>
+        <v>138671.066920111</v>
       </c>
       <c r="C60" t="n">
-        <v>9769.23941055802</v>
+        <v>9.38769658218336</v>
       </c>
       <c r="D60" t="n">
-        <v>5805.36853578815</v>
+        <v>0.043954034945308</v>
       </c>
       <c r="E60" t="n">
-        <v>93960.7827041949</v>
+        <v>1984683147.0949</v>
       </c>
       <c r="F60" t="n">
-        <v>186795.992243729</v>
+        <v>222151967810.648</v>
       </c>
       <c r="G60" t="s">
         <v>65</v>
@@ -3031,16 +3031,16 @@
         <v>4827</v>
       </c>
       <c r="I60" t="n">
-        <v>23646</v>
+        <v>133844</v>
       </c>
       <c r="J60" t="s">
         <v>17</v>
       </c>
       <c r="K60" t="n">
-        <v>5.899</v>
+        <v>28.728</v>
       </c>
       <c r="L60" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="M60" t="s">
         <v>27</v>
@@ -3051,19 +3051,19 @@
         <v>44166</v>
       </c>
       <c r="B61" t="n">
-        <v>25306.1273728446</v>
+        <v>108134.765586482</v>
       </c>
       <c r="C61" t="n">
-        <v>8739.64023960259</v>
+        <v>2.60460544585139</v>
       </c>
       <c r="D61" t="n">
-        <v>5211.40383585192</v>
+        <v>0.00451657556483353</v>
       </c>
       <c r="E61" t="n">
-        <v>82964.4160454323</v>
+        <v>5006800691.26465</v>
       </c>
       <c r="F61" t="n">
-        <v>164367.924519339</v>
+        <v>1950497103814.46</v>
       </c>
       <c r="G61" t="s">
         <v>65</v>
@@ -3072,16 +3072,16 @@
         <v>2773</v>
       </c>
       <c r="I61" t="n">
-        <v>22533</v>
+        <v>105362</v>
       </c>
       <c r="J61" t="s">
         <v>17</v>
       </c>
       <c r="K61" t="n">
-        <v>9.126</v>
+        <v>38.995</v>
       </c>
       <c r="L61" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="M61" t="s">
         <v>28</v>
@@ -3092,19 +3092,19 @@
         <v>44197</v>
       </c>
       <c r="B62" t="n">
-        <v>39185.1939769969</v>
+        <v>199544.242595082</v>
       </c>
       <c r="C62" t="n">
-        <v>12386.0019049687</v>
+        <v>1.20923797839871</v>
       </c>
       <c r="D62" t="n">
-        <v>7088.18106816738</v>
+        <v>0.00114275063205101</v>
       </c>
       <c r="E62" t="n">
-        <v>142647.132344371</v>
+        <v>28691562464.5602</v>
       </c>
       <c r="F62" t="n">
-        <v>300938.94232535</v>
+        <v>26470620878651.5</v>
       </c>
       <c r="G62" t="s">
         <v>65</v>
@@ -3113,13 +3113,13 @@
         <v>2083</v>
       </c>
       <c r="I62" t="n">
-        <v>37102</v>
+        <v>197461</v>
       </c>
       <c r="J62" t="s">
         <v>17</v>
       </c>
       <c r="K62" t="n">
-        <v>18.812</v>
+        <v>95.796</v>
       </c>
       <c r="L62" t="s">
         <v>66</v>
@@ -3133,19 +3133,19 @@
         <v>44228</v>
       </c>
       <c r="B63" t="n">
-        <v>46019.4319918879</v>
+        <v>277521.744465236</v>
       </c>
       <c r="C63" t="n">
-        <v>13341.4198100815</v>
+        <v>0.328620538338981</v>
       </c>
       <c r="D63" t="n">
-        <v>7346.09754184325</v>
+        <v>0.000179684905841331</v>
       </c>
       <c r="E63" t="n">
-        <v>186454.303481013</v>
+        <v>162280904381.574</v>
       </c>
       <c r="F63" t="n">
-        <v>420311.342693995</v>
+        <v>236366005951326</v>
       </c>
       <c r="G63" t="s">
         <v>65</v>
@@ -3154,13 +3154,13 @@
         <v>1814</v>
       </c>
       <c r="I63" t="n">
-        <v>44205</v>
+        <v>275708</v>
       </c>
       <c r="J63" t="s">
         <v>17</v>
       </c>
       <c r="K63" t="n">
-        <v>25.369</v>
+        <v>152.988</v>
       </c>
       <c r="L63" t="s">
         <v>66</v>
@@ -3174,19 +3174,19 @@
         <v>44256</v>
       </c>
       <c r="B64" t="n">
-        <v>44819.1137869866</v>
+        <v>252819.413865148</v>
       </c>
       <c r="C64" t="n">
-        <v>12368.9271447659</v>
+        <v>0.0771441281774991</v>
       </c>
       <c r="D64" t="n">
-        <v>6668.43718806343</v>
+        <v>0.0000125822020080386</v>
       </c>
       <c r="E64" t="n">
-        <v>193536.813337469</v>
+        <v>555844918612.219</v>
       </c>
       <c r="F64" t="n">
-        <v>454340.313396212</v>
+        <v>920257935361258</v>
       </c>
       <c r="G64" t="s">
         <v>65</v>
@@ -3195,13 +3195,13 @@
         <v>2157</v>
       </c>
       <c r="I64" t="n">
-        <v>42662</v>
+        <v>250662</v>
       </c>
       <c r="J64" t="s">
         <v>17</v>
       </c>
       <c r="K64" t="n">
-        <v>20.778</v>
+        <v>117.208</v>
       </c>
       <c r="L64" t="s">
         <v>66</v>
@@ -3215,19 +3215,19 @@
         <v>44287</v>
       </c>
       <c r="B65" t="n">
-        <v>27156.8158743909</v>
+        <v>145131.768784507</v>
       </c>
       <c r="C65" t="n">
-        <v>7740.08629337968</v>
+        <v>0.0110761301346282</v>
       </c>
       <c r="D65" t="n">
-        <v>4244.07962737848</v>
+        <v>0.000000590929704199397</v>
       </c>
       <c r="E65" t="n">
-        <v>113554.577739976</v>
+        <v>1340388703629.96</v>
       </c>
       <c r="F65" t="n">
-        <v>262134.585153496</v>
+        <v>5574659394853173</v>
       </c>
       <c r="G65" t="s">
         <v>65</v>
@@ -3236,13 +3236,13 @@
         <v>1388</v>
       </c>
       <c r="I65" t="n">
-        <v>25769</v>
+        <v>143744</v>
       </c>
       <c r="J65" t="s">
         <v>17</v>
       </c>
       <c r="K65" t="n">
-        <v>19.565</v>
+        <v>104.561</v>
       </c>
       <c r="L65" t="s">
         <v>66</v>
@@ -3256,19 +3256,19 @@
         <v>44317</v>
       </c>
       <c r="B66" t="n">
-        <v>22818.6997593848</v>
+        <v>155533.932621893</v>
       </c>
       <c r="C66" t="n">
-        <v>6556.77378245592</v>
+        <v>0.00221735151222512</v>
       </c>
       <c r="D66" t="n">
-        <v>3611.77038872125</v>
+        <v>0.0000000775970027382413</v>
       </c>
       <c r="E66" t="n">
-        <v>94737.0044497907</v>
+        <v>7498849499322.89</v>
       </c>
       <c r="F66" t="n">
-        <v>217991.603047653</v>
+        <v>53956330847507416</v>
       </c>
       <c r="G66" t="s">
         <v>65</v>
@@ -3277,13 +3277,13 @@
         <v>641</v>
       </c>
       <c r="I66" t="n">
-        <v>22178</v>
+        <v>154893</v>
       </c>
       <c r="J66" t="s">
         <v>17</v>
       </c>
       <c r="K66" t="n">
-        <v>35.598</v>
+        <v>242.639</v>
       </c>
       <c r="L66" t="s">
         <v>66</v>
@@ -3297,19 +3297,19 @@
         <v>44348</v>
       </c>
       <c r="B67" t="n">
-        <v>30998.2233739948</v>
+        <v>310421.053290781</v>
       </c>
       <c r="C67" t="n">
-        <v>8509.61013373528</v>
+        <v>0.000466228094487146</v>
       </c>
       <c r="D67" t="n">
-        <v>4588.09821659073</v>
+        <v>0.0000000259786194298613</v>
       </c>
       <c r="E67" t="n">
-        <v>135747.720672098</v>
+        <v>87940076756577.3</v>
       </c>
       <c r="F67" t="n">
-        <v>322442.424515013</v>
+        <v>1477067611806574080</v>
       </c>
       <c r="G67" t="s">
         <v>65</v>
@@ -3318,13 +3318,13 @@
         <v>558</v>
       </c>
       <c r="I67" t="n">
-        <v>30440</v>
+        <v>309863</v>
       </c>
       <c r="J67" t="s">
         <v>17</v>
       </c>
       <c r="K67" t="n">
-        <v>55.551</v>
+        <v>556.3</v>
       </c>
       <c r="L67" t="s">
         <v>66</v>
@@ -3338,19 +3338,19 @@
         <v>44378</v>
       </c>
       <c r="B68" t="n">
-        <v>35329.7644699922</v>
+        <v>532469.673064288</v>
       </c>
       <c r="C68" t="n">
-        <v>9477.72510710137</v>
+        <v>0.000115432219056015</v>
       </c>
       <c r="D68" t="n">
-        <v>5055.89451332804</v>
+        <v>0.00000000337342017062847</v>
       </c>
       <c r="E68" t="n">
-        <v>159018.567233704</v>
+        <v>557104418310171</v>
       </c>
       <c r="F68" t="n">
-        <v>384021.91376031</v>
+        <v>29083956846753189888</v>
       </c>
       <c r="G68" t="s">
         <v>65</v>
@@ -3359,13 +3359,13 @@
         <v>505</v>
       </c>
       <c r="I68" t="n">
-        <v>34825</v>
+        <v>531965</v>
       </c>
       <c r="J68" t="s">
         <v>17</v>
       </c>
       <c r="K68" t="n">
-        <v>69.959</v>
+        <v>1054.375</v>
       </c>
       <c r="L68" t="s">
         <v>66</v>
@@ -3379,19 +3379,19 @@
         <v>44409</v>
       </c>
       <c r="B69" t="n">
-        <v>36637.0504960747</v>
+        <v>791416.162831245</v>
       </c>
       <c r="C69" t="n">
-        <v>9708.98003641138</v>
+        <v>0.0000525379148092499</v>
       </c>
       <c r="D69" t="n">
-        <v>5151.20133075156</v>
+        <v>0.00000000109852716221498</v>
       </c>
       <c r="E69" t="n">
-        <v>167435.427106867</v>
+        <v>4229166624819932</v>
       </c>
       <c r="F69" t="n">
-        <v>408205.429374119</v>
+        <v>547861126797460307968</v>
       </c>
       <c r="G69" t="s">
         <v>65</v>
@@ -3400,13 +3400,13 @@
         <v>308</v>
       </c>
       <c r="I69" t="n">
-        <v>36329</v>
+        <v>791108</v>
       </c>
       <c r="J69" t="s">
         <v>17</v>
       </c>
       <c r="K69" t="n">
-        <v>118.948</v>
+        <v>2569.45</v>
       </c>
       <c r="L69" t="s">
         <v>66</v>
@@ -3420,19 +3420,19 @@
         <v>44440</v>
       </c>
       <c r="B70" t="n">
-        <v>51752.489457875</v>
+        <v>1011861.76258663</v>
       </c>
       <c r="C70" t="n">
-        <v>13013.6846614796</v>
+        <v>0.0000181007727148137</v>
       </c>
       <c r="D70" t="n">
-        <v>6736.99195325289</v>
+        <v>0.0000000000839199214237874</v>
       </c>
       <c r="E70" t="n">
-        <v>251515.268190693</v>
+        <v>27744886416275600</v>
       </c>
       <c r="F70" t="n">
-        <v>636122.447873634</v>
+        <v>15071199233731846996288</v>
       </c>
       <c r="G70" t="s">
         <v>65</v>
@@ -3441,13 +3441,13 @@
         <v>330</v>
       </c>
       <c r="I70" t="n">
-        <v>51422</v>
+        <v>1011532</v>
       </c>
       <c r="J70" t="s">
         <v>17</v>
       </c>
       <c r="K70" t="n">
-        <v>156.821</v>
+        <v>3066.155</v>
       </c>
       <c r="L70" t="s">
         <v>66</v>
@@ -3461,19 +3461,19 @@
         <v>44470</v>
       </c>
       <c r="B71" t="n">
-        <v>41009.9634829682</v>
+        <v>762326.065340525</v>
       </c>
       <c r="C71" t="n">
-        <v>10529.0672761123</v>
+        <v>0.00000145559308383719</v>
       </c>
       <c r="D71" t="n">
-        <v>5507.68433294396</v>
+        <v>0.0000000000053722221043259</v>
       </c>
       <c r="E71" t="n">
-        <v>194903.269429372</v>
+        <v>93170524249812672</v>
       </c>
       <c r="F71" t="n">
-        <v>486838.641437447</v>
+        <v>120413529218262763578202</v>
       </c>
       <c r="G71" t="s">
         <v>65</v>
@@ -3482,13 +3482,13 @@
         <v>304</v>
       </c>
       <c r="I71" t="n">
-        <v>40706</v>
+        <v>762022</v>
       </c>
       <c r="J71" t="s">
         <v>17</v>
       </c>
       <c r="K71" t="n">
-        <v>134.897</v>
+        <v>2507.569</v>
       </c>
       <c r="L71" t="s">
         <v>66</v>
@@ -3502,19 +3502,19 @@
         <v>44501</v>
       </c>
       <c r="B72" t="n">
-        <v>34226.5961245013</v>
+        <v>612756.219130381</v>
       </c>
       <c r="C72" t="n">
-        <v>8923.88032285447</v>
+        <v>0.000000136948897523273</v>
       </c>
       <c r="D72" t="n">
-        <v>4704.39138215186</v>
+        <v>0.000000000000180189277732695</v>
       </c>
       <c r="E72" t="n">
-        <v>160026.824541469</v>
+        <v>291651921722042176</v>
       </c>
       <c r="F72" t="n">
-        <v>396132.805670105</v>
+        <v>932660666076253239922448</v>
       </c>
       <c r="G72" t="s">
         <v>65</v>
@@ -3523,13 +3523,13 @@
         <v>504</v>
       </c>
       <c r="I72" t="n">
-        <v>33723</v>
+        <v>612252</v>
       </c>
       <c r="J72" t="s">
         <v>17</v>
       </c>
       <c r="K72" t="n">
-        <v>67.909</v>
+        <v>1215.762</v>
       </c>
       <c r="L72" t="s">
         <v>66</v>
@@ -3543,19 +3543,19 @@
         <v>44531</v>
       </c>
       <c r="B73" t="n">
-        <v>30243.5306200499</v>
+        <v>462097.732216002</v>
       </c>
       <c r="C73" t="n">
-        <v>7959.7862097803</v>
+        <v>0.0000000143313546131426</v>
       </c>
       <c r="D73" t="n">
-        <v>4216.46616781481</v>
+        <v>0.00000000000000763064464629873</v>
       </c>
       <c r="E73" t="n">
-        <v>140043.954393212</v>
+        <v>900412821175982080</v>
       </c>
       <c r="F73" t="n">
-        <v>344873.904122109</v>
+        <v>11596088812637740778602002</v>
       </c>
       <c r="G73" t="s">
         <v>65</v>
@@ -3564,13 +3564,13 @@
         <v>582</v>
       </c>
       <c r="I73" t="n">
-        <v>29662</v>
+        <v>461516</v>
       </c>
       <c r="J73" t="s">
         <v>17</v>
       </c>
       <c r="K73" t="n">
-        <v>51.964</v>
+        <v>793.969</v>
       </c>
       <c r="L73" t="s">
         <v>66</v>
@@ -3584,19 +3584,19 @@
         <v>44562</v>
       </c>
       <c r="B74" t="n">
-        <v>41894.7413067609</v>
+        <v>800075.152864363</v>
       </c>
       <c r="C74" t="n">
-        <v>10150.7496829759</v>
+        <v>0.0000000028106132733815</v>
       </c>
       <c r="D74" t="n">
-        <v>5181.22649246002</v>
+        <v>0.00000000000000055118892425442</v>
       </c>
       <c r="E74" t="n">
-        <v>214854.73646606</v>
+        <v>5616866340864987136</v>
       </c>
       <c r="F74" t="n">
-        <v>563642.562047577</v>
+        <v>152275675528014379750420282</v>
       </c>
       <c r="G74" t="s">
         <v>65</v>
@@ -3605,13 +3605,13 @@
         <v>1925</v>
       </c>
       <c r="I74" t="n">
-        <v>39970</v>
+        <v>798150</v>
       </c>
       <c r="J74" t="s">
         <v>17</v>
       </c>
       <c r="K74" t="n">
-        <v>21.763</v>
+        <v>415.621</v>
       </c>
       <c r="L74" t="s">
         <v>66</v>
@@ -3625,19 +3625,19 @@
         <v>44593</v>
       </c>
       <c r="B75" t="n">
-        <v>46726.2095850249</v>
+        <v>1052913.35879585</v>
       </c>
       <c r="C75" t="n">
-        <v>10462.2539026424</v>
+        <v>0.000000000682235896698557</v>
       </c>
       <c r="D75" t="n">
-        <v>5163.51192408543</v>
+        <v>0.0000000000000000348664418257195</v>
       </c>
       <c r="E75" t="n">
-        <v>265624.931061148</v>
+        <v>46817400003290218496</v>
       </c>
       <c r="F75" t="n">
-        <v>744462.541460032</v>
+        <v>3307325919534645430402084868</v>
       </c>
       <c r="G75" t="s">
         <v>65</v>
@@ -3646,13 +3646,13 @@
         <v>2075</v>
       </c>
       <c r="I75" t="n">
-        <v>44651</v>
+        <v>1050838</v>
       </c>
       <c r="J75" t="s">
         <v>17</v>
       </c>
       <c r="K75" t="n">
-        <v>22.519</v>
+        <v>507.426</v>
       </c>
       <c r="L75" t="s">
         <v>66</v>
@@ -3666,19 +3666,19 @@
         <v>44621</v>
       </c>
       <c r="B76" t="n">
-        <v>45359.5749167557</v>
+        <v>925528.695036291</v>
       </c>
       <c r="C76" t="n">
-        <v>9697.26116761739</v>
+        <v>0.0000000000880284241999778</v>
       </c>
       <c r="D76" t="n">
-        <v>4697.04672337675</v>
+        <v>0.00000000000000000177891663061899</v>
       </c>
       <c r="E76" t="n">
-        <v>274761.96552137</v>
+        <v>273658949903650226186</v>
       </c>
       <c r="F76" t="n">
-        <v>803159.391281604</v>
+        <v>32484141757443762778604444240</v>
       </c>
       <c r="G76" t="s">
         <v>65</v>
@@ -3687,13 +3687,13 @@
         <v>4287</v>
       </c>
       <c r="I76" t="n">
-        <v>41073</v>
+        <v>921242</v>
       </c>
       <c r="J76" t="s">
         <v>17</v>
       </c>
       <c r="K76" t="n">
-        <v>10.581</v>
+        <v>215.891</v>
       </c>
       <c r="L76" t="s">
         <v>66</v>
@@ -3707,19 +3707,19 @@
         <v>44652</v>
       </c>
       <c r="B77" t="n">
-        <v>30407.4129105097</v>
+        <v>508020.283008632</v>
       </c>
       <c r="C77" t="n">
-        <v>6690.5544725944</v>
+        <v>0.00000000000783309979507574</v>
       </c>
       <c r="D77" t="n">
-        <v>3290.70661787062</v>
+        <v>0.0000000000000000000709789331584831</v>
       </c>
       <c r="E77" t="n">
-        <v>179129.999076005</v>
+        <v>878474519529441984582</v>
       </c>
       <c r="F77" t="n">
-        <v>516339.093836268</v>
+        <v>458910575750925996128424020842</v>
       </c>
       <c r="G77" t="s">
         <v>65</v>
@@ -3728,13 +3728,13 @@
         <v>2013</v>
       </c>
       <c r="I77" t="n">
-        <v>28394</v>
+        <v>506007</v>
       </c>
       <c r="J77" t="s">
         <v>17</v>
       </c>
       <c r="K77" t="n">
-        <v>15.105</v>
+        <v>252.368</v>
       </c>
       <c r="L77" t="s">
         <v>66</v>
@@ -3748,19 +3748,19 @@
         <v>44682</v>
       </c>
       <c r="B78" t="n">
-        <v>26840.0992429917</v>
+        <v>531821.923506323</v>
       </c>
       <c r="C78" t="n">
-        <v>5925.3292670231</v>
+        <v>0.00000000000221823704757319</v>
       </c>
       <c r="D78" t="n">
-        <v>2921.63483413047</v>
+        <v>0.00000000000000000000691976888947113</v>
       </c>
       <c r="E78" t="n">
-        <v>157979.292868394</v>
+        <v>7313570128653664125808</v>
       </c>
       <c r="F78" t="n">
-        <v>455764.123684396</v>
+        <v>11969749824392788048062428264442</v>
       </c>
       <c r="G78" t="s">
         <v>65</v>
@@ -3769,13 +3769,13 @@
         <v>1209</v>
       </c>
       <c r="I78" t="n">
-        <v>25631</v>
+        <v>530613</v>
       </c>
       <c r="J78" t="s">
         <v>17</v>
       </c>
       <c r="K78" t="n">
-        <v>22.2</v>
+        <v>439.882</v>
       </c>
       <c r="L78" t="s">
         <v>66</v>
@@ -3789,19 +3789,19 @@
         <v>44713</v>
       </c>
       <c r="B79" t="n">
-        <v>34614.6436644904</v>
+        <v>1030328.64284233</v>
       </c>
       <c r="C79" t="n">
-        <v>7289.90489311192</v>
+        <v>0.000000000000522378284657193</v>
       </c>
       <c r="D79" t="n">
-        <v>3518.15602232647</v>
+        <v>0.00000000000000000000120008390832249</v>
       </c>
       <c r="E79" t="n">
-        <v>215740.049905894</v>
+        <v>120573113880024665032866</v>
       </c>
       <c r="F79" t="n">
-        <v>644623.984525605</v>
+        <v>375457166254949885524822688024224</v>
       </c>
       <c r="G79" t="s">
         <v>65</v>
@@ -3810,13 +3810,13 @@
         <v>1636</v>
       </c>
       <c r="I79" t="n">
-        <v>32979</v>
+        <v>1028693</v>
       </c>
       <c r="J79" t="s">
         <v>17</v>
       </c>
       <c r="K79" t="n">
-        <v>21.158</v>
+        <v>629.781</v>
       </c>
       <c r="L79" t="s">
         <v>66</v>
@@ -3830,19 +3830,19 @@
         <v>44743</v>
       </c>
       <c r="B80" t="n">
-        <v>38684.6338093892</v>
+        <v>1685654.01741633</v>
       </c>
       <c r="C80" t="n">
-        <v>7944.19401531186</v>
+        <v>0.000000000000086588732654083</v>
       </c>
       <c r="D80" t="n">
-        <v>3791.05941558837</v>
+        <v>0.0000000000000000000000884198669709445</v>
       </c>
       <c r="E80" t="n">
-        <v>248798.268445528</v>
+        <v>2584259677704325880064868</v>
       </c>
       <c r="F80" t="n">
-        <v>758108.701086432</v>
+        <v>15257767978579207267248444008682862</v>
       </c>
       <c r="G80" t="s">
         <v>65</v>
@@ -3851,13 +3851,13 @@
         <v>3656</v>
       </c>
       <c r="I80" t="n">
-        <v>35029</v>
+        <v>1681998</v>
       </c>
       <c r="J80" t="s">
         <v>17</v>
       </c>
       <c r="K80" t="n">
-        <v>10.581</v>
+        <v>461.064</v>
       </c>
       <c r="L80" t="s">
         <v>66</v>
@@ -3871,19 +3871,19 @@
         <v>44774</v>
       </c>
       <c r="B81" t="n">
-        <v>40153.9940191463</v>
+        <v>2438249.93578897</v>
       </c>
       <c r="C81" t="n">
-        <v>8120.52687007729</v>
+        <v>0.0000000000000340770353326122</v>
       </c>
       <c r="D81" t="n">
-        <v>3849.95193962083</v>
+        <v>0.0000000000000000000000026673173297355</v>
       </c>
       <c r="E81" t="n">
-        <v>263477.474781579</v>
+        <v>38055732345014742812820848</v>
       </c>
       <c r="F81" t="n">
-        <v>813274.60838863</v>
+        <v>1899596388747923750244848844240026048</v>
       </c>
       <c r="G81" t="s">
         <v>65</v>
@@ -3892,16 +3892,16 @@
         <v>8548</v>
       </c>
       <c r="I81" t="n">
-        <v>31606</v>
+        <v>2429702</v>
       </c>
       <c r="J81" t="s">
         <v>17</v>
       </c>
       <c r="K81" t="n">
-        <v>4.697</v>
+        <v>285.242</v>
       </c>
       <c r="L81" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="M81" t="s">
         <v>48</v>
@@ -3912,19 +3912,19 @@
         <v>44805</v>
       </c>
       <c r="B82" t="n">
-        <v>52295.1925879847</v>
+        <v>3145159.02999882</v>
       </c>
       <c r="C82" t="n">
-        <v>10052.0329159779</v>
+        <v>0.00000000000000683253188743688</v>
       </c>
       <c r="D82" t="n">
-        <v>4657.25344041177</v>
+        <v>0.0000000000000000000000000528024771236654</v>
       </c>
       <c r="E82" t="n">
-        <v>365128.421547105</v>
+        <v>270893695496802557264862484</v>
       </c>
       <c r="F82" t="n">
-        <v>1170980.94381573</v>
+        <v>166491446502892833408086066444420242068</v>
       </c>
       <c r="G82" t="s">
         <v>65</v>
@@ -3933,16 +3933,16 @@
         <v>19572</v>
       </c>
       <c r="I82" t="n">
-        <v>32723</v>
+        <v>3125587</v>
       </c>
       <c r="J82" t="s">
         <v>17</v>
       </c>
       <c r="K82" t="n">
-        <v>2.672</v>
+        <v>160.697</v>
       </c>
       <c r="L82" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="M82" t="s">
         <v>49</v>
@@ -3953,19 +3953,19 @@
         <v>44835</v>
       </c>
       <c r="B83" t="n">
-        <v>43021.8064324778</v>
+        <v>2377397.35662467</v>
       </c>
       <c r="C83" t="n">
-        <v>8425.39992609669</v>
+        <v>0.000000000000000709211213926289</v>
       </c>
       <c r="D83" t="n">
-        <v>3940.56874203087</v>
+        <v>0.00000000000000000000000000160669046017634</v>
       </c>
       <c r="E83" t="n">
-        <v>294526.378224409</v>
+        <v>2384017289667170328264428444</v>
       </c>
       <c r="F83" t="n">
-        <v>934455.917200329</v>
+        <v>2241353976111817067206442864046480800282</v>
       </c>
       <c r="G83" t="s">
         <v>65</v>
@@ -3974,16 +3974,16 @@
         <v>18319</v>
       </c>
       <c r="I83" t="n">
-        <v>24703</v>
+        <v>2359078</v>
       </c>
       <c r="J83" t="s">
         <v>17</v>
       </c>
       <c r="K83" t="n">
-        <v>2.348</v>
+        <v>129.778</v>
       </c>
       <c r="L83" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="M83" t="s">
         <v>50</v>
@@ -3994,19 +3994,19 @@
         <v>44866</v>
       </c>
       <c r="B84" t="n">
-        <v>37165.5003691662</v>
+        <v>1869001.64325242</v>
       </c>
       <c r="C84" t="n">
-        <v>7369.89645479685</v>
+        <v>0.0000000000000000726789433444389</v>
       </c>
       <c r="D84" t="n">
-        <v>3469.25568656566</v>
+        <v>0.000000000000000000000000000122241653825145</v>
       </c>
       <c r="E84" t="n">
-        <v>251245.684038089</v>
+        <v>18748370488061958522606004680</v>
       </c>
       <c r="F84" t="n">
-        <v>791883.925807271</v>
+        <v>22765582201399467772264440002248288400066</v>
       </c>
       <c r="G84" t="s">
         <v>65</v>
@@ -4015,16 +4015,16 @@
         <v>11554</v>
       </c>
       <c r="I84" t="n">
-        <v>25612</v>
+        <v>1857448</v>
       </c>
       <c r="J84" t="s">
         <v>17</v>
       </c>
       <c r="K84" t="n">
-        <v>3.217</v>
+        <v>161.762</v>
       </c>
       <c r="L84" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="M84" t="s">
         <v>51</v>
@@ -4035,19 +4035,19 @@
         <v>44896</v>
       </c>
       <c r="B85" t="n">
-        <v>33858.7179711844</v>
+        <v>1404841.42839724</v>
       </c>
       <c r="C85" t="n">
-        <v>6752.51084871241</v>
+        <v>0.0000000000000000105623543883411</v>
       </c>
       <c r="D85" t="n">
-        <v>3188.88264628378</v>
+        <v>0.00000000000000000000000000000409141339430636</v>
       </c>
       <c r="E85" t="n">
-        <v>227779.655853086</v>
+        <v>151487773154279633824604606060</v>
       </c>
       <c r="F85" t="n">
-        <v>716430.08153826</v>
+        <v>571180567659679792800662800404608266620000</v>
       </c>
       <c r="G85" t="s">
         <v>65</v>
@@ -4056,16 +4056,16 @@
         <v>6520</v>
       </c>
       <c r="I85" t="n">
-        <v>27339</v>
+        <v>1398321</v>
       </c>
       <c r="J85" t="s">
         <v>17</v>
       </c>
       <c r="K85" t="n">
-        <v>5.193</v>
+        <v>215.466</v>
       </c>
       <c r="L85" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="M85" t="s">
         <v>52</v>
@@ -4076,19 +4076,19 @@
         <v>44927</v>
       </c>
       <c r="B86" t="n">
-        <v>44668.3909673076</v>
+        <v>2443799.17940242</v>
       </c>
       <c r="C86" t="n">
-        <v>8281.03945355599</v>
+        <v>0.00000000000000000165087409208068</v>
       </c>
       <c r="D86" t="n">
-        <v>3787.7445206392</v>
+        <v>0.000000000000000000000000000000435862344807599</v>
       </c>
       <c r="E86" t="n">
-        <v>329778.122590086</v>
+        <v>3842805798396407780462206400068</v>
       </c>
       <c r="F86" t="n">
-        <v>1100184.68577423</v>
+        <v>15386140053895368762688482846088626668860226</v>
       </c>
       <c r="G86" t="s">
         <v>65</v>
@@ -4097,16 +4097,16 @@
         <v>10129</v>
       </c>
       <c r="I86" t="n">
-        <v>34539</v>
+        <v>2433670</v>
       </c>
       <c r="J86" t="s">
         <v>17</v>
       </c>
       <c r="K86" t="n">
-        <v>4.41</v>
+        <v>241.267</v>
       </c>
       <c r="L86" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="M86" t="s">
         <v>53</v>
@@ -4117,19 +4117,19 @@
         <v>44958</v>
       </c>
       <c r="B87" t="n">
-        <v>49160.7007693464</v>
+        <v>3282354.04260765</v>
       </c>
       <c r="C87" t="n">
-        <v>8590.73771767565</v>
+        <v>0.000000000000000000255643040073462</v>
       </c>
       <c r="D87" t="n">
-        <v>3834.66112903595</v>
+        <v>0.0000000000000000000000000000000465976245214565</v>
       </c>
       <c r="E87" t="n">
-        <v>393230.65900981</v>
+        <v>93320641846864680400224206406802</v>
       </c>
       <c r="F87" t="n">
-        <v>1383104.30729336</v>
+        <v>244880823003493852246822004488048848668424208</v>
       </c>
       <c r="G87" t="s">
         <v>65</v>
@@ -4138,16 +4138,16 @@
         <v>15673</v>
       </c>
       <c r="I87" t="n">
-        <v>33488</v>
+        <v>3266681</v>
       </c>
       <c r="J87" t="s">
         <v>17</v>
       </c>
       <c r="K87" t="n">
-        <v>3.137</v>
+        <v>209.427</v>
       </c>
       <c r="L87" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="M87" t="s">
         <v>54</v>
@@ -4158,19 +4158,19 @@
         <v>44986</v>
       </c>
       <c r="B88" t="n">
-        <v>48106.2767441886</v>
+        <v>2849665.60574127</v>
       </c>
       <c r="C88" t="n">
-        <v>8134.84537721831</v>
+        <v>0.0000000000000000000233977524290045</v>
       </c>
       <c r="D88" t="n">
-        <v>3585.5880626293</v>
+        <v>0.00000000000000000000000000000000162145985922657</v>
       </c>
       <c r="E88" t="n">
-        <v>403586.872349901</v>
+        <v>372031480511376898560004402868028</v>
       </c>
       <c r="F88" t="n">
-        <v>1466770.62918513</v>
+        <v>8018450450171548036888882068020684646280846462</v>
       </c>
       <c r="G88" t="s">
         <v>65</v>
@@ -4179,16 +4179,16 @@
         <v>15196</v>
       </c>
       <c r="I88" t="n">
-        <v>32910</v>
+        <v>2834470</v>
       </c>
       <c r="J88" t="s">
         <v>17</v>
       </c>
       <c r="K88" t="n">
-        <v>3.166</v>
+        <v>187.527</v>
       </c>
       <c r="L88" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="M88" t="s">
         <v>55</v>
@@ -4199,19 +4199,19 @@
         <v>45017</v>
       </c>
       <c r="B89" t="n">
-        <v>34571.8936458794</v>
+        <v>1567688.7805624</v>
       </c>
       <c r="C89" t="n">
-        <v>6030.41411661015</v>
+        <v>0.00000000000000000000101230116124807</v>
       </c>
       <c r="D89" t="n">
-        <v>2700.82598306015</v>
+        <v>0.0000000000000000000000000000000000319835893725185</v>
       </c>
       <c r="E89" t="n">
-        <v>281038.435166286</v>
+        <v>1730973368149162467468406402282062</v>
       </c>
       <c r="F89" t="n">
-        <v>1004613.98344074</v>
+        <v>164252762982902645322040888082886868062468648080</v>
       </c>
       <c r="G89" t="s">
         <v>65</v>
@@ -4220,16 +4220,16 @@
         <v>7717</v>
       </c>
       <c r="I89" t="n">
-        <v>26855</v>
+        <v>1559972</v>
       </c>
       <c r="J89" t="s">
         <v>17</v>
       </c>
       <c r="K89" t="n">
-        <v>4.48</v>
+        <v>203.147</v>
       </c>
       <c r="L89" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="M89" t="s">
         <v>56</v>
@@ -4240,19 +4240,19 @@
         <v>45047</v>
       </c>
       <c r="B90" t="n">
-        <v>31020.6798122436</v>
+        <v>1598882.66953988</v>
       </c>
       <c r="C90" t="n">
-        <v>5431.1155590984</v>
+        <v>0.000000000000000000000121764595598695</v>
       </c>
       <c r="D90" t="n">
-        <v>2439.10834738748</v>
+        <v>0.00000000000000000000000000000000000155003742150985</v>
       </c>
       <c r="E90" t="n">
-        <v>251925.809836865</v>
+        <v>19312640808491091324280408400204600</v>
       </c>
       <c r="F90" t="n">
-        <v>901456.714271941</v>
+        <v>7322677051812927680000480642426842242880224640646</v>
       </c>
       <c r="G90" t="s">
         <v>65</v>
@@ -4261,16 +4261,16 @@
         <v>6519</v>
       </c>
       <c r="I90" t="n">
-        <v>24502</v>
+        <v>1592364</v>
       </c>
       <c r="J90" t="s">
         <v>17</v>
       </c>
       <c r="K90" t="n">
-        <v>4.758</v>
+        <v>245.265</v>
       </c>
       <c r="L90" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="M90" t="s">
         <v>57</v>
@@ -4281,19 +4281,19 @@
         <v>45078</v>
       </c>
       <c r="B91" t="n">
-        <v>38198.9386979223</v>
+        <v>3094419.58431866</v>
       </c>
       <c r="C91" t="n">
-        <v>6390.27695815804</v>
+        <v>0.0000000000000000000000165530066287904</v>
       </c>
       <c r="D91" t="n">
-        <v>2812.60411509585</v>
+        <v>0.0000000000000000000000000000000000000787375279706452</v>
       </c>
       <c r="E91" t="n">
-        <v>328507.256308641</v>
+        <v>445762434514459579520080040446082604</v>
       </c>
       <c r="F91" t="n">
-        <v>1218612.85292282</v>
+        <v>850501099929186521364282802222268886048402464680062</v>
       </c>
       <c r="G91" t="s">
         <v>65</v>
@@ -4302,16 +4302,16 @@
         <v>11446</v>
       </c>
       <c r="I91" t="n">
-        <v>26753</v>
+        <v>3082974</v>
       </c>
       <c r="J91" t="s">
         <v>17</v>
       </c>
       <c r="K91" t="n">
-        <v>3.337</v>
+        <v>270.349</v>
       </c>
       <c r="L91" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="M91" t="s">
         <v>58</v>
@@ -4322,19 +4322,19 @@
         <v>45108</v>
       </c>
       <c r="B92" t="n">
-        <v>41785.6022753753</v>
+        <v>5095129.12467555</v>
       </c>
       <c r="C92" t="n">
-        <v>6817.41171936709</v>
+        <v>0.00000000000000000000000379836086028631</v>
       </c>
       <c r="D92" t="n">
-        <v>2968.43895263968</v>
+        <v>0.00000000000000000000000000000000000000328782629149905</v>
       </c>
       <c r="E92" t="n">
-        <v>371244.826678332</v>
+        <v>5516608744350111479844884624880888280</v>
       </c>
       <c r="F92" t="n">
-        <v>1406302.98708811</v>
+        <v>117101429234016167394086002644244280022488646844680200</v>
       </c>
       <c r="G92" t="s">
         <v>65</v>
@@ -4343,16 +4343,16 @@
         <v>26877</v>
       </c>
       <c r="I92" t="n">
-        <v>14909</v>
+        <v>5068252</v>
       </c>
       <c r="J92" t="s">
         <v>17</v>
       </c>
       <c r="K92" t="n">
-        <v>1.555</v>
+        <v>189.572</v>
       </c>
       <c r="L92" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="M92" t="s">
         <v>59</v>
@@ -4363,19 +4363,19 @@
         <v>45139</v>
       </c>
       <c r="B93" t="n">
-        <v>42977.532774327</v>
+        <v>7307103.16138789</v>
       </c>
       <c r="C93" t="n">
-        <v>6904.86845867806</v>
+        <v>0.000000000000000000000000311761832498374</v>
       </c>
       <c r="D93" t="n">
-        <v>2987.70971403528</v>
+        <v>0.000000000000000000000000000000000000000068495686686604</v>
       </c>
       <c r="E93" t="n">
-        <v>389999.296892614</v>
+        <v>49780084479229471624420806208064024428</v>
       </c>
       <c r="F93" t="n">
-        <v>1498338.03623051</v>
+        <v>12663422667913967713806624088882222286488060606268440204</v>
       </c>
       <c r="G93" t="s">
         <v>65</v>
@@ -4384,16 +4384,16 @@
         <v>56671</v>
       </c>
       <c r="I93" t="n">
-        <v>-13693</v>
+        <v>7250432</v>
       </c>
       <c r="J93" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K93" t="n">
-        <v>0.758</v>
+        <v>128.939</v>
       </c>
       <c r="L93" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="M93" t="s">
         <v>60</v>
@@ -4404,19 +4404,19 @@
         <v>45170</v>
       </c>
       <c r="B94" t="n">
-        <v>53595.2302604067</v>
+        <v>9256264.76361762</v>
       </c>
       <c r="C94" t="n">
-        <v>8196.65422823081</v>
+        <v>0.0000000000000000000000000400875906922208</v>
       </c>
       <c r="D94" t="n">
-        <v>3470.40653255435</v>
+        <v>0.00000000000000000000000000000000000000000183528759045371</v>
       </c>
       <c r="E94" t="n">
-        <v>517619.296388022</v>
+        <v>731869481799268370880868686042222002402</v>
       </c>
       <c r="F94" t="n">
-        <v>2068448.54562734</v>
+        <v>1786191233464566020804888228228428826482048682604420642882</v>
       </c>
       <c r="G94" t="s">
         <v>65</v>
@@ -4425,16 +4425,16 @@
         <v>129898</v>
       </c>
       <c r="I94" t="n">
-        <v>-76303</v>
+        <v>9126367</v>
       </c>
       <c r="J94" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K94" t="n">
-        <v>0.413</v>
+        <v>71.258</v>
       </c>
       <c r="L94" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="M94" t="s">
         <v>61</v>
@@ -4445,19 +4445,19 @@
         <v>45200</v>
       </c>
       <c r="B95" t="n">
-        <v>45795.6229816455</v>
+        <v>6961229.17373436</v>
       </c>
       <c r="C95" t="n">
-        <v>7114.7332202481</v>
+        <v>0.00000000000000000000000000314586709378607</v>
       </c>
       <c r="D95" t="n">
-        <v>3036.64459434812</v>
+        <v>0.0000000000000000000000000000000000000000000354792538899494</v>
       </c>
       <c r="E95" t="n">
-        <v>435229.814254606</v>
+        <v>9858735129873158383266400442884048846462</v>
       </c>
       <c r="F95" t="n">
-        <v>1724485.33523417</v>
+        <v>157344169376694339466028488800426042886662242648682404448602</v>
       </c>
       <c r="G95" t="s">
         <v>65</v>
@@ -4466,16 +4466,16 @@
         <v>98281</v>
       </c>
       <c r="I95" t="n">
-        <v>-52485</v>
+        <v>6862948</v>
       </c>
       <c r="J95" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K95" t="n">
-        <v>0.466</v>
+        <v>70.83</v>
       </c>
       <c r="L95" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="M95" t="s">
         <v>62</v>
@@ -4486,19 +4486,19 @@
         <v>45231</v>
       </c>
       <c r="B96" t="n">
-        <v>40615.6908994606</v>
+        <v>5491253.18357623</v>
       </c>
       <c r="C96" t="n">
-        <v>6374.93110224788</v>
+        <v>0.000000000000000000000000000141236041325343</v>
       </c>
       <c r="D96" t="n">
-        <v>2735.82304667299</v>
+        <v>0.000000000000000000000000000000000000000000000831322379354401</v>
       </c>
       <c r="E96" t="n">
-        <v>382280.831547203</v>
+        <v>98118147376842276738688022246460462662240</v>
       </c>
       <c r="F96" t="n">
-        <v>1507618.20329807</v>
+        <v>6992516606205256810888606026684848846248824400628846028440066</v>
       </c>
       <c r="G96" t="s">
         <v>65</v>
@@ -4507,16 +4507,16 @@
         <v>65841</v>
       </c>
       <c r="I96" t="n">
-        <v>-25225</v>
+        <v>5425412</v>
       </c>
       <c r="J96" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K96" t="n">
-        <v>0.617</v>
+        <v>83.402</v>
       </c>
       <c r="L96" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="M96" t="s">
         <v>63</v>
@@ -4527,19 +4527,19 @@
         <v>45261</v>
       </c>
       <c r="B97" t="n">
-        <v>37535.2903889886</v>
+        <v>4155067.69104445</v>
       </c>
       <c r="C97" t="n">
-        <v>5915.82580644763</v>
+        <v>0.00000000000000000000000000000869398287518479</v>
       </c>
       <c r="D97" t="n">
-        <v>2545.4345671624</v>
+        <v>0.0000000000000000000000000000000000000000000000233915303208813</v>
       </c>
       <c r="E97" t="n">
-        <v>352395.69652777</v>
+        <v>703792934033039263460666664646624644660606</v>
       </c>
       <c r="F97" t="n">
-        <v>1389193.49826467</v>
+        <v>213152127941016812620402800286808008004868048842064466064024004</v>
       </c>
       <c r="G97" t="s">
         <v>65</v>
@@ -4548,16 +4548,16 @@
         <v>42725</v>
       </c>
       <c r="I97" t="n">
-        <v>-5190</v>
+        <v>4112343</v>
       </c>
       <c r="J97" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K97" t="n">
-        <v>0.879</v>
+        <v>97.251</v>
       </c>
       <c r="L97" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="M97" t="s">
         <v>64</v>
@@ -4568,19 +4568,19 @@
         <v>43831</v>
       </c>
       <c r="B98" t="n">
-        <v>1247.85036128434</v>
+        <v>1314.11144388969</v>
       </c>
       <c r="C98" t="n">
-        <v>820.543381061309</v>
+        <v>1110.4003918757</v>
       </c>
       <c r="D98" t="n">
-        <v>728.436138665204</v>
+        <v>987.194031032428</v>
       </c>
       <c r="E98" t="n">
-        <v>1541.55203714607</v>
+        <v>1575.50638399222</v>
       </c>
       <c r="F98" t="n">
-        <v>1668.26539384492</v>
+        <v>1716.81062828322</v>
       </c>
       <c r="G98" t="s">
         <v>67</v>
@@ -4589,13 +4589,13 @@
         <v>1382</v>
       </c>
       <c r="I98" t="n">
-        <v>-134</v>
+        <v>-68</v>
       </c>
       <c r="J98" t="s">
         <v>14</v>
       </c>
       <c r="K98" t="n">
-        <v>0.903</v>
+        <v>0.951</v>
       </c>
       <c r="L98" t="s">
         <v>15</v>
@@ -4609,19 +4609,19 @@
         <v>43862</v>
       </c>
       <c r="B99" t="n">
-        <v>889.76380278569</v>
+        <v>936.280820110512</v>
       </c>
       <c r="C99" t="n">
-        <v>589.325835172614</v>
+        <v>746.835653454045</v>
       </c>
       <c r="D99" t="n">
-        <v>499.768508445293</v>
+        <v>656.555570406603</v>
       </c>
       <c r="E99" t="n">
-        <v>1132.74080341762</v>
+        <v>1193.346613905</v>
       </c>
       <c r="F99" t="n">
-        <v>1262.72202311251</v>
+        <v>1348.01838805727</v>
       </c>
       <c r="G99" t="s">
         <v>67</v>
@@ -4630,13 +4630,13 @@
         <v>935</v>
       </c>
       <c r="I99" t="n">
-        <v>-45</v>
+        <v>1</v>
       </c>
       <c r="J99" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K99" t="n">
-        <v>0.952</v>
+        <v>1.001</v>
       </c>
       <c r="L99" t="s">
         <v>15</v>
@@ -4650,19 +4650,19 @@
         <v>43891</v>
       </c>
       <c r="B100" t="n">
-        <v>865.588337094806</v>
+        <v>910.648392251448</v>
       </c>
       <c r="C100" t="n">
-        <v>536.964124358242</v>
+        <v>674.452091215567</v>
       </c>
       <c r="D100" t="n">
-        <v>443.62670683748</v>
+        <v>571.678468788626</v>
       </c>
       <c r="E100" t="n">
-        <v>1167.51145468654</v>
+        <v>1215.23024958871</v>
       </c>
       <c r="F100" t="n">
-        <v>1331.60850198316</v>
+        <v>1411.73959017987</v>
       </c>
       <c r="G100" t="s">
         <v>67</v>
@@ -4671,13 +4671,13 @@
         <v>891</v>
       </c>
       <c r="I100" t="n">
-        <v>-25</v>
+        <v>20</v>
       </c>
       <c r="J100" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K100" t="n">
-        <v>0.971</v>
+        <v>1.022</v>
       </c>
       <c r="L100" t="s">
         <v>15</v>
@@ -4691,19 +4691,19 @@
         <v>43922</v>
       </c>
       <c r="B101" t="n">
-        <v>800.892396156355</v>
+        <v>843.722494827421</v>
       </c>
       <c r="C101" t="n">
-        <v>528.276632844824</v>
+        <v>583.784469327055</v>
       </c>
       <c r="D101" t="n">
-        <v>458.724509449696</v>
+        <v>478.875581969702</v>
       </c>
       <c r="E101" t="n">
-        <v>1139.32624713849</v>
+        <v>1201.27533557543</v>
       </c>
       <c r="F101" t="n">
-        <v>1340.55281005639</v>
+        <v>1434.6337731767</v>
       </c>
       <c r="G101" t="s">
         <v>67</v>
@@ -4712,13 +4712,13 @@
         <v>674</v>
       </c>
       <c r="I101" t="n">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c r="J101" t="s">
         <v>17</v>
       </c>
       <c r="K101" t="n">
-        <v>1.188</v>
+        <v>1.252</v>
       </c>
       <c r="L101" t="s">
         <v>15</v>
@@ -4732,19 +4732,19 @@
         <v>43952</v>
       </c>
       <c r="B102" t="n">
-        <v>786.042584183418</v>
+        <v>847.720442846605</v>
       </c>
       <c r="C102" t="n">
-        <v>483.135425610558</v>
+        <v>558.71942157996</v>
       </c>
       <c r="D102" t="n">
-        <v>401.222159086689</v>
+        <v>438.519225426218</v>
       </c>
       <c r="E102" t="n">
-        <v>1222.58903802798</v>
+        <v>1266.83665204756</v>
       </c>
       <c r="F102" t="n">
-        <v>1507.45433068156</v>
+        <v>1638.05533836135</v>
       </c>
       <c r="G102" t="s">
         <v>67</v>
@@ -4753,13 +4753,13 @@
         <v>686</v>
       </c>
       <c r="I102" t="n">
-        <v>100</v>
+        <v>162</v>
       </c>
       <c r="J102" t="s">
         <v>17</v>
       </c>
       <c r="K102" t="n">
-        <v>1.146</v>
+        <v>1.236</v>
       </c>
       <c r="L102" t="s">
         <v>15</v>
@@ -4773,19 +4773,19 @@
         <v>43983</v>
       </c>
       <c r="B103" t="n">
-        <v>731.39109831325</v>
+        <v>793.525688891121</v>
       </c>
       <c r="C103" t="n">
-        <v>425.531633944141</v>
+        <v>482.79144190147</v>
       </c>
       <c r="D103" t="n">
-        <v>325.631380361327</v>
+        <v>379.561716736593</v>
       </c>
       <c r="E103" t="n">
-        <v>1230.60163580979</v>
+        <v>1276.19979034433</v>
       </c>
       <c r="F103" t="n">
-        <v>1567.21186488005</v>
+        <v>1709.80233695079</v>
       </c>
       <c r="G103" t="s">
         <v>67</v>
@@ -4794,13 +4794,13 @@
         <v>722</v>
       </c>
       <c r="I103" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="J103" t="s">
         <v>17</v>
       </c>
       <c r="K103" t="n">
-        <v>1.013</v>
+        <v>1.099</v>
       </c>
       <c r="L103" t="s">
         <v>15</v>
@@ -4814,19 +4814,19 @@
         <v>44013</v>
       </c>
       <c r="B104" t="n">
-        <v>703.734600003869</v>
+        <v>780.479721431668</v>
       </c>
       <c r="C104" t="n">
-        <v>398.631943208977</v>
+        <v>434.339977921457</v>
       </c>
       <c r="D104" t="n">
-        <v>330.631340640638</v>
+        <v>336.054685085079</v>
       </c>
       <c r="E104" t="n">
-        <v>1279.41004529287</v>
+        <v>1373.14966112741</v>
       </c>
       <c r="F104" t="n">
-        <v>1691.5948973322</v>
+        <v>1930.15362115226</v>
       </c>
       <c r="G104" t="s">
         <v>67</v>
@@ -4835,13 +4835,13 @@
         <v>666</v>
       </c>
       <c r="I104" t="n">
-        <v>38</v>
+        <v>114</v>
       </c>
       <c r="J104" t="s">
         <v>17</v>
       </c>
       <c r="K104" t="n">
-        <v>1.057</v>
+        <v>1.172</v>
       </c>
       <c r="L104" t="s">
         <v>15</v>
@@ -4855,19 +4855,19 @@
         <v>44044</v>
       </c>
       <c r="B105" t="n">
-        <v>695.636385787942</v>
+        <v>776.49968626889</v>
       </c>
       <c r="C105" t="n">
-        <v>376.315942971225</v>
+        <v>405.138322267785</v>
       </c>
       <c r="D105" t="n">
-        <v>302.200273291083</v>
+        <v>282.856712937878</v>
       </c>
       <c r="E105" t="n">
-        <v>1382.5422692484</v>
+        <v>1442.74000933</v>
       </c>
       <c r="F105" t="n">
-        <v>1898.04149230283</v>
+        <v>2297.4085816587</v>
       </c>
       <c r="G105" t="s">
         <v>67</v>
@@ -4876,13 +4876,13 @@
         <v>677</v>
       </c>
       <c r="I105" t="n">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="J105" t="s">
         <v>17</v>
       </c>
       <c r="K105" t="n">
-        <v>1.028</v>
+        <v>1.147</v>
       </c>
       <c r="L105" t="s">
         <v>15</v>
@@ -4896,19 +4896,19 @@
         <v>44075</v>
       </c>
       <c r="B106" t="n">
-        <v>666.134596859329</v>
+        <v>743.9581271893</v>
       </c>
       <c r="C106" t="n">
-        <v>350.444724807283</v>
+        <v>351.661372718011</v>
       </c>
       <c r="D106" t="n">
-        <v>254.137809290567</v>
+        <v>247.696678024637</v>
       </c>
       <c r="E106" t="n">
-        <v>1409.7255364136</v>
+        <v>1534.87271605872</v>
       </c>
       <c r="F106" t="n">
-        <v>2017.71112057218</v>
+        <v>2402.23674810207</v>
       </c>
       <c r="G106" t="s">
         <v>67</v>
@@ -4917,13 +4917,13 @@
         <v>675</v>
       </c>
       <c r="I106" t="n">
-        <v>-9</v>
+        <v>69</v>
       </c>
       <c r="J106" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K106" t="n">
-        <v>0.987</v>
+        <v>1.102</v>
       </c>
       <c r="L106" t="s">
         <v>15</v>
@@ -4937,19 +4937,19 @@
         <v>44105</v>
       </c>
       <c r="B107" t="n">
-        <v>688.106006526996</v>
+        <v>796.301335550637</v>
       </c>
       <c r="C107" t="n">
-        <v>328.27802366881</v>
+        <v>343.852852178816</v>
       </c>
       <c r="D107" t="n">
-        <v>245.522238328893</v>
+        <v>226.070481215649</v>
       </c>
       <c r="E107" t="n">
-        <v>1606.80540820183</v>
+        <v>1784.43332343785</v>
       </c>
       <c r="F107" t="n">
-        <v>2380.76281380773</v>
+        <v>3330.36909679476</v>
       </c>
       <c r="G107" t="s">
         <v>67</v>
@@ -4958,13 +4958,13 @@
         <v>658</v>
       </c>
       <c r="I107" t="n">
-        <v>30</v>
+        <v>138</v>
       </c>
       <c r="J107" t="s">
         <v>17</v>
       </c>
       <c r="K107" t="n">
-        <v>1.046</v>
+        <v>1.21</v>
       </c>
       <c r="L107" t="s">
         <v>15</v>
@@ -4978,19 +4978,19 @@
         <v>44136</v>
       </c>
       <c r="B108" t="n">
-        <v>601.08716334091</v>
+        <v>684.306805624264</v>
       </c>
       <c r="C108" t="n">
-        <v>286.863016311003</v>
+        <v>272.030067152288</v>
       </c>
       <c r="D108" t="n">
-        <v>186.154719138403</v>
+        <v>182.288968976215</v>
       </c>
       <c r="E108" t="n">
-        <v>1469.60892490742</v>
+        <v>1632.84223605149</v>
       </c>
       <c r="F108" t="n">
-        <v>2264.65626132053</v>
+        <v>2966.99934363703</v>
       </c>
       <c r="G108" t="s">
         <v>67</v>
@@ -4999,13 +4999,13 @@
         <v>615</v>
       </c>
       <c r="I108" t="n">
-        <v>-14</v>
+        <v>69</v>
       </c>
       <c r="J108" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K108" t="n">
-        <v>0.977</v>
+        <v>1.113</v>
       </c>
       <c r="L108" t="s">
         <v>15</v>
@@ -5019,19 +5019,19 @@
         <v>44166</v>
       </c>
       <c r="B109" t="n">
-        <v>444.946097747409</v>
+        <v>485.961212383156</v>
       </c>
       <c r="C109" t="n">
-        <v>192.541781820274</v>
+        <v>173.663970226699</v>
       </c>
       <c r="D109" t="n">
-        <v>120.438256715617</v>
+        <v>110.792650299875</v>
       </c>
       <c r="E109" t="n">
-        <v>1133.31485535842</v>
+        <v>1350.36872755575</v>
       </c>
       <c r="F109" t="n">
-        <v>1811.80356130444</v>
+        <v>2663.10453517245</v>
       </c>
       <c r="G109" t="s">
         <v>67</v>
@@ -5040,13 +5040,13 @@
         <v>589</v>
       </c>
       <c r="I109" t="n">
-        <v>-144</v>
+        <v>-103</v>
       </c>
       <c r="J109" t="s">
         <v>14</v>
       </c>
       <c r="K109" t="n">
-        <v>0.755</v>
+        <v>0.825</v>
       </c>
       <c r="L109" t="s">
         <v>15</v>
@@ -5060,19 +5060,19 @@
         <v>44197</v>
       </c>
       <c r="B110" t="n">
-        <v>1148.29267193515</v>
+        <v>1554.41411433735</v>
       </c>
       <c r="C110" t="n">
-        <v>394.60678065482</v>
+        <v>492.896537984556</v>
       </c>
       <c r="D110" t="n">
-        <v>318.028140055957</v>
+        <v>299.538996328511</v>
       </c>
       <c r="E110" t="n">
-        <v>3683.22955185238</v>
+        <v>4616.78111253981</v>
       </c>
       <c r="F110" t="n">
-        <v>6119.2156939312</v>
+        <v>9697.29497061414</v>
       </c>
       <c r="G110" t="s">
         <v>67</v>
@@ -5081,13 +5081,13 @@
         <v>1381</v>
       </c>
       <c r="I110" t="n">
-        <v>-233</v>
+        <v>173</v>
       </c>
       <c r="J110" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K110" t="n">
-        <v>0.831</v>
+        <v>1.126</v>
       </c>
       <c r="L110" t="s">
         <v>15</v>
@@ -5101,19 +5101,19 @@
         <v>44228</v>
       </c>
       <c r="B111" t="n">
-        <v>853.648576276533</v>
+        <v>1103.85291685318</v>
       </c>
       <c r="C111" t="n">
-        <v>334.894040885786</v>
+        <v>307.136723583444</v>
       </c>
       <c r="D111" t="n">
-        <v>213.80690644549</v>
+        <v>181.792140149728</v>
       </c>
       <c r="E111" t="n">
-        <v>2845.81181367868</v>
+        <v>3740.81089922168</v>
       </c>
       <c r="F111" t="n">
-        <v>4891.98623597839</v>
+        <v>8397.74657620475</v>
       </c>
       <c r="G111" t="s">
         <v>67</v>
@@ -5122,13 +5122,13 @@
         <v>837</v>
       </c>
       <c r="I111" t="n">
-        <v>17</v>
+        <v>267</v>
       </c>
       <c r="J111" t="s">
         <v>17</v>
       </c>
       <c r="K111" t="n">
-        <v>1.02</v>
+        <v>1.319</v>
       </c>
       <c r="L111" t="s">
         <v>15</v>
@@ -5142,19 +5142,19 @@
         <v>44256</v>
       </c>
       <c r="B112" t="n">
-        <v>828.420089781314</v>
+        <v>1081.0043688184</v>
       </c>
       <c r="C112" t="n">
-        <v>327.168229100384</v>
+        <v>279.185126425772</v>
       </c>
       <c r="D112" t="n">
-        <v>183.224065387376</v>
+        <v>153.407105076283</v>
       </c>
       <c r="E112" t="n">
-        <v>2924.49668764057</v>
+        <v>4004.3002778242</v>
       </c>
       <c r="F112" t="n">
-        <v>5222.0345902679</v>
+        <v>10038.1730072246</v>
       </c>
       <c r="G112" t="s">
         <v>67</v>
@@ -5163,13 +5163,13 @@
         <v>1000</v>
       </c>
       <c r="I112" t="n">
-        <v>-172</v>
+        <v>81</v>
       </c>
       <c r="J112" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K112" t="n">
-        <v>0.828</v>
+        <v>1.081</v>
       </c>
       <c r="L112" t="s">
         <v>15</v>
@@ -5183,19 +5183,19 @@
         <v>44287</v>
       </c>
       <c r="B113" t="n">
-        <v>773.75175274293</v>
+        <v>992.804048498189</v>
       </c>
       <c r="C113" t="n">
-        <v>282.155404040414</v>
+        <v>219.057689619358</v>
       </c>
       <c r="D113" t="n">
-        <v>152.711554440777</v>
+        <v>123.846769466032</v>
       </c>
       <c r="E113" t="n">
-        <v>2869.38879012055</v>
+        <v>4066.33528295713</v>
       </c>
       <c r="F113" t="n">
-        <v>5301.58677988083</v>
+        <v>10422.9576245183</v>
       </c>
       <c r="G113" t="s">
         <v>67</v>
@@ -5204,13 +5204,13 @@
         <v>628</v>
       </c>
       <c r="I113" t="n">
-        <v>146</v>
+        <v>365</v>
       </c>
       <c r="J113" t="s">
         <v>17</v>
       </c>
       <c r="K113" t="n">
-        <v>1.232</v>
+        <v>1.581</v>
       </c>
       <c r="L113" t="s">
         <v>15</v>
@@ -5224,19 +5224,19 @@
         <v>44317</v>
       </c>
       <c r="B114" t="n">
-        <v>757.771002378383</v>
+        <v>990.606527659765</v>
       </c>
       <c r="C114" t="n">
-        <v>255.2818292258</v>
+        <v>191.244155724175</v>
       </c>
       <c r="D114" t="n">
-        <v>133.270896750848</v>
+        <v>96.0059487738606</v>
       </c>
       <c r="E114" t="n">
-        <v>2975.20195719729</v>
+        <v>4877.94053920672</v>
       </c>
       <c r="F114" t="n">
-        <v>5699.03123246171</v>
+        <v>12283.2812386591</v>
       </c>
       <c r="G114" t="s">
         <v>67</v>
@@ -5245,13 +5245,13 @@
         <v>614</v>
       </c>
       <c r="I114" t="n">
-        <v>144</v>
+        <v>377</v>
       </c>
       <c r="J114" t="s">
         <v>17</v>
       </c>
       <c r="K114" t="n">
-        <v>1.234</v>
+        <v>1.613</v>
       </c>
       <c r="L114" t="s">
         <v>15</v>
@@ -5265,19 +5265,19 @@
         <v>44348</v>
       </c>
       <c r="B115" t="n">
-        <v>711.555263631532</v>
+        <v>928.042982643391</v>
       </c>
       <c r="C115" t="n">
-        <v>231.138697577483</v>
+        <v>154.436854524428</v>
       </c>
       <c r="D115" t="n">
-        <v>116.774629621028</v>
+        <v>76.4940334769727</v>
       </c>
       <c r="E115" t="n">
-        <v>3049.07161393174</v>
+        <v>4913.1388055151</v>
       </c>
       <c r="F115" t="n">
-        <v>6035.20173108978</v>
+        <v>13908.3935194359</v>
       </c>
       <c r="G115" t="s">
         <v>67</v>
@@ -5286,13 +5286,13 @@
         <v>606</v>
       </c>
       <c r="I115" t="n">
-        <v>106</v>
+        <v>322</v>
       </c>
       <c r="J115" t="s">
         <v>17</v>
       </c>
       <c r="K115" t="n">
-        <v>1.174</v>
+        <v>1.531</v>
       </c>
       <c r="L115" t="s">
         <v>15</v>
@@ -5306,19 +5306,19 @@
         <v>44378</v>
       </c>
       <c r="B116" t="n">
-        <v>681.453769096672</v>
+        <v>913.281395114297</v>
       </c>
       <c r="C116" t="n">
-        <v>203.70293704856</v>
+        <v>141.51262688152</v>
       </c>
       <c r="D116" t="n">
-        <v>99.3477340636535</v>
+        <v>64.2539053792403</v>
       </c>
       <c r="E116" t="n">
-        <v>3070.11265575923</v>
+        <v>5427.60060922734</v>
       </c>
       <c r="F116" t="n">
-        <v>6294.96964452467</v>
+        <v>17454.2830750566</v>
       </c>
       <c r="G116" t="s">
         <v>67</v>
@@ -5327,13 +5327,13 @@
         <v>468</v>
       </c>
       <c r="I116" t="n">
-        <v>213</v>
+        <v>445</v>
       </c>
       <c r="J116" t="s">
         <v>17</v>
       </c>
       <c r="K116" t="n">
-        <v>1.456</v>
+        <v>1.951</v>
       </c>
       <c r="L116" t="s">
         <v>15</v>
@@ -5347,19 +5347,19 @@
         <v>44409</v>
       </c>
       <c r="B117" t="n">
-        <v>671.111646661792</v>
+        <v>914.814448630732</v>
       </c>
       <c r="C117" t="n">
-        <v>194.137574960167</v>
+        <v>126.045655831298</v>
       </c>
       <c r="D117" t="n">
-        <v>91.7104794690189</v>
+        <v>53.0281128437925</v>
       </c>
       <c r="E117" t="n">
-        <v>3300.63973405482</v>
+        <v>6067.82690057676</v>
       </c>
       <c r="F117" t="n">
-        <v>6986.96815497394</v>
+        <v>21313.3953429108</v>
       </c>
       <c r="G117" t="s">
         <v>67</v>
@@ -5368,13 +5368,13 @@
         <v>456</v>
       </c>
       <c r="I117" t="n">
-        <v>215</v>
+        <v>459</v>
       </c>
       <c r="J117" t="s">
         <v>17</v>
       </c>
       <c r="K117" t="n">
-        <v>1.472</v>
+        <v>2.006</v>
       </c>
       <c r="L117" t="s">
         <v>15</v>
@@ -5388,19 +5388,19 @@
         <v>44440</v>
       </c>
       <c r="B118" t="n">
-        <v>636.311212153033</v>
+        <v>877.538756190984</v>
       </c>
       <c r="C118" t="n">
-        <v>169.540846368441</v>
+        <v>109.94362772584</v>
       </c>
       <c r="D118" t="n">
-        <v>77.4464586786765</v>
+        <v>41.0384021080519</v>
       </c>
       <c r="E118" t="n">
-        <v>3272.31822965391</v>
+        <v>6502.73415136208</v>
       </c>
       <c r="F118" t="n">
-        <v>7163.55037027569</v>
+        <v>24982.4688875275</v>
       </c>
       <c r="G118" t="s">
         <v>67</v>
@@ -5409,13 +5409,13 @@
         <v>486</v>
       </c>
       <c r="I118" t="n">
-        <v>150</v>
+        <v>392</v>
       </c>
       <c r="J118" t="s">
         <v>17</v>
       </c>
       <c r="K118" t="n">
-        <v>1.309</v>
+        <v>1.806</v>
       </c>
       <c r="L118" t="s">
         <v>15</v>
@@ -5429,19 +5429,19 @@
         <v>44470</v>
       </c>
       <c r="B119" t="n">
-        <v>654.073321969847</v>
+        <v>933.647063687549</v>
       </c>
       <c r="C119" t="n">
-        <v>172.546169592516</v>
+        <v>106.68853983672</v>
       </c>
       <c r="D119" t="n">
-        <v>76.4197164240188</v>
+        <v>34.5310919926154</v>
       </c>
       <c r="E119" t="n">
-        <v>3742.9615654775</v>
+        <v>7701.99648551374</v>
       </c>
       <c r="F119" t="n">
-        <v>8451.13955048971</v>
+        <v>31770.7985492296</v>
       </c>
       <c r="G119" t="s">
         <v>67</v>
@@ -5450,13 +5450,13 @@
         <v>486</v>
       </c>
       <c r="I119" t="n">
-        <v>168</v>
+        <v>448</v>
       </c>
       <c r="J119" t="s">
         <v>17</v>
       </c>
       <c r="K119" t="n">
-        <v>1.346</v>
+        <v>1.921</v>
       </c>
       <c r="L119" t="s">
         <v>15</v>
@@ -5470,19 +5470,19 @@
         <v>44501</v>
       </c>
       <c r="B120" t="n">
-        <v>564.207760279783</v>
+        <v>808.756055921981</v>
       </c>
       <c r="C120" t="n">
-        <v>134.807397788764</v>
+        <v>80.3813886270136</v>
       </c>
       <c r="D120" t="n">
-        <v>57.7967505959378</v>
+        <v>23.0555220568815</v>
       </c>
       <c r="E120" t="n">
-        <v>3306.23820214799</v>
+        <v>7449.36810426999</v>
       </c>
       <c r="F120" t="n">
-        <v>7711.59916760806</v>
+        <v>37665.2303488656</v>
       </c>
       <c r="G120" t="s">
         <v>67</v>
@@ -5491,13 +5491,13 @@
         <v>485</v>
       </c>
       <c r="I120" t="n">
-        <v>79</v>
+        <v>324</v>
       </c>
       <c r="J120" t="s">
         <v>17</v>
       </c>
       <c r="K120" t="n">
-        <v>1.163</v>
+        <v>1.668</v>
       </c>
       <c r="L120" t="s">
         <v>15</v>
@@ -5511,19 +5511,19 @@
         <v>44531</v>
       </c>
       <c r="B121" t="n">
-        <v>419.735826271358</v>
+        <v>572.307690446044</v>
       </c>
       <c r="C121" t="n">
-        <v>92.7094704168424</v>
+        <v>50.7280759840377</v>
       </c>
       <c r="D121" t="n">
-        <v>38.5792328292825</v>
+        <v>12.7319675333474</v>
       </c>
       <c r="E121" t="n">
-        <v>2545.12639733593</v>
+        <v>6022.98587197156</v>
       </c>
       <c r="F121" t="n">
-        <v>6116.1745921586</v>
+        <v>36566.7951632666</v>
       </c>
       <c r="G121" t="s">
         <v>67</v>
@@ -5532,13 +5532,13 @@
         <v>403</v>
       </c>
       <c r="I121" t="n">
-        <v>17</v>
+        <v>169</v>
       </c>
       <c r="J121" t="s">
         <v>17</v>
       </c>
       <c r="K121" t="n">
-        <v>1.042</v>
+        <v>1.42</v>
       </c>
       <c r="L121" t="s">
         <v>15</v>
@@ -5552,19 +5552,19 @@
         <v>44562</v>
       </c>
       <c r="B122" t="n">
-        <v>1019.06338233129</v>
+        <v>1816.17409135922</v>
       </c>
       <c r="C122" t="n">
-        <v>196.503782636754</v>
+        <v>141.816695513446</v>
       </c>
       <c r="D122" t="n">
-        <v>105.051581023179</v>
+        <v>34.0609780674523</v>
       </c>
       <c r="E122" t="n">
-        <v>8041.92334287045</v>
+        <v>21547.9140273606</v>
       </c>
       <c r="F122" t="n">
-        <v>19936.5874797469</v>
+        <v>141247.539654374</v>
       </c>
       <c r="G122" t="s">
         <v>67</v>
@@ -5573,13 +5573,13 @@
         <v>1088</v>
       </c>
       <c r="I122" t="n">
-        <v>-69</v>
+        <v>728</v>
       </c>
       <c r="J122" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K122" t="n">
-        <v>0.937</v>
+        <v>1.669</v>
       </c>
       <c r="L122" t="s">
         <v>15</v>
@@ -5593,19 +5593,19 @@
         <v>44593</v>
       </c>
       <c r="B123" t="n">
-        <v>758.037776041393</v>
+        <v>1285.48545725497</v>
       </c>
       <c r="C123" t="n">
-        <v>180.4236520441</v>
+        <v>87.0544679743241</v>
       </c>
       <c r="D123" t="n">
-        <v>70.7240355680097</v>
+        <v>20.1996896841295</v>
       </c>
       <c r="E123" t="n">
-        <v>6207.86885346265</v>
+        <v>18577.9968301017</v>
       </c>
       <c r="F123" t="n">
-        <v>15836.8562562877</v>
+        <v>116957.006790186</v>
       </c>
       <c r="G123" t="s">
         <v>67</v>
@@ -5614,13 +5614,13 @@
         <v>758</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>527</v>
       </c>
       <c r="J123" t="s">
         <v>17</v>
       </c>
       <c r="K123" t="n">
-        <v>1</v>
+        <v>1.696</v>
       </c>
       <c r="L123" t="s">
         <v>15</v>
@@ -5634,19 +5634,19 @@
         <v>44621</v>
       </c>
       <c r="B124" t="n">
-        <v>718.808423959998</v>
+        <v>1259.18998136652</v>
       </c>
       <c r="C124" t="n">
-        <v>160.154965393165</v>
+        <v>76.5417840365249</v>
       </c>
       <c r="D124" t="n">
-        <v>60.9032255173193</v>
+        <v>17.2710887128418</v>
       </c>
       <c r="E124" t="n">
-        <v>6179.60640994509</v>
+        <v>19867.713870361</v>
       </c>
       <c r="F124" t="n">
-        <v>16250.2832455406</v>
+        <v>176987.444921272</v>
       </c>
       <c r="G124" t="s">
         <v>67</v>
@@ -5655,13 +5655,13 @@
         <v>793</v>
       </c>
       <c r="I124" t="n">
-        <v>-74</v>
+        <v>466</v>
       </c>
       <c r="J124" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K124" t="n">
-        <v>0.906</v>
+        <v>1.588</v>
       </c>
       <c r="L124" t="s">
         <v>15</v>
@@ -5675,19 +5675,19 @@
         <v>44652</v>
       </c>
       <c r="B125" t="n">
-        <v>675.457363389536</v>
+        <v>1151.14637662987</v>
       </c>
       <c r="C125" t="n">
-        <v>141.548569791347</v>
+        <v>61.1295695128153</v>
       </c>
       <c r="D125" t="n">
-        <v>52.3595806140667</v>
+        <v>12.1671343938805</v>
       </c>
       <c r="E125" t="n">
-        <v>6063.14254005579</v>
+        <v>20952.3549970026</v>
       </c>
       <c r="F125" t="n">
-        <v>16391.0626938981</v>
+        <v>192671.073756566</v>
       </c>
       <c r="G125" t="s">
         <v>67</v>
@@ -5696,13 +5696,13 @@
         <v>611</v>
       </c>
       <c r="I125" t="n">
-        <v>64</v>
+        <v>540</v>
       </c>
       <c r="J125" t="s">
         <v>17</v>
       </c>
       <c r="K125" t="n">
-        <v>1.105</v>
+        <v>1.884</v>
       </c>
       <c r="L125" t="s">
         <v>15</v>
@@ -5716,19 +5716,19 @@
         <v>44682</v>
       </c>
       <c r="B126" t="n">
-        <v>654.606056903581</v>
+        <v>1155.51702137477</v>
       </c>
       <c r="C126" t="n">
-        <v>127.867302622863</v>
+        <v>54.5197972047324</v>
       </c>
       <c r="D126" t="n">
-        <v>45.9436401039543</v>
+        <v>9.65392585318756</v>
       </c>
       <c r="E126" t="n">
-        <v>6112.92880141595</v>
+        <v>24601.0473052706</v>
       </c>
       <c r="F126" t="n">
-        <v>17013.0997095758</v>
+        <v>236670.457035059</v>
       </c>
       <c r="G126" t="s">
         <v>67</v>
@@ -5737,13 +5737,13 @@
         <v>714</v>
       </c>
       <c r="I126" t="n">
-        <v>-59</v>
+        <v>442</v>
       </c>
       <c r="J126" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K126" t="n">
-        <v>0.917</v>
+        <v>1.618</v>
       </c>
       <c r="L126" t="s">
         <v>15</v>
@@ -5757,19 +5757,19 @@
         <v>44713</v>
       </c>
       <c r="B127" t="n">
-        <v>610.243143130588</v>
+        <v>1081.45908818223</v>
       </c>
       <c r="C127" t="n">
-        <v>118.282909525427</v>
+        <v>43.203931405176</v>
       </c>
       <c r="D127" t="n">
-        <v>41.3751569991047</v>
+        <v>6.83144646461018</v>
       </c>
       <c r="E127" t="n">
-        <v>6257.77490950803</v>
+        <v>25978.2883825529</v>
       </c>
       <c r="F127" t="n">
-        <v>17889.6683503464</v>
+        <v>291012.267635965</v>
       </c>
       <c r="G127" t="s">
         <v>67</v>
@@ -5778,13 +5778,13 @@
         <v>725</v>
       </c>
       <c r="I127" t="n">
-        <v>-115</v>
+        <v>356</v>
       </c>
       <c r="J127" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K127" t="n">
-        <v>0.842</v>
+        <v>1.492</v>
       </c>
       <c r="L127" t="s">
         <v>15</v>
@@ -5798,19 +5798,19 @@
         <v>44743</v>
       </c>
       <c r="B128" t="n">
-        <v>594.165815063892</v>
+        <v>1052.71369827833</v>
       </c>
       <c r="C128" t="n">
-        <v>104.118827867526</v>
+        <v>36.5758614239639</v>
       </c>
       <c r="D128" t="n">
-        <v>35.4108831788173</v>
+        <v>5.13498456027499</v>
       </c>
       <c r="E128" t="n">
-        <v>6125.73664968218</v>
+        <v>29315.901818584</v>
       </c>
       <c r="F128" t="n">
-        <v>18011.5398069057</v>
+        <v>334344.714341222</v>
       </c>
       <c r="G128" t="s">
         <v>67</v>
@@ -5819,13 +5819,13 @@
         <v>697</v>
       </c>
       <c r="I128" t="n">
-        <v>-103</v>
+        <v>356</v>
       </c>
       <c r="J128" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K128" t="n">
-        <v>0.852</v>
+        <v>1.51</v>
       </c>
       <c r="L128" t="s">
         <v>15</v>
@@ -5839,19 +5839,19 @@
         <v>44774</v>
       </c>
       <c r="B129" t="n">
-        <v>593.391870310453</v>
+        <v>1046.26523158553</v>
       </c>
       <c r="C129" t="n">
-        <v>101.555981390731</v>
+        <v>32.0940593515913</v>
       </c>
       <c r="D129" t="n">
-        <v>33.6552813772689</v>
+        <v>4.90599105657625</v>
       </c>
       <c r="E129" t="n">
-        <v>6589.84170994478</v>
+        <v>34335.4964279725</v>
       </c>
       <c r="F129" t="n">
-        <v>19885.0768160791</v>
+        <v>467914.931227221</v>
       </c>
       <c r="G129" t="s">
         <v>67</v>
@@ -5860,13 +5860,13 @@
         <v>881</v>
       </c>
       <c r="I129" t="n">
-        <v>-288</v>
+        <v>165</v>
       </c>
       <c r="J129" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K129" t="n">
-        <v>0.674</v>
+        <v>1.188</v>
       </c>
       <c r="L129" t="s">
         <v>15</v>
@@ -5880,19 +5880,19 @@
         <v>44805</v>
       </c>
       <c r="B130" t="n">
-        <v>555.134485527668</v>
+        <v>1010.54511474258</v>
       </c>
       <c r="C130" t="n">
-        <v>88.5130506392055</v>
+        <v>26.2151082799193</v>
       </c>
       <c r="D130" t="n">
-        <v>28.5492348834186</v>
+        <v>3.23248497131257</v>
       </c>
       <c r="E130" t="n">
-        <v>6362.22782418266</v>
+        <v>38081.511157065</v>
       </c>
       <c r="F130" t="n">
-        <v>19725.2293422353</v>
+        <v>558214.946117546</v>
       </c>
       <c r="G130" t="s">
         <v>67</v>
@@ -5901,13 +5901,13 @@
         <v>876</v>
       </c>
       <c r="I130" t="n">
-        <v>-321</v>
+        <v>135</v>
       </c>
       <c r="J130" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K130" t="n">
-        <v>0.634</v>
+        <v>1.154</v>
       </c>
       <c r="L130" t="s">
         <v>15</v>
@@ -5921,19 +5921,19 @@
         <v>44835</v>
       </c>
       <c r="B131" t="n">
-        <v>583.346729411998</v>
+        <v>1083.10727788258</v>
       </c>
       <c r="C131" t="n">
-        <v>92.0562442623278</v>
+        <v>26.3342900964259</v>
       </c>
       <c r="D131" t="n">
-        <v>28.9532900863276</v>
+        <v>2.79385741614394</v>
       </c>
       <c r="E131" t="n">
-        <v>7277.74596737585</v>
+        <v>46651.5094397137</v>
       </c>
       <c r="F131" t="n">
-        <v>23139.4074127328</v>
+        <v>761970.691429717</v>
       </c>
       <c r="G131" t="s">
         <v>67</v>
@@ -5942,13 +5942,13 @@
         <v>741</v>
       </c>
       <c r="I131" t="n">
-        <v>-158</v>
+        <v>342</v>
       </c>
       <c r="J131" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K131" t="n">
-        <v>0.787</v>
+        <v>1.462</v>
       </c>
       <c r="L131" t="s">
         <v>15</v>
@@ -5962,19 +5962,19 @@
         <v>44866</v>
       </c>
       <c r="B132" t="n">
-        <v>509.40340051429</v>
+        <v>934.225941434517</v>
       </c>
       <c r="C132" t="n">
-        <v>71.8219394192201</v>
+        <v>19.031711290338</v>
       </c>
       <c r="D132" t="n">
-        <v>22.0060877619683</v>
+        <v>1.85831370255973</v>
       </c>
       <c r="E132" t="n">
-        <v>6267.81155258456</v>
+        <v>44202.2508025822</v>
       </c>
       <c r="F132" t="n">
-        <v>20456.4481105734</v>
+        <v>809640.838458016</v>
       </c>
       <c r="G132" t="s">
         <v>67</v>
@@ -5983,13 +5983,13 @@
         <v>701</v>
       </c>
       <c r="I132" t="n">
-        <v>-192</v>
+        <v>233</v>
       </c>
       <c r="J132" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K132" t="n">
-        <v>0.727</v>
+        <v>1.333</v>
       </c>
       <c r="L132" t="s">
         <v>15</v>
@@ -6003,19 +6003,19 @@
         <v>44896</v>
       </c>
       <c r="B133" t="n">
-        <v>378.123588843559</v>
+        <v>661.525465564928</v>
       </c>
       <c r="C133" t="n">
-        <v>50.475528659832</v>
+        <v>10.8017222022161</v>
       </c>
       <c r="D133" t="n">
-        <v>14.1628244721071</v>
+        <v>0.940828081459299</v>
       </c>
       <c r="E133" t="n">
-        <v>4830.75893190331</v>
+        <v>38436.549258091</v>
       </c>
       <c r="F133" t="n">
-        <v>16156.1195289201</v>
+        <v>705339.91194498</v>
       </c>
       <c r="G133" t="s">
         <v>67</v>
@@ -6024,13 +6024,13 @@
         <v>618</v>
       </c>
       <c r="I133" t="n">
-        <v>-240</v>
+        <v>44</v>
       </c>
       <c r="J133" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K133" t="n">
-        <v>0.612</v>
+        <v>1.07</v>
       </c>
       <c r="L133" t="s">
         <v>15</v>
@@ -6044,19 +6044,19 @@
         <v>44927</v>
       </c>
       <c r="B134" t="n">
-        <v>905.562085323423</v>
+        <v>2101.17770058527</v>
       </c>
       <c r="C134" t="n">
-        <v>134.581685787933</v>
+        <v>30.0027511544907</v>
       </c>
       <c r="D134" t="n">
-        <v>41.2437578130604</v>
+        <v>2.3762738422454</v>
       </c>
       <c r="E134" t="n">
-        <v>14896.0064117044</v>
+        <v>147494.341828693</v>
       </c>
       <c r="F134" t="n">
-        <v>51093.9963831404</v>
+        <v>2963221.15333389</v>
       </c>
       <c r="G134" t="s">
         <v>67</v>
@@ -6065,13 +6065,13 @@
         <v>1414</v>
       </c>
       <c r="I134" t="n">
-        <v>-508</v>
+        <v>687</v>
       </c>
       <c r="J134" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K134" t="n">
-        <v>0.64</v>
+        <v>1.486</v>
       </c>
       <c r="L134" t="s">
         <v>15</v>
@@ -6085,19 +6085,19 @@
         <v>44958</v>
       </c>
       <c r="B135" t="n">
-        <v>690.447431700858</v>
+        <v>1506.73402804059</v>
       </c>
       <c r="C135" t="n">
-        <v>100.068605585631</v>
+        <v>17.9810204852973</v>
       </c>
       <c r="D135" t="n">
-        <v>28.4963728741775</v>
+        <v>1.17754228631589</v>
       </c>
       <c r="E135" t="n">
-        <v>11515.3502139225</v>
+        <v>133349.325568518</v>
       </c>
       <c r="F135" t="n">
-        <v>40437.6049138249</v>
+        <v>2576661.6807834</v>
       </c>
       <c r="G135" t="s">
         <v>67</v>
@@ -6106,13 +6106,13 @@
         <v>861</v>
       </c>
       <c r="I135" t="n">
-        <v>-171</v>
+        <v>646</v>
       </c>
       <c r="J135" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K135" t="n">
-        <v>0.802</v>
+        <v>1.75</v>
       </c>
       <c r="L135" t="s">
         <v>15</v>
@@ -6126,19 +6126,19 @@
         <v>44986</v>
       </c>
       <c r="B136" t="n">
-        <v>647.253673842323</v>
+        <v>1471.72103548612</v>
       </c>
       <c r="C136" t="n">
-        <v>88.6542324557553</v>
+        <v>15.759467162893</v>
       </c>
       <c r="D136" t="n">
-        <v>24.6296703007247</v>
+        <v>1.0072370195792</v>
       </c>
       <c r="E136" t="n">
-        <v>11200.2458029709</v>
+        <v>146009.409906591</v>
       </c>
       <c r="F136" t="n">
-        <v>40315.1649725755</v>
+        <v>3282236.81885922</v>
       </c>
       <c r="G136" t="s">
         <v>67</v>
@@ -6147,13 +6147,13 @@
         <v>661</v>
       </c>
       <c r="I136" t="n">
-        <v>-14</v>
+        <v>811</v>
       </c>
       <c r="J136" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K136" t="n">
-        <v>0.979</v>
+        <v>2.226</v>
       </c>
       <c r="L136" t="s">
         <v>15</v>
@@ -6167,19 +6167,19 @@
         <v>45017</v>
       </c>
       <c r="B137" t="n">
-        <v>604.300330724571</v>
+        <v>1354.28391323662</v>
       </c>
       <c r="C137" t="n">
-        <v>79.9517896756452</v>
+        <v>11.6188166622285</v>
       </c>
       <c r="D137" t="n">
-        <v>21.7101601719139</v>
+        <v>0.732604072624387</v>
       </c>
       <c r="E137" t="n">
-        <v>11011.6174810563</v>
+        <v>160054.085378411</v>
       </c>
       <c r="F137" t="n">
-        <v>40552.3746694876</v>
+        <v>3771495.24782593</v>
       </c>
       <c r="G137" t="s">
         <v>67</v>
@@ -6188,13 +6188,13 @@
         <v>539</v>
       </c>
       <c r="I137" t="n">
-        <v>65</v>
+        <v>815</v>
       </c>
       <c r="J137" t="s">
         <v>17</v>
       </c>
       <c r="K137" t="n">
-        <v>1.121</v>
+        <v>2.513</v>
       </c>
       <c r="L137" t="s">
         <v>15</v>
@@ -6208,19 +6208,19 @@
         <v>45047</v>
       </c>
       <c r="B138" t="n">
-        <v>594.330591918459</v>
+        <v>1354.5793638384</v>
       </c>
       <c r="C138" t="n">
-        <v>72.0372570825535</v>
+        <v>9.91962271245774</v>
       </c>
       <c r="D138" t="n">
-        <v>19.1000321547035</v>
+        <v>0.554162356238193</v>
       </c>
       <c r="E138" t="n">
-        <v>10857.0841347151</v>
+        <v>194527.589905616</v>
       </c>
       <c r="F138" t="n">
-        <v>40948.3386002183</v>
+        <v>5404049.79457968</v>
       </c>
       <c r="G138" t="s">
         <v>67</v>
@@ -6229,13 +6229,13 @@
         <v>672</v>
       </c>
       <c r="I138" t="n">
-        <v>-78</v>
+        <v>683</v>
       </c>
       <c r="J138" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K138" t="n">
-        <v>0.884</v>
+        <v>2.016</v>
       </c>
       <c r="L138" t="s">
         <v>15</v>
@@ -6249,19 +6249,19 @@
         <v>45078</v>
       </c>
       <c r="B139" t="n">
-        <v>558.442473232883</v>
+        <v>1274.56188467096</v>
       </c>
       <c r="C139" t="n">
-        <v>67.9609033291573</v>
+        <v>8.76386636005489</v>
       </c>
       <c r="D139" t="n">
-        <v>16.6586444837439</v>
+        <v>0.383548677601781</v>
       </c>
       <c r="E139" t="n">
-        <v>11141.1910882334</v>
+        <v>208602.690030887</v>
       </c>
       <c r="F139" t="n">
-        <v>42965.5153118796</v>
+        <v>7411743.55360297</v>
       </c>
       <c r="G139" t="s">
         <v>67</v>
@@ -6270,13 +6270,13 @@
         <v>515</v>
       </c>
       <c r="I139" t="n">
-        <v>43</v>
+        <v>760</v>
       </c>
       <c r="J139" t="s">
         <v>17</v>
       </c>
       <c r="K139" t="n">
-        <v>1.084</v>
+        <v>2.475</v>
       </c>
       <c r="L139" t="s">
         <v>15</v>
@@ -6290,19 +6290,19 @@
         <v>45108</v>
       </c>
       <c r="B140" t="n">
-        <v>536.107045326571</v>
+        <v>1253.65043025645</v>
       </c>
       <c r="C140" t="n">
-        <v>59.6630844318718</v>
+        <v>5.93466185020804</v>
       </c>
       <c r="D140" t="n">
-        <v>14.0548737010501</v>
+        <v>0.27560296174348</v>
       </c>
       <c r="E140" t="n">
-        <v>10677.2521245077</v>
+        <v>234298.061471383</v>
       </c>
       <c r="F140" t="n">
-        <v>42143.1909107011</v>
+        <v>11312253.5536789</v>
       </c>
       <c r="G140" t="s">
         <v>67</v>
@@ -6311,13 +6311,13 @@
         <v>591</v>
       </c>
       <c r="I140" t="n">
-        <v>-55</v>
+        <v>663</v>
       </c>
       <c r="J140" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K140" t="n">
-        <v>0.907</v>
+        <v>2.121</v>
       </c>
       <c r="L140" t="s">
         <v>15</v>
@@ -6331,19 +6331,19 @@
         <v>45139</v>
       </c>
       <c r="B141" t="n">
-        <v>548.766186969132</v>
+        <v>1247.84398956989</v>
       </c>
       <c r="C141" t="n">
-        <v>59.3052633933905</v>
+        <v>5.61337538386583</v>
       </c>
       <c r="D141" t="n">
-        <v>12.5127507425612</v>
+        <v>0.200292436696532</v>
       </c>
       <c r="E141" t="n">
-        <v>11518.171606585</v>
+        <v>292660.326713053</v>
       </c>
       <c r="F141" t="n">
-        <v>46457.6682321591</v>
+        <v>15259627.0941143</v>
       </c>
       <c r="G141" t="s">
         <v>67</v>
@@ -6352,13 +6352,13 @@
         <v>582</v>
       </c>
       <c r="I141" t="n">
-        <v>-33</v>
+        <v>666</v>
       </c>
       <c r="J141" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K141" t="n">
-        <v>0.943</v>
+        <v>2.144</v>
       </c>
       <c r="L141" t="s">
         <v>15</v>
@@ -6372,19 +6372,19 @@
         <v>45170</v>
       </c>
       <c r="B142" t="n">
-        <v>517.954915843124</v>
+        <v>1204.17869575204</v>
       </c>
       <c r="C142" t="n">
-        <v>51.5312991785194</v>
+        <v>4.50748058392719</v>
       </c>
       <c r="D142" t="n">
-        <v>10.4735465235404</v>
+        <v>0.142905115933976</v>
       </c>
       <c r="E142" t="n">
-        <v>10896.1279300606</v>
+        <v>328938.965211113</v>
       </c>
       <c r="F142" t="n">
-        <v>44948.5571052976</v>
+        <v>22868983.3960869</v>
       </c>
       <c r="G142" t="s">
         <v>67</v>
@@ -6393,13 +6393,13 @@
         <v>480</v>
       </c>
       <c r="I142" t="n">
-        <v>38</v>
+        <v>724</v>
       </c>
       <c r="J142" t="s">
         <v>17</v>
       </c>
       <c r="K142" t="n">
-        <v>1.079</v>
+        <v>2.509</v>
       </c>
       <c r="L142" t="s">
         <v>15</v>
@@ -6413,19 +6413,19 @@
         <v>45200</v>
       </c>
       <c r="B143" t="n">
-        <v>542.194218199022</v>
+        <v>1285.53904224935</v>
       </c>
       <c r="C143" t="n">
-        <v>54.5894867331737</v>
+        <v>4.02876600337668</v>
       </c>
       <c r="D143" t="n">
-        <v>10.2800479928784</v>
+        <v>0.115718600959528</v>
       </c>
       <c r="E143" t="n">
-        <v>12503.446309758</v>
+        <v>378300.134116258</v>
       </c>
       <c r="F143" t="n">
-        <v>52682.0933537295</v>
+        <v>35381589.3448147</v>
       </c>
       <c r="G143" t="s">
         <v>67</v>
@@ -6434,13 +6434,13 @@
         <v>379</v>
       </c>
       <c r="I143" t="n">
-        <v>163</v>
+        <v>907</v>
       </c>
       <c r="J143" t="s">
         <v>17</v>
       </c>
       <c r="K143" t="n">
-        <v>1.431</v>
+        <v>3.392</v>
       </c>
       <c r="L143" t="s">
         <v>15</v>
@@ -6454,19 +6454,19 @@
         <v>45231</v>
       </c>
       <c r="B144" t="n">
-        <v>482.986701157745</v>
+        <v>1107.60380381814</v>
       </c>
       <c r="C144" t="n">
-        <v>42.4508974622427</v>
+        <v>2.93382330459079</v>
       </c>
       <c r="D144" t="n">
-        <v>7.13085076230624</v>
+        <v>0.0740196331935199</v>
       </c>
       <c r="E144" t="n">
-        <v>10560.8210300805</v>
+        <v>365089.146535298</v>
       </c>
       <c r="F144" t="n">
-        <v>45481.0523227952</v>
+        <v>47275739.7444263</v>
       </c>
       <c r="G144" t="s">
         <v>67</v>
@@ -6475,13 +6475,13 @@
         <v>367</v>
       </c>
       <c r="I144" t="n">
-        <v>116</v>
+        <v>741</v>
       </c>
       <c r="J144" t="s">
         <v>17</v>
       </c>
       <c r="K144" t="n">
-        <v>1.316</v>
+        <v>3.018</v>
       </c>
       <c r="L144" t="s">
         <v>15</v>
@@ -6495,19 +6495,19 @@
         <v>45261</v>
       </c>
       <c r="B145" t="n">
-        <v>366.701407102783</v>
+        <v>783.535439628389</v>
       </c>
       <c r="C145" t="n">
-        <v>28.9024201500616</v>
+        <v>1.67202447666101</v>
       </c>
       <c r="D145" t="n">
-        <v>3.21066148788807</v>
+        <v>0.038883496420069</v>
       </c>
       <c r="E145" t="n">
-        <v>8167.39380594463</v>
+        <v>309365.30804497</v>
       </c>
       <c r="F145" t="n">
-        <v>35907.1155494906</v>
+        <v>46353667.1883134</v>
       </c>
       <c r="G145" t="s">
         <v>67</v>
@@ -6516,13 +6516,13 @@
         <v>345</v>
       </c>
       <c r="I145" t="n">
-        <v>22</v>
+        <v>439</v>
       </c>
       <c r="J145" t="s">
         <v>17</v>
       </c>
       <c r="K145" t="n">
-        <v>1.063</v>
+        <v>2.271</v>
       </c>
       <c r="L145" t="s">
         <v>15</v>
@@ -6536,19 +6536,19 @@
         <v>43831</v>
       </c>
       <c r="B146" t="n">
-        <v>600.965311443641</v>
+        <v>674.734190833609</v>
       </c>
       <c r="C146" t="n">
-        <v>456.465405752206</v>
+        <v>502.444699758521</v>
       </c>
       <c r="D146" t="n">
-        <v>394.620224756706</v>
+        <v>433.789140885646</v>
       </c>
       <c r="E146" t="n">
-        <v>791.208492488934</v>
+        <v>889.843653548469</v>
       </c>
       <c r="F146" t="n">
-        <v>915.20728766808</v>
+        <v>1041.19994683043</v>
       </c>
       <c r="G146" t="s">
         <v>68</v>
@@ -6557,13 +6557,13 @@
         <v>742</v>
       </c>
       <c r="I146" t="n">
-        <v>-141</v>
+        <v>-67</v>
       </c>
       <c r="J146" t="s">
         <v>14</v>
       </c>
       <c r="K146" t="n">
-        <v>0.81</v>
+        <v>0.909</v>
       </c>
       <c r="L146" t="s">
         <v>15</v>
@@ -6577,19 +6577,19 @@
         <v>43862</v>
       </c>
       <c r="B147" t="n">
-        <v>506.909388659943</v>
+        <v>464.430548223127</v>
       </c>
       <c r="C147" t="n">
-        <v>367.053187022673</v>
+        <v>331.636429615371</v>
       </c>
       <c r="D147" t="n">
-        <v>309.393293320317</v>
+        <v>269.457785242862</v>
       </c>
       <c r="E147" t="n">
-        <v>700.054208481033</v>
+        <v>653.595724494925</v>
       </c>
       <c r="F147" t="n">
-        <v>830.51938700419</v>
+        <v>776.123056719253</v>
       </c>
       <c r="G147" t="s">
         <v>68</v>
@@ -6598,13 +6598,13 @@
         <v>540</v>
       </c>
       <c r="I147" t="n">
-        <v>-33</v>
+        <v>-76</v>
       </c>
       <c r="J147" t="s">
         <v>14</v>
       </c>
       <c r="K147" t="n">
-        <v>0.939</v>
+        <v>0.86</v>
       </c>
       <c r="L147" t="s">
         <v>15</v>
@@ -6618,19 +6618,19 @@
         <v>43891</v>
       </c>
       <c r="B148" t="n">
-        <v>390.708794761186</v>
+        <v>424.59935311216</v>
       </c>
       <c r="C148" t="n">
-        <v>270.491520065634</v>
+        <v>287.188173495887</v>
       </c>
       <c r="D148" t="n">
-        <v>222.645452177746</v>
+        <v>227.336193006875</v>
       </c>
       <c r="E148" t="n">
-        <v>564.355445474587</v>
+        <v>635.733927447223</v>
       </c>
       <c r="F148" t="n">
-        <v>685.634315952118</v>
+        <v>771.182311049317</v>
       </c>
       <c r="G148" t="s">
         <v>68</v>
@@ -6639,13 +6639,13 @@
         <v>398</v>
       </c>
       <c r="I148" t="n">
-        <v>-7</v>
+        <v>27</v>
       </c>
       <c r="J148" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K148" t="n">
-        <v>0.982</v>
+        <v>1.067</v>
       </c>
       <c r="L148" t="s">
         <v>15</v>
@@ -6659,19 +6659,19 @@
         <v>43922</v>
       </c>
       <c r="B149" t="n">
-        <v>403.766684968689</v>
+        <v>393.284943203163</v>
       </c>
       <c r="C149" t="n">
-        <v>270.310834147885</v>
+        <v>252.618161544767</v>
       </c>
       <c r="D149" t="n">
-        <v>218.580824492033</v>
+        <v>193.380810092962</v>
       </c>
       <c r="E149" t="n">
-        <v>603.111364013672</v>
+        <v>612.857908644978</v>
       </c>
       <c r="F149" t="n">
-        <v>745.845552872577</v>
+        <v>759.010163480519</v>
       </c>
       <c r="G149" t="s">
         <v>68</v>
@@ -6680,13 +6680,13 @@
         <v>259</v>
       </c>
       <c r="I149" t="n">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="J149" t="s">
         <v>17</v>
       </c>
       <c r="K149" t="n">
-        <v>1.559</v>
+        <v>1.518</v>
       </c>
       <c r="L149" t="s">
         <v>15</v>
@@ -6700,19 +6700,19 @@
         <v>43952</v>
       </c>
       <c r="B150" t="n">
-        <v>343.264160738725</v>
+        <v>374.220123896311</v>
       </c>
       <c r="C150" t="n">
-        <v>222.369011997842</v>
+        <v>221.440868391596</v>
       </c>
       <c r="D150" t="n">
-        <v>176.709421264457</v>
+        <v>178.64625396171</v>
       </c>
       <c r="E150" t="n">
-        <v>529.88625973121</v>
+        <v>603.701954595657</v>
       </c>
       <c r="F150" t="n">
-        <v>666.802500990146</v>
+        <v>822.010367948322</v>
       </c>
       <c r="G150" t="s">
         <v>68</v>
@@ -6721,13 +6721,13 @@
         <v>268</v>
       </c>
       <c r="I150" t="n">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="J150" t="s">
         <v>17</v>
       </c>
       <c r="K150" t="n">
-        <v>1.281</v>
+        <v>1.396</v>
       </c>
       <c r="L150" t="s">
         <v>15</v>
@@ -6741,19 +6741,19 @@
         <v>43983</v>
       </c>
       <c r="B151" t="n">
-        <v>335.33332381225</v>
+        <v>345.015025447481</v>
       </c>
       <c r="C151" t="n">
-        <v>211.074161288903</v>
+        <v>203.748359897932</v>
       </c>
       <c r="D151" t="n">
-        <v>165.200004933224</v>
+        <v>136.770723830763</v>
       </c>
       <c r="E151" t="n">
-        <v>532.743739794188</v>
+        <v>602.226610221224</v>
       </c>
       <c r="F151" t="n">
-        <v>680.680597463813</v>
+        <v>784.010056377431</v>
       </c>
       <c r="G151" t="s">
         <v>68</v>
@@ -6762,13 +6762,13 @@
         <v>329</v>
       </c>
       <c r="I151" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J151" t="s">
         <v>17</v>
       </c>
       <c r="K151" t="n">
-        <v>1.019</v>
+        <v>1.049</v>
       </c>
       <c r="L151" t="s">
         <v>15</v>
@@ -6782,19 +6782,19 @@
         <v>44013</v>
       </c>
       <c r="B152" t="n">
-        <v>313.508785540056</v>
+        <v>345.938811512179</v>
       </c>
       <c r="C152" t="n">
-        <v>191.913603270968</v>
+        <v>190.417388050607</v>
       </c>
       <c r="D152" t="n">
-        <v>148.004242633796</v>
+        <v>127.192317067454</v>
       </c>
       <c r="E152" t="n">
-        <v>512.145866346045</v>
+        <v>638.234732145284</v>
       </c>
       <c r="F152" t="n">
-        <v>664.087440074217</v>
+        <v>870.552626429093</v>
       </c>
       <c r="G152" t="s">
         <v>68</v>
@@ -6803,13 +6803,13 @@
         <v>333</v>
       </c>
       <c r="I152" t="n">
-        <v>-19</v>
+        <v>13</v>
       </c>
       <c r="J152" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K152" t="n">
-        <v>0.941</v>
+        <v>1.039</v>
       </c>
       <c r="L152" t="s">
         <v>15</v>
@@ -6823,19 +6823,19 @@
         <v>44044</v>
       </c>
       <c r="B153" t="n">
-        <v>371.699999165314</v>
+        <v>379.413785464359</v>
       </c>
       <c r="C153" t="n">
-        <v>221.781948300055</v>
+        <v>200.29007399512</v>
       </c>
       <c r="D153" t="n">
-        <v>168.735612218692</v>
+        <v>144.363923688973</v>
       </c>
       <c r="E153" t="n">
-        <v>622.958227387256</v>
+        <v>722.960860185287</v>
       </c>
       <c r="F153" t="n">
-        <v>818.801008055306</v>
+        <v>1071.90968722013</v>
       </c>
       <c r="G153" t="s">
         <v>68</v>
@@ -6844,13 +6844,13 @@
         <v>299</v>
       </c>
       <c r="I153" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="J153" t="s">
         <v>17</v>
       </c>
       <c r="K153" t="n">
-        <v>1.243</v>
+        <v>1.269</v>
       </c>
       <c r="L153" t="s">
         <v>15</v>
@@ -6864,19 +6864,19 @@
         <v>44075</v>
       </c>
       <c r="B154" t="n">
-        <v>294.211990968975</v>
+        <v>333.584978255607</v>
       </c>
       <c r="C154" t="n">
-        <v>171.295664837907</v>
+        <v>165.658889380749</v>
       </c>
       <c r="D154" t="n">
-        <v>128.644260176144</v>
+        <v>115.275167759665</v>
       </c>
       <c r="E154" t="n">
-        <v>505.329167038982</v>
+        <v>668.946506672943</v>
       </c>
       <c r="F154" t="n">
-        <v>672.868696290113</v>
+        <v>1047.4630113747</v>
       </c>
       <c r="G154" t="s">
         <v>68</v>
@@ -6885,13 +6885,13 @@
         <v>364</v>
       </c>
       <c r="I154" t="n">
-        <v>-70</v>
+        <v>-30</v>
       </c>
       <c r="J154" t="s">
         <v>14</v>
       </c>
       <c r="K154" t="n">
-        <v>0.808</v>
+        <v>0.916</v>
       </c>
       <c r="L154" t="s">
         <v>15</v>
@@ -6905,19 +6905,19 @@
         <v>44105</v>
       </c>
       <c r="B155" t="n">
-        <v>360.002100477206</v>
+        <v>363.458461234101</v>
       </c>
       <c r="C155" t="n">
-        <v>204.764539233255</v>
+        <v>165.968577054037</v>
       </c>
       <c r="D155" t="n">
-        <v>151.891322265764</v>
+        <v>111.66003568286</v>
       </c>
       <c r="E155" t="n">
-        <v>632.929475158615</v>
+        <v>761.175798942496</v>
       </c>
       <c r="F155" t="n">
-        <v>853.251590773808</v>
+        <v>1200.46489798896</v>
       </c>
       <c r="G155" t="s">
         <v>68</v>
@@ -6926,13 +6926,13 @@
         <v>330</v>
       </c>
       <c r="I155" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J155" t="s">
         <v>17</v>
       </c>
       <c r="K155" t="n">
-        <v>1.091</v>
+        <v>1.101</v>
       </c>
       <c r="L155" t="s">
         <v>15</v>
@@ -6946,19 +6946,19 @@
         <v>44136</v>
       </c>
       <c r="B156" t="n">
-        <v>309.517001973735</v>
+        <v>345.187632338826</v>
       </c>
       <c r="C156" t="n">
-        <v>172.258105393444</v>
+        <v>154.384054573003</v>
       </c>
       <c r="D156" t="n">
-        <v>126.314422296151</v>
+        <v>92.1842209634147</v>
       </c>
       <c r="E156" t="n">
-        <v>556.146686346032</v>
+        <v>774.009843582143</v>
       </c>
       <c r="F156" t="n">
-        <v>758.431007080087</v>
+        <v>1247.75497160748</v>
       </c>
       <c r="G156" t="s">
         <v>68</v>
@@ -6967,13 +6967,13 @@
         <v>307</v>
       </c>
       <c r="I156" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="J156" t="s">
         <v>17</v>
       </c>
       <c r="K156" t="n">
-        <v>1.008</v>
+        <v>1.124</v>
       </c>
       <c r="L156" t="s">
         <v>15</v>
@@ -6987,19 +6987,19 @@
         <v>44166</v>
       </c>
       <c r="B157" t="n">
-        <v>250.547759326923</v>
+        <v>265.219702363336</v>
       </c>
       <c r="C157" t="n">
-        <v>136.458573143845</v>
+        <v>111.810795977508</v>
       </c>
       <c r="D157" t="n">
-        <v>98.9249998785594</v>
+        <v>65.8116321694353</v>
       </c>
       <c r="E157" t="n">
-        <v>460.023714578705</v>
+        <v>626.791369337222</v>
       </c>
       <c r="F157" t="n">
-        <v>634.56335386205</v>
+        <v>974.783874079851</v>
       </c>
       <c r="G157" t="s">
         <v>68</v>
@@ -7008,13 +7008,13 @@
         <v>306</v>
       </c>
       <c r="I157" t="n">
-        <v>-55</v>
+        <v>-41</v>
       </c>
       <c r="J157" t="s">
         <v>14</v>
       </c>
       <c r="K157" t="n">
-        <v>0.819</v>
+        <v>0.867</v>
       </c>
       <c r="L157" t="s">
         <v>15</v>
@@ -7028,19 +7028,19 @@
         <v>44197</v>
       </c>
       <c r="B158" t="n">
-        <v>600.965311443641</v>
+        <v>731.027036912322</v>
       </c>
       <c r="C158" t="n">
-        <v>321.551065726458</v>
+        <v>285.368269530235</v>
       </c>
       <c r="D158" t="n">
-        <v>230.926561332664</v>
+        <v>152.755055634002</v>
       </c>
       <c r="E158" t="n">
-        <v>1123.17869245002</v>
+        <v>1867.63935505797</v>
       </c>
       <c r="F158" t="n">
-        <v>1563.95740478844</v>
+        <v>3037.1562602725</v>
       </c>
       <c r="G158" t="s">
         <v>68</v>
@@ -7049,13 +7049,13 @@
         <v>819</v>
       </c>
       <c r="I158" t="n">
-        <v>-218</v>
+        <v>-88</v>
       </c>
       <c r="J158" t="s">
         <v>14</v>
       </c>
       <c r="K158" t="n">
-        <v>0.734</v>
+        <v>0.893</v>
       </c>
       <c r="L158" t="s">
         <v>15</v>
@@ -7069,19 +7069,19 @@
         <v>44228</v>
       </c>
       <c r="B159" t="n">
-        <v>506.909388659943</v>
+        <v>497.894828621896</v>
       </c>
       <c r="C159" t="n">
-        <v>265.205709734504</v>
+        <v>185.668345924606</v>
       </c>
       <c r="D159" t="n">
-        <v>188.21165713216</v>
+        <v>98.3750386720541</v>
       </c>
       <c r="E159" t="n">
-        <v>968.897421434992</v>
+        <v>1330.82923027584</v>
       </c>
       <c r="F159" t="n">
-        <v>1365.25618140201</v>
+        <v>2222.32408562685</v>
       </c>
       <c r="G159" t="s">
         <v>68</v>
@@ -7090,13 +7090,13 @@
         <v>538</v>
       </c>
       <c r="I159" t="n">
-        <v>-31</v>
+        <v>-40</v>
       </c>
       <c r="J159" t="s">
         <v>14</v>
       </c>
       <c r="K159" t="n">
-        <v>0.942</v>
+        <v>0.925</v>
       </c>
       <c r="L159" t="s">
         <v>15</v>
@@ -7110,19 +7110,19 @@
         <v>44256</v>
       </c>
       <c r="B160" t="n">
-        <v>390.708794761187</v>
+        <v>462.930435092376</v>
       </c>
       <c r="C160" t="n">
-        <v>199.663585524231</v>
+        <v>159.239853895765</v>
       </c>
       <c r="D160" t="n">
-        <v>139.945626614565</v>
+        <v>79.9426735957452</v>
       </c>
       <c r="E160" t="n">
-        <v>764.552844741003</v>
+        <v>1351.28576770031</v>
       </c>
       <c r="F160" t="n">
-        <v>1090.80480752838</v>
+        <v>2327.37149222332</v>
       </c>
       <c r="G160" t="s">
         <v>68</v>
@@ -7131,13 +7131,13 @@
         <v>585</v>
       </c>
       <c r="I160" t="n">
-        <v>-194</v>
+        <v>-122</v>
       </c>
       <c r="J160" t="s">
         <v>14</v>
       </c>
       <c r="K160" t="n">
-        <v>0.668</v>
+        <v>0.791</v>
       </c>
       <c r="L160" t="s">
         <v>15</v>
@@ -7151,19 +7151,19 @@
         <v>44287</v>
       </c>
       <c r="B161" t="n">
-        <v>403.766684968689</v>
+        <v>420.691859483416</v>
       </c>
       <c r="C161" t="n">
-        <v>202.464520770614</v>
+        <v>132.079593793483</v>
       </c>
       <c r="D161" t="n">
-        <v>140.492830430162</v>
+        <v>69.5508538458603</v>
       </c>
       <c r="E161" t="n">
-        <v>805.215329925924</v>
+        <v>1229.59050639422</v>
       </c>
       <c r="F161" t="n">
-        <v>1160.39754762891</v>
+        <v>2469.7323454689</v>
       </c>
       <c r="G161" t="s">
         <v>68</v>
@@ -7172,13 +7172,13 @@
         <v>420</v>
       </c>
       <c r="I161" t="n">
-        <v>-16</v>
+        <v>1</v>
       </c>
       <c r="J161" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K161" t="n">
-        <v>0.961</v>
+        <v>1.002</v>
       </c>
       <c r="L161" t="s">
         <v>15</v>
@@ -7192,19 +7192,19 @@
         <v>44317</v>
       </c>
       <c r="B162" t="n">
-        <v>343.264160738725</v>
+        <v>397.732120249189</v>
       </c>
       <c r="C162" t="n">
-        <v>168.780526745002</v>
+        <v>115.96913484262</v>
       </c>
       <c r="D162" t="n">
-        <v>115.908406255842</v>
+        <v>60.2820614472996</v>
       </c>
       <c r="E162" t="n">
-        <v>698.127244416546</v>
+        <v>1324.60131339807</v>
       </c>
       <c r="F162" t="n">
-        <v>1016.58100438011</v>
+        <v>2415.16309602453</v>
       </c>
       <c r="G162" t="s">
         <v>68</v>
@@ -7213,13 +7213,13 @@
         <v>374</v>
       </c>
       <c r="I162" t="n">
-        <v>-31</v>
+        <v>24</v>
       </c>
       <c r="J162" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K162" t="n">
-        <v>0.918</v>
+        <v>1.063</v>
       </c>
       <c r="L162" t="s">
         <v>15</v>
@@ -7233,19 +7233,19 @@
         <v>44348</v>
       </c>
       <c r="B163" t="n">
-        <v>335.33332381225</v>
+        <v>368.417494092082</v>
       </c>
       <c r="C163" t="n">
-        <v>161.949296413823</v>
+        <v>104.018115969393</v>
       </c>
       <c r="D163" t="n">
-        <v>110.165872515612</v>
+        <v>49.633595282986</v>
       </c>
       <c r="E163" t="n">
-        <v>694.343480021279</v>
+        <v>1270.25521653437</v>
       </c>
       <c r="F163" t="n">
-        <v>1020.71935247494</v>
+        <v>2352.15071504657</v>
       </c>
       <c r="G163" t="s">
         <v>68</v>
@@ -7254,13 +7254,13 @@
         <v>368</v>
       </c>
       <c r="I163" t="n">
-        <v>-33</v>
+        <v>0</v>
       </c>
       <c r="J163" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K163" t="n">
-        <v>0.911</v>
+        <v>1.001</v>
       </c>
       <c r="L163" t="s">
         <v>15</v>
@@ -7274,19 +7274,19 @@
         <v>44378</v>
       </c>
       <c r="B164" t="n">
-        <v>313.508785540056</v>
+        <v>366.506717391968</v>
       </c>
       <c r="C164" t="n">
-        <v>148.703162721607</v>
+        <v>93.5883626579861</v>
       </c>
       <c r="D164" t="n">
-        <v>100.194130557339</v>
+        <v>42.8134281389661</v>
       </c>
       <c r="E164" t="n">
-        <v>660.966161122003</v>
+        <v>1370.24285065685</v>
       </c>
       <c r="F164" t="n">
-        <v>980.973217333856</v>
+        <v>2681.58198490013</v>
       </c>
       <c r="G164" t="s">
         <v>68</v>
@@ -7295,13 +7295,13 @@
         <v>296</v>
       </c>
       <c r="I164" t="n">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="J164" t="s">
         <v>17</v>
       </c>
       <c r="K164" t="n">
-        <v>1.059</v>
+        <v>1.238</v>
       </c>
       <c r="L164" t="s">
         <v>15</v>
@@ -7315,19 +7315,19 @@
         <v>44409</v>
       </c>
       <c r="B165" t="n">
-        <v>371.699999165314</v>
+        <v>407.977601310183</v>
       </c>
       <c r="C165" t="n">
-        <v>173.316014773259</v>
+        <v>108.848789182626</v>
       </c>
       <c r="D165" t="n">
-        <v>115.725896372829</v>
+        <v>44.4181445991047</v>
       </c>
       <c r="E165" t="n">
-        <v>797.161702340341</v>
+        <v>1550.25648204225</v>
       </c>
       <c r="F165" t="n">
-        <v>1193.86320356844</v>
+        <v>3205.88064218805</v>
       </c>
       <c r="G165" t="s">
         <v>68</v>
@@ -7336,13 +7336,13 @@
         <v>291</v>
       </c>
       <c r="I165" t="n">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="J165" t="s">
         <v>17</v>
       </c>
       <c r="K165" t="n">
-        <v>1.277</v>
+        <v>1.402</v>
       </c>
       <c r="L165" t="s">
         <v>15</v>
@@ -7356,19 +7356,19 @@
         <v>44440</v>
       </c>
       <c r="B166" t="n">
-        <v>294.211990968974</v>
+        <v>356.578044194756</v>
       </c>
       <c r="C166" t="n">
-        <v>134.899167314621</v>
+        <v>83.1980764702078</v>
       </c>
       <c r="D166" t="n">
-        <v>89.2767157841733</v>
+        <v>33.5398652779915</v>
       </c>
       <c r="E166" t="n">
-        <v>641.669606662918</v>
+        <v>1495.90109875289</v>
       </c>
       <c r="F166" t="n">
-        <v>969.57750819585</v>
+        <v>2999.85986849807</v>
       </c>
       <c r="G166" t="s">
         <v>68</v>
@@ -7377,13 +7377,13 @@
         <v>281</v>
       </c>
       <c r="I166" t="n">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="J166" t="s">
         <v>17</v>
       </c>
       <c r="K166" t="n">
-        <v>1.047</v>
+        <v>1.269</v>
       </c>
       <c r="L166" t="s">
         <v>15</v>
@@ -7397,19 +7397,19 @@
         <v>44470</v>
       </c>
       <c r="B167" t="n">
-        <v>360.002100477205</v>
+        <v>386.934894516845</v>
       </c>
       <c r="C167" t="n">
-        <v>162.384863859033</v>
+        <v>81.0759182142466</v>
       </c>
       <c r="D167" t="n">
-        <v>106.539714394712</v>
+        <v>31.1175635152111</v>
       </c>
       <c r="E167" t="n">
-        <v>798.113255558766</v>
+        <v>1653.9972889615</v>
       </c>
       <c r="F167" t="n">
-        <v>1216.46198400577</v>
+        <v>3539.32409444286</v>
       </c>
       <c r="G167" t="s">
         <v>68</v>
@@ -7418,13 +7418,13 @@
         <v>246</v>
       </c>
       <c r="I167" t="n">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="J167" t="s">
         <v>17</v>
       </c>
       <c r="K167" t="n">
-        <v>1.463</v>
+        <v>1.573</v>
       </c>
       <c r="L167" t="s">
         <v>15</v>
@@ -7438,19 +7438,19 @@
         <v>44501</v>
       </c>
       <c r="B168" t="n">
-        <v>309.517001973735</v>
+        <v>373.706394171095</v>
       </c>
       <c r="C168" t="n">
-        <v>137.455202399259</v>
+        <v>75.9265549312115</v>
       </c>
       <c r="D168" t="n">
-        <v>89.4430508057776</v>
+        <v>28.2908650515042</v>
       </c>
       <c r="E168" t="n">
-        <v>696.959975603843</v>
+        <v>1727.42145018938</v>
       </c>
       <c r="F168" t="n">
-        <v>1071.08124832232</v>
+        <v>3710.83134657577</v>
       </c>
       <c r="G168" t="s">
         <v>68</v>
@@ -7459,13 +7459,13 @@
         <v>252</v>
       </c>
       <c r="I168" t="n">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="J168" t="s">
         <v>17</v>
       </c>
       <c r="K168" t="n">
-        <v>1.228</v>
+        <v>1.483</v>
       </c>
       <c r="L168" t="s">
         <v>15</v>
@@ -7479,19 +7479,19 @@
         <v>44531</v>
       </c>
       <c r="B169" t="n">
-        <v>250.547759326923</v>
+        <v>283.97173498174</v>
       </c>
       <c r="C169" t="n">
-        <v>109.530004397738</v>
+        <v>52.4622675325095</v>
       </c>
       <c r="D169" t="n">
-        <v>70.6806897603937</v>
+        <v>20.4701867551921</v>
       </c>
       <c r="E169" t="n">
-        <v>573.123136887576</v>
+        <v>1393.66121027733</v>
       </c>
       <c r="F169" t="n">
-        <v>888.137621697595</v>
+        <v>3233.38599623121</v>
       </c>
       <c r="G169" t="s">
         <v>68</v>
@@ -7500,13 +7500,13 @@
         <v>263</v>
       </c>
       <c r="I169" t="n">
-        <v>-12</v>
+        <v>21</v>
       </c>
       <c r="J169" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K169" t="n">
-        <v>0.953</v>
+        <v>1.08</v>
       </c>
       <c r="L169" t="s">
         <v>15</v>
@@ -7520,19 +7520,19 @@
         <v>44562</v>
       </c>
       <c r="B170" t="n">
-        <v>600.96531144364</v>
+        <v>773.710890812885</v>
       </c>
       <c r="C170" t="n">
-        <v>259.294264865933</v>
+        <v>137.128728752171</v>
       </c>
       <c r="D170" t="n">
-        <v>166.166578172365</v>
+        <v>47.7311499421265</v>
       </c>
       <c r="E170" t="n">
-        <v>1392.85497018335</v>
+        <v>4111.8981519131</v>
       </c>
       <c r="F170" t="n">
-        <v>2173.47741965246</v>
+        <v>9808.52521546817</v>
       </c>
       <c r="G170" t="s">
         <v>68</v>
@@ -7541,13 +7541,13 @@
         <v>509</v>
       </c>
       <c r="I170" t="n">
-        <v>92</v>
+        <v>265</v>
       </c>
       <c r="J170" t="s">
         <v>17</v>
       </c>
       <c r="K170" t="n">
-        <v>1.181</v>
+        <v>1.52</v>
       </c>
       <c r="L170" t="s">
         <v>15</v>
@@ -7561,19 +7561,19 @@
         <v>44593</v>
       </c>
       <c r="B171" t="n">
-        <v>506.909388659943</v>
+        <v>527.452765629328</v>
       </c>
       <c r="C171" t="n">
-        <v>215.062364328681</v>
+        <v>92.7181505277399</v>
       </c>
       <c r="D171" t="n">
-        <v>136.598460729232</v>
+        <v>30.7817396547581</v>
       </c>
       <c r="E171" t="n">
-        <v>1194.80286154991</v>
+        <v>2969.57480781546</v>
       </c>
       <c r="F171" t="n">
-        <v>1881.1129125455</v>
+        <v>7926.46402131886</v>
       </c>
       <c r="G171" t="s">
         <v>68</v>
@@ -7582,13 +7582,13 @@
         <v>364</v>
       </c>
       <c r="I171" t="n">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="J171" t="s">
         <v>17</v>
       </c>
       <c r="K171" t="n">
-        <v>1.393</v>
+        <v>1.449</v>
       </c>
       <c r="L171" t="s">
         <v>15</v>
@@ -7602,19 +7602,19 @@
         <v>44621</v>
       </c>
       <c r="B172" t="n">
-        <v>390.708794761186</v>
+        <v>490.524584272233</v>
       </c>
       <c r="C172" t="n">
-        <v>162.823278880581</v>
+        <v>77.5093515436357</v>
       </c>
       <c r="D172" t="n">
-        <v>102.443471614988</v>
+        <v>23.5960245040142</v>
       </c>
       <c r="E172" t="n">
-        <v>937.540156132703</v>
+        <v>2999.49778918172</v>
       </c>
       <c r="F172" t="n">
-        <v>1490.12289311566</v>
+        <v>7267.16284225278</v>
       </c>
       <c r="G172" t="s">
         <v>68</v>
@@ -7623,13 +7623,13 @@
         <v>346</v>
       </c>
       <c r="I172" t="n">
-        <v>45</v>
+        <v>145</v>
       </c>
       <c r="J172" t="s">
         <v>17</v>
       </c>
       <c r="K172" t="n">
-        <v>1.129</v>
+        <v>1.418</v>
       </c>
       <c r="L172" t="s">
         <v>15</v>
@@ -7643,19 +7643,19 @@
         <v>44652</v>
       </c>
       <c r="B173" t="n">
-        <v>403.766684968689</v>
+        <v>442.223372203384</v>
       </c>
       <c r="C173" t="n">
-        <v>165.82410976655</v>
+        <v>66.060104911312</v>
       </c>
       <c r="D173" t="n">
-        <v>103.527573364587</v>
+        <v>18.0277821324543</v>
       </c>
       <c r="E173" t="n">
-        <v>983.135299927842</v>
+        <v>2823.8071056539</v>
       </c>
       <c r="F173" t="n">
-        <v>1574.7257526889</v>
+        <v>7621.52159385744</v>
       </c>
       <c r="G173" t="s">
         <v>68</v>
@@ -7664,13 +7664,13 @@
         <v>267</v>
       </c>
       <c r="I173" t="n">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="J173" t="s">
         <v>17</v>
       </c>
       <c r="K173" t="n">
-        <v>1.512</v>
+        <v>1.656</v>
       </c>
       <c r="L173" t="s">
         <v>15</v>
@@ -7684,19 +7684,19 @@
         <v>44682</v>
       </c>
       <c r="B174" t="n">
-        <v>343.264160738726</v>
+        <v>420.295985510486</v>
       </c>
       <c r="C174" t="n">
-        <v>138.834249483064</v>
+        <v>58.1068392298421</v>
       </c>
       <c r="D174" t="n">
-        <v>85.9775744694032</v>
+        <v>18.5257341893767</v>
       </c>
       <c r="E174" t="n">
-        <v>848.711931575901</v>
+        <v>2936.20734419181</v>
       </c>
       <c r="F174" t="n">
-        <v>1370.47695023769</v>
+        <v>8031.23339559715</v>
       </c>
       <c r="G174" t="s">
         <v>68</v>
@@ -7705,13 +7705,13 @@
         <v>309</v>
       </c>
       <c r="I174" t="n">
-        <v>34</v>
+        <v>111</v>
       </c>
       <c r="J174" t="s">
         <v>17</v>
       </c>
       <c r="K174" t="n">
-        <v>1.111</v>
+        <v>1.36</v>
       </c>
       <c r="L174" t="s">
         <v>15</v>
@@ -7725,19 +7725,19 @@
         <v>44713</v>
       </c>
       <c r="B175" t="n">
-        <v>335.33332381225</v>
+        <v>389.649399206791</v>
       </c>
       <c r="C175" t="n">
-        <v>133.722733680454</v>
+        <v>49.7895506574597</v>
       </c>
       <c r="D175" t="n">
-        <v>82.1946780656154</v>
+        <v>13.9091783873992</v>
       </c>
       <c r="E175" t="n">
-        <v>840.90741315295</v>
+        <v>2859.19666237641</v>
       </c>
       <c r="F175" t="n">
-        <v>1368.07443870277</v>
+        <v>9506.1925992305</v>
       </c>
       <c r="G175" t="s">
         <v>68</v>
@@ -7746,13 +7746,13 @@
         <v>325</v>
       </c>
       <c r="I175" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="J175" t="s">
         <v>17</v>
       </c>
       <c r="K175" t="n">
-        <v>1.032</v>
+        <v>1.199</v>
       </c>
       <c r="L175" t="s">
         <v>15</v>
@@ -7766,19 +7766,19 @@
         <v>44743</v>
       </c>
       <c r="B176" t="n">
-        <v>313.508785540056</v>
+        <v>383.273219761026</v>
       </c>
       <c r="C176" t="n">
-        <v>123.239419160095</v>
+        <v>45.3881114136227</v>
       </c>
       <c r="D176" t="n">
-        <v>75.1780178242892</v>
+        <v>13.1604319049271</v>
       </c>
       <c r="E176" t="n">
-        <v>797.535068573471</v>
+        <v>2957.97712975719</v>
       </c>
       <c r="F176" t="n">
-        <v>1307.40024085931</v>
+        <v>9922.91907197832</v>
       </c>
       <c r="G176" t="s">
         <v>68</v>
@@ -7787,13 +7787,13 @@
         <v>282</v>
       </c>
       <c r="I176" t="n">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="J176" t="s">
         <v>17</v>
       </c>
       <c r="K176" t="n">
-        <v>1.112</v>
+        <v>1.359</v>
       </c>
       <c r="L176" t="s">
         <v>15</v>
@@ -7807,19 +7807,19 @@
         <v>44774</v>
       </c>
       <c r="B177" t="n">
-        <v>371.699999165314</v>
+        <v>422.870491220032</v>
       </c>
       <c r="C177" t="n">
-        <v>144.124355812189</v>
+        <v>47.3511397874569</v>
       </c>
       <c r="D177" t="n">
-        <v>87.2822962600912</v>
+        <v>12.1097812784621</v>
       </c>
       <c r="E177" t="n">
-        <v>958.622771292973</v>
+        <v>3536.40151524512</v>
       </c>
       <c r="F177" t="n">
-        <v>1582.9199654394</v>
+        <v>11793.812157089</v>
       </c>
       <c r="G177" t="s">
         <v>68</v>
@@ -7828,13 +7828,13 @@
         <v>408</v>
       </c>
       <c r="I177" t="n">
-        <v>-36</v>
+        <v>15</v>
       </c>
       <c r="J177" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K177" t="n">
-        <v>0.911</v>
+        <v>1.036</v>
       </c>
       <c r="L177" t="s">
         <v>15</v>
@@ -7848,19 +7848,19 @@
         <v>44805</v>
       </c>
       <c r="B178" t="n">
-        <v>294.211990968974</v>
+        <v>374.636589385541</v>
       </c>
       <c r="C178" t="n">
-        <v>112.539801287114</v>
+        <v>38.366988348069</v>
       </c>
       <c r="D178" t="n">
-        <v>67.6662584035116</v>
+        <v>9.82231499833033</v>
       </c>
       <c r="E178" t="n">
-        <v>769.156286397668</v>
+        <v>3150.36585322352</v>
       </c>
       <c r="F178" t="n">
-        <v>1279.22982106893</v>
+        <v>11932.2793826709</v>
       </c>
       <c r="G178" t="s">
         <v>68</v>
@@ -7869,13 +7869,13 @@
         <v>350</v>
       </c>
       <c r="I178" t="n">
-        <v>-56</v>
+        <v>25</v>
       </c>
       <c r="J178" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K178" t="n">
-        <v>0.841</v>
+        <v>1.07</v>
       </c>
       <c r="L178" t="s">
         <v>15</v>
@@ -7889,19 +7889,19 @@
         <v>44835</v>
       </c>
       <c r="B179" t="n">
-        <v>360.002100477205</v>
+        <v>413.329145850658</v>
       </c>
       <c r="C179" t="n">
-        <v>135.882177739615</v>
+        <v>36.4247689073984</v>
       </c>
       <c r="D179" t="n">
-        <v>81.1268046307371</v>
+        <v>8.86130739206455</v>
       </c>
       <c r="E179" t="n">
-        <v>953.778593366005</v>
+        <v>3881.64998048044</v>
       </c>
       <c r="F179" t="n">
-        <v>1597.5177740317</v>
+        <v>13313.9266606365</v>
       </c>
       <c r="G179" t="s">
         <v>68</v>
@@ -7910,13 +7910,13 @@
         <v>317</v>
       </c>
       <c r="I179" t="n">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="J179" t="s">
         <v>17</v>
       </c>
       <c r="K179" t="n">
-        <v>1.136</v>
+        <v>1.304</v>
       </c>
       <c r="L179" t="s">
         <v>15</v>
@@ -7930,19 +7930,19 @@
         <v>44866</v>
       </c>
       <c r="B180" t="n">
-        <v>309.517001973735</v>
+        <v>397.271022542055</v>
       </c>
       <c r="C180" t="n">
-        <v>115.344622762106</v>
+        <v>35.5743341806384</v>
       </c>
       <c r="D180" t="n">
-        <v>68.4012565723714</v>
+        <v>7.17326475352768</v>
       </c>
       <c r="E180" t="n">
-        <v>830.561253890393</v>
+        <v>3934.9488427925</v>
       </c>
       <c r="F180" t="n">
-        <v>1400.57038878296</v>
+        <v>14961.3728793328</v>
       </c>
       <c r="G180" t="s">
         <v>68</v>
@@ -7951,13 +7951,13 @@
         <v>287</v>
       </c>
       <c r="I180" t="n">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="J180" t="s">
         <v>17</v>
       </c>
       <c r="K180" t="n">
-        <v>1.078</v>
+        <v>1.384</v>
       </c>
       <c r="L180" t="s">
         <v>15</v>
@@ -7971,19 +7971,19 @@
         <v>44896</v>
       </c>
       <c r="B181" t="n">
-        <v>250.547759326922</v>
+        <v>302.083677165308</v>
       </c>
       <c r="C181" t="n">
-        <v>92.1650078492268</v>
+        <v>23.3091642514558</v>
       </c>
       <c r="D181" t="n">
-        <v>54.2810930275213</v>
+        <v>4.95476915578884</v>
       </c>
       <c r="E181" t="n">
-        <v>681.106432567489</v>
+        <v>3056.14423101228</v>
       </c>
       <c r="F181" t="n">
-        <v>1156.46491628151</v>
+        <v>11828.5005948759</v>
       </c>
       <c r="G181" t="s">
         <v>68</v>
@@ -7992,13 +7992,13 @@
         <v>279</v>
       </c>
       <c r="I181" t="n">
-        <v>-28</v>
+        <v>23</v>
       </c>
       <c r="J181" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K181" t="n">
-        <v>0.898</v>
+        <v>1.083</v>
       </c>
       <c r="L181" t="s">
         <v>15</v>
@@ -8012,19 +8012,19 @@
         <v>44927</v>
       </c>
       <c r="B182" t="n">
-        <v>600.96531144364</v>
+        <v>817.158142810069</v>
       </c>
       <c r="C182" t="n">
-        <v>218.674377284218</v>
+        <v>64.9625198341637</v>
       </c>
       <c r="D182" t="n">
-        <v>128.049554109113</v>
+        <v>12.9338272016249</v>
       </c>
       <c r="E182" t="n">
-        <v>1651.58492752509</v>
+        <v>9724.50981389876</v>
       </c>
       <c r="F182" t="n">
-        <v>2820.46515562876</v>
+        <v>37442.7160804973</v>
       </c>
       <c r="G182" t="s">
         <v>68</v>
@@ -8033,13 +8033,13 @@
         <v>677</v>
       </c>
       <c r="I182" t="n">
-        <v>-76</v>
+        <v>140</v>
       </c>
       <c r="J182" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K182" t="n">
-        <v>0.888</v>
+        <v>1.207</v>
       </c>
       <c r="L182" t="s">
         <v>15</v>
@@ -8053,19 +8053,19 @@
         <v>44958</v>
       </c>
       <c r="B183" t="n">
-        <v>506.909388659944</v>
+        <v>567.309820988334</v>
       </c>
       <c r="C183" t="n">
-        <v>181.879086753422</v>
+        <v>38.6768330771834</v>
       </c>
       <c r="D183" t="n">
-        <v>105.714820224931</v>
+        <v>7.09110707194649</v>
       </c>
       <c r="E183" t="n">
-        <v>1412.79095303553</v>
+        <v>7750.19538342198</v>
       </c>
       <c r="F183" t="n">
-        <v>2430.66324820746</v>
+        <v>30420.388751653</v>
       </c>
       <c r="G183" t="s">
         <v>68</v>
@@ -8074,13 +8074,13 @@
         <v>406</v>
       </c>
       <c r="I183" t="n">
-        <v>101</v>
+        <v>161</v>
       </c>
       <c r="J183" t="s">
         <v>17</v>
       </c>
       <c r="K183" t="n">
-        <v>1.249</v>
+        <v>1.397</v>
       </c>
       <c r="L183" t="s">
         <v>15</v>
@@ -8094,19 +8094,19 @@
         <v>44986</v>
       </c>
       <c r="B184" t="n">
-        <v>390.708794761186</v>
+        <v>529.070694839274</v>
       </c>
       <c r="C184" t="n">
-        <v>138.097333952563</v>
+        <v>35.5801484433422</v>
       </c>
       <c r="D184" t="n">
-        <v>79.6318407234053</v>
+        <v>5.07078601860645</v>
       </c>
       <c r="E184" t="n">
-        <v>1105.40412283539</v>
+        <v>7188.15265407483</v>
       </c>
       <c r="F184" t="n">
-        <v>1916.98899481638</v>
+        <v>33325.0713043915</v>
       </c>
       <c r="G184" t="s">
         <v>68</v>
@@ -8115,13 +8115,13 @@
         <v>294</v>
       </c>
       <c r="I184" t="n">
-        <v>97</v>
+        <v>235</v>
       </c>
       <c r="J184" t="s">
         <v>17</v>
       </c>
       <c r="K184" t="n">
-        <v>1.329</v>
+        <v>1.8</v>
       </c>
       <c r="L184" t="s">
         <v>15</v>
@@ -8135,19 +8135,19 @@
         <v>45017</v>
       </c>
       <c r="B185" t="n">
-        <v>403.766684968689</v>
+        <v>481.906628860024</v>
       </c>
       <c r="C185" t="n">
-        <v>140.964145824864</v>
+        <v>27.8719782060841</v>
       </c>
       <c r="D185" t="n">
-        <v>80.7562097955803</v>
+        <v>4.03860193603428</v>
       </c>
       <c r="E185" t="n">
-        <v>1156.5177438322</v>
+        <v>7072.85653521005</v>
       </c>
       <c r="F185" t="n">
-        <v>2018.76160735229</v>
+        <v>34460.6444527542</v>
       </c>
       <c r="G185" t="s">
         <v>68</v>
@@ -8156,13 +8156,13 @@
         <v>219</v>
       </c>
       <c r="I185" t="n">
-        <v>185</v>
+        <v>263</v>
       </c>
       <c r="J185" t="s">
         <v>17</v>
       </c>
       <c r="K185" t="n">
-        <v>1.844</v>
+        <v>2.2</v>
       </c>
       <c r="L185" t="s">
         <v>15</v>
@@ -8176,19 +8176,19 @@
         <v>45047</v>
       </c>
       <c r="B186" t="n">
-        <v>343.264160738726</v>
+        <v>455.333705759705</v>
       </c>
       <c r="C186" t="n">
-        <v>118.296049427242</v>
+        <v>26.4902019557272</v>
       </c>
       <c r="D186" t="n">
-        <v>67.305998799351</v>
+        <v>3.13123197706415</v>
       </c>
       <c r="E186" t="n">
-        <v>996.06271399734</v>
+        <v>7488.4309965397</v>
       </c>
       <c r="F186" t="n">
-        <v>1750.66541095291</v>
+        <v>35226.5304216431</v>
       </c>
       <c r="G186" t="s">
         <v>68</v>
@@ -8197,13 +8197,13 @@
         <v>261</v>
       </c>
       <c r="I186" t="n">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="J186" t="s">
         <v>17</v>
       </c>
       <c r="K186" t="n">
-        <v>1.315</v>
+        <v>1.745</v>
       </c>
       <c r="L186" t="s">
         <v>15</v>
@@ -8217,19 +8217,19 @@
         <v>45078</v>
       </c>
       <c r="B187" t="n">
-        <v>335.33332381225</v>
+        <v>425.2896764439</v>
       </c>
       <c r="C187" t="n">
-        <v>114.180071471345</v>
+        <v>21.7558496292856</v>
       </c>
       <c r="D187" t="n">
-        <v>64.5514809189879</v>
+        <v>2.89632568432569</v>
       </c>
       <c r="E187" t="n">
-        <v>984.834188750633</v>
+        <v>7266.94922103987</v>
       </c>
       <c r="F187" t="n">
-        <v>1741.99625567219</v>
+        <v>39128.7229908597</v>
       </c>
       <c r="G187" t="s">
         <v>68</v>
@@ -8238,13 +8238,13 @@
         <v>185</v>
       </c>
       <c r="I187" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="J187" t="s">
         <v>17</v>
       </c>
       <c r="K187" t="n">
-        <v>1.813</v>
+        <v>2.299</v>
       </c>
       <c r="L187" t="s">
         <v>15</v>
@@ -8258,19 +8258,19 @@
         <v>45108</v>
       </c>
       <c r="B188" t="n">
-        <v>313.508785540056</v>
+        <v>423.959151115876</v>
       </c>
       <c r="C188" t="n">
-        <v>105.447668731645</v>
+        <v>17.4789719458853</v>
       </c>
       <c r="D188" t="n">
-        <v>59.2288490766651</v>
+        <v>2.08366330266331</v>
       </c>
       <c r="E188" t="n">
-        <v>932.099872790307</v>
+        <v>8042.57298796474</v>
       </c>
       <c r="F188" t="n">
-        <v>1659.45751340835</v>
+        <v>45153.1271942972</v>
       </c>
       <c r="G188" t="s">
         <v>68</v>
@@ -8279,13 +8279,13 @@
         <v>202</v>
       </c>
       <c r="I188" t="n">
-        <v>112</v>
+        <v>222</v>
       </c>
       <c r="J188" t="s">
         <v>17</v>
       </c>
       <c r="K188" t="n">
-        <v>1.552</v>
+        <v>2.099</v>
       </c>
       <c r="L188" t="s">
         <v>15</v>
@@ -8299,19 +8299,19 @@
         <v>45139</v>
       </c>
       <c r="B189" t="n">
-        <v>371.699999165314</v>
+        <v>468.680627322006</v>
       </c>
       <c r="C189" t="n">
-        <v>123.556897218383</v>
+        <v>18.3474140328594</v>
       </c>
       <c r="D189" t="n">
-        <v>68.9694454578572</v>
+        <v>1.93861959324743</v>
       </c>
       <c r="E189" t="n">
-        <v>1118.19649481242</v>
+        <v>9296.06252756103</v>
       </c>
       <c r="F189" t="n">
-        <v>2003.21879438506</v>
+        <v>49322.3595583359</v>
       </c>
       <c r="G189" t="s">
         <v>68</v>
@@ -8320,13 +8320,13 @@
         <v>165</v>
       </c>
       <c r="I189" t="n">
-        <v>207</v>
+        <v>304</v>
       </c>
       <c r="J189" t="s">
         <v>17</v>
       </c>
       <c r="K189" t="n">
-        <v>2.253</v>
+        <v>2.84</v>
       </c>
       <c r="L189" t="s">
         <v>15</v>
@@ -8340,19 +8340,19 @@
         <v>45170</v>
       </c>
       <c r="B190" t="n">
-        <v>294.211990968974</v>
+        <v>413.163562282602</v>
       </c>
       <c r="C190" t="n">
-        <v>96.6609569408551</v>
+        <v>15.6137410978467</v>
       </c>
       <c r="D190" t="n">
-        <v>53.6228232673698</v>
+        <v>1.47574088918885</v>
       </c>
       <c r="E190" t="n">
-        <v>895.508366246494</v>
+        <v>10198.4240715728</v>
       </c>
       <c r="F190" t="n">
-        <v>1614.25099156615</v>
+        <v>50450.8549444451</v>
       </c>
       <c r="G190" t="s">
         <v>68</v>
@@ -8361,13 +8361,13 @@
         <v>195</v>
       </c>
       <c r="I190" t="n">
-        <v>99</v>
+        <v>218</v>
       </c>
       <c r="J190" t="s">
         <v>17</v>
       </c>
       <c r="K190" t="n">
-        <v>1.509</v>
+        <v>2.119</v>
       </c>
       <c r="L190" t="s">
         <v>15</v>
@@ -8381,19 +8381,19 @@
         <v>45200</v>
       </c>
       <c r="B191" t="n">
-        <v>360.002100477205</v>
+        <v>448.077908611792</v>
       </c>
       <c r="C191" t="n">
-        <v>116.920227189505</v>
+        <v>15.8069591417263</v>
       </c>
       <c r="D191" t="n">
-        <v>64.4671044313278</v>
+        <v>1.44532199932599</v>
       </c>
       <c r="E191" t="n">
-        <v>1108.46100339799</v>
+        <v>10464.150247112</v>
       </c>
       <c r="F191" t="n">
-        <v>2010.35106960721</v>
+        <v>63124.3845036126</v>
       </c>
       <c r="G191" t="s">
         <v>68</v>
@@ -8402,13 +8402,13 @@
         <v>111</v>
       </c>
       <c r="I191" t="n">
-        <v>249</v>
+        <v>337</v>
       </c>
       <c r="J191" t="s">
         <v>17</v>
       </c>
       <c r="K191" t="n">
-        <v>3.243</v>
+        <v>4.036</v>
       </c>
       <c r="L191" t="s">
         <v>15</v>
@@ -8422,19 +8422,19 @@
         <v>45231</v>
       </c>
       <c r="B192" t="n">
-        <v>309.517001973735</v>
+        <v>431.660931489877</v>
       </c>
       <c r="C192" t="n">
-        <v>99.4163298681314</v>
+        <v>13.8154955519515</v>
       </c>
       <c r="D192" t="n">
-        <v>54.4953239727232</v>
+        <v>1.11355146097553</v>
       </c>
       <c r="E192" t="n">
-        <v>963.632178313986</v>
+        <v>11592.6244068255</v>
       </c>
       <c r="F192" t="n">
-        <v>1757.96320724253</v>
+        <v>73387.8156288801</v>
       </c>
       <c r="G192" t="s">
         <v>68</v>
@@ -8443,13 +8443,13 @@
         <v>106</v>
       </c>
       <c r="I192" t="n">
-        <v>204</v>
+        <v>326</v>
       </c>
       <c r="J192" t="s">
         <v>17</v>
       </c>
       <c r="K192" t="n">
-        <v>2.92</v>
+        <v>4.072</v>
       </c>
       <c r="L192" t="s">
         <v>15</v>
@@ -8463,19 +8463,19 @@
         <v>45261</v>
       </c>
       <c r="B193" t="n">
-        <v>250.547759326922</v>
+        <v>327.404582579793</v>
       </c>
       <c r="C193" t="n">
-        <v>79.5712695457056</v>
+        <v>9.01286747910357</v>
       </c>
       <c r="D193" t="n">
-        <v>43.3570725739076</v>
+        <v>0.702773303824581</v>
       </c>
       <c r="E193" t="n">
-        <v>788.905091776674</v>
+        <v>9310.72813967383</v>
       </c>
       <c r="F193" t="n">
-        <v>1447.8417470814</v>
+        <v>58603.9828931683</v>
       </c>
       <c r="G193" t="s">
         <v>68</v>
@@ -8484,13 +8484,13 @@
         <v>105</v>
       </c>
       <c r="I193" t="n">
-        <v>146</v>
+        <v>222</v>
       </c>
       <c r="J193" t="s">
         <v>17</v>
       </c>
       <c r="K193" t="n">
-        <v>2.386</v>
+        <v>3.118</v>
       </c>
       <c r="L193" t="s">
         <v>15</v>
@@ -10472,19 +10472,19 @@
         <v>43831</v>
       </c>
       <c r="B242" t="n">
-        <v>26.0338676630422</v>
+        <v>25.0076305545845</v>
       </c>
       <c r="C242" t="n">
-        <v>16.7598692414701</v>
+        <v>14.6101317329283</v>
       </c>
       <c r="D242" t="n">
-        <v>13.0487902757839</v>
+        <v>10.9098133857939</v>
       </c>
       <c r="E242" t="n">
-        <v>39.139694553668</v>
+        <v>42.7295780262215</v>
       </c>
       <c r="F242" t="n">
-        <v>48.0591254717645</v>
+        <v>55.1254897005897</v>
       </c>
       <c r="G242" t="s">
         <v>70</v>
@@ -10493,13 +10493,13 @@
         <v>31</v>
       </c>
       <c r="I242" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J242" t="s">
         <v>14</v>
       </c>
       <c r="K242" t="n">
-        <v>0.84</v>
+        <v>0.807</v>
       </c>
       <c r="L242" t="s">
         <v>15</v>
@@ -10513,19 +10513,19 @@
         <v>43862</v>
       </c>
       <c r="B243" t="n">
-        <v>19.1487258091164</v>
+        <v>18.4828542281959</v>
       </c>
       <c r="C243" t="n">
-        <v>11.3423804542323</v>
+        <v>10.3426576744345</v>
       </c>
       <c r="D243" t="n">
-        <v>8.35297472388004</v>
+        <v>7.57283792824978</v>
       </c>
       <c r="E243" t="n">
-        <v>30.7501831333425</v>
+        <v>33.6793194079908</v>
       </c>
       <c r="F243" t="n">
-        <v>38.9189756671806</v>
+        <v>42.2796363091235</v>
       </c>
       <c r="G243" t="s">
         <v>70</v>
@@ -10534,13 +10534,13 @@
         <v>24</v>
       </c>
       <c r="I243" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J243" t="s">
         <v>14</v>
       </c>
       <c r="K243" t="n">
-        <v>0.798</v>
+        <v>0.77</v>
       </c>
       <c r="L243" t="s">
         <v>15</v>
@@ -10554,19 +10554,19 @@
         <v>43891</v>
       </c>
       <c r="B244" t="n">
-        <v>16.2738600839784</v>
+        <v>15.327208693279</v>
       </c>
       <c r="C244" t="n">
-        <v>8.96586943970077</v>
+        <v>8.02211651666547</v>
       </c>
       <c r="D244" t="n">
-        <v>6.27037041367459</v>
+        <v>5.81852652468762</v>
       </c>
       <c r="E244" t="n">
-        <v>27.6090626771434</v>
+        <v>30.4962434543631</v>
       </c>
       <c r="F244" t="n">
-        <v>35.8217133392415</v>
+        <v>43.0421890047142</v>
       </c>
       <c r="G244" t="s">
         <v>70</v>
@@ -10575,13 +10575,13 @@
         <v>25</v>
       </c>
       <c r="I244" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="J244" t="s">
         <v>14</v>
       </c>
       <c r="K244" t="n">
-        <v>0.651</v>
+        <v>0.613</v>
       </c>
       <c r="L244" t="s">
         <v>15</v>
@@ -10595,19 +10595,19 @@
         <v>43922</v>
       </c>
       <c r="B245" t="n">
-        <v>16.1061380387927</v>
+        <v>14.5671701008544</v>
       </c>
       <c r="C245" t="n">
-        <v>8.4408790554431</v>
+        <v>7.12887468169434</v>
       </c>
       <c r="D245" t="n">
-        <v>5.69561747745156</v>
+        <v>4.9952319678691</v>
       </c>
       <c r="E245" t="n">
-        <v>28.3968261337172</v>
+        <v>28.787291411368</v>
       </c>
       <c r="F245" t="n">
-        <v>37.5009403095613</v>
+        <v>42.4867861861986</v>
       </c>
       <c r="G245" t="s">
         <v>70</v>
@@ -10616,13 +10616,13 @@
         <v>15</v>
       </c>
       <c r="I245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J245" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K245" t="n">
-        <v>1.074</v>
+        <v>0.971</v>
       </c>
       <c r="L245" t="s">
         <v>15</v>
@@ -10636,19 +10636,19 @@
         <v>43952</v>
       </c>
       <c r="B246" t="n">
-        <v>14.309307493733</v>
+        <v>15.4335896185166</v>
       </c>
       <c r="C246" t="n">
-        <v>7.00156245962521</v>
+        <v>7.37523416177314</v>
       </c>
       <c r="D246" t="n">
-        <v>4.46831556692771</v>
+        <v>4.75706096515154</v>
       </c>
       <c r="E246" t="n">
-        <v>26.4719161182711</v>
+        <v>34.3133461107729</v>
       </c>
       <c r="F246" t="n">
-        <v>35.7038615023721</v>
+        <v>52.3493333353805</v>
       </c>
       <c r="G246" t="s">
         <v>70</v>
@@ -10657,13 +10657,13 @@
         <v>10</v>
       </c>
       <c r="I246" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J246" t="s">
         <v>17</v>
       </c>
       <c r="K246" t="n">
-        <v>1.431</v>
+        <v>1.543</v>
       </c>
       <c r="L246" t="s">
         <v>15</v>
@@ -10677,19 +10677,19 @@
         <v>43983</v>
       </c>
       <c r="B247" t="n">
-        <v>15.4595344915785</v>
+        <v>14.90483540755</v>
       </c>
       <c r="C247" t="n">
-        <v>7.34661624294857</v>
+        <v>6.50450760433106</v>
       </c>
       <c r="D247" t="n">
-        <v>4.59705389196699</v>
+        <v>3.88471246762832</v>
       </c>
       <c r="E247" t="n">
-        <v>29.2966349436723</v>
+        <v>33.3189478532331</v>
       </c>
       <c r="F247" t="n">
-        <v>39.9705663069066</v>
+        <v>48.907514189499</v>
       </c>
       <c r="G247" t="s">
         <v>70</v>
@@ -10704,7 +10704,7 @@
         <v>17</v>
       </c>
       <c r="K247" t="n">
-        <v>1.104</v>
+        <v>1.065</v>
       </c>
       <c r="L247" t="s">
         <v>15</v>
@@ -10718,19 +10718,19 @@
         <v>44013</v>
       </c>
       <c r="B248" t="n">
-        <v>13.5192592948058</v>
+        <v>14.0672800801007</v>
       </c>
       <c r="C248" t="n">
-        <v>5.96586472834795</v>
+        <v>5.87238623165644</v>
       </c>
       <c r="D248" t="n">
-        <v>3.48211165454755</v>
+        <v>3.6052254533939</v>
       </c>
       <c r="E248" t="n">
-        <v>26.8720016753164</v>
+        <v>32.3935455980099</v>
       </c>
       <c r="F248" t="n">
-        <v>37.4122673934012</v>
+        <v>52.4651315492341</v>
       </c>
       <c r="G248" t="s">
         <v>70</v>
@@ -10745,7 +10745,7 @@
         <v>14</v>
       </c>
       <c r="K248" t="n">
-        <v>0.541</v>
+        <v>0.563</v>
       </c>
       <c r="L248" t="s">
         <v>15</v>
@@ -10759,19 +10759,19 @@
         <v>44044</v>
       </c>
       <c r="B249" t="n">
-        <v>13.4682450711578</v>
+        <v>13.0890281080425</v>
       </c>
       <c r="C249" t="n">
-        <v>5.68515645736193</v>
+        <v>5.18981724555519</v>
       </c>
       <c r="D249" t="n">
-        <v>3.18510853670634</v>
+        <v>2.91050091078718</v>
       </c>
       <c r="E249" t="n">
-        <v>27.599077936302</v>
+        <v>33.3217177353593</v>
       </c>
       <c r="F249" t="n">
-        <v>38.9467067109698</v>
+        <v>55.2186959074021</v>
       </c>
       <c r="G249" t="s">
         <v>70</v>
@@ -10786,7 +10786,7 @@
         <v>14</v>
       </c>
       <c r="K249" t="n">
-        <v>0.842</v>
+        <v>0.818</v>
       </c>
       <c r="L249" t="s">
         <v>15</v>
@@ -10800,19 +10800,19 @@
         <v>44075</v>
       </c>
       <c r="B250" t="n">
-        <v>15.1552509191016</v>
+        <v>14.7576184626992</v>
       </c>
       <c r="C250" t="n">
-        <v>6.33213341899523</v>
+        <v>5.83933367801379</v>
       </c>
       <c r="D250" t="n">
-        <v>3.54922309136228</v>
+        <v>3.62396644209043</v>
       </c>
       <c r="E250" t="n">
-        <v>31.4526789049199</v>
+        <v>39.4565292053722</v>
       </c>
       <c r="F250" t="n">
-        <v>44.688298910205</v>
+        <v>70.6423981895699</v>
       </c>
       <c r="G250" t="s">
         <v>70</v>
@@ -10827,7 +10827,7 @@
         <v>14</v>
       </c>
       <c r="K250" t="n">
-        <v>0.689</v>
+        <v>0.671</v>
       </c>
       <c r="L250" t="s">
         <v>15</v>
@@ -10841,19 +10841,19 @@
         <v>44105</v>
       </c>
       <c r="B251" t="n">
-        <v>13.8316138953696</v>
+        <v>13.0261236909588</v>
       </c>
       <c r="C251" t="n">
-        <v>5.4147736619654</v>
+        <v>4.83117025430414</v>
       </c>
       <c r="D251" t="n">
-        <v>2.82387938426382</v>
+        <v>2.35899626534081</v>
       </c>
       <c r="E251" t="n">
-        <v>29.859342468714</v>
+        <v>37.8116450419296</v>
       </c>
       <c r="F251" t="n">
-        <v>43.1281446641392</v>
+        <v>70.4606200701833</v>
       </c>
       <c r="G251" t="s">
         <v>70</v>
@@ -10862,13 +10862,13 @@
         <v>20</v>
       </c>
       <c r="I251" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="J251" t="s">
         <v>14</v>
       </c>
       <c r="K251" t="n">
-        <v>0.692</v>
+        <v>0.651</v>
       </c>
       <c r="L251" t="s">
         <v>15</v>
@@ -10882,19 +10882,19 @@
         <v>44136</v>
       </c>
       <c r="B252" t="n">
-        <v>12.9939364659813</v>
+        <v>13.2148697174667</v>
       </c>
       <c r="C252" t="n">
-        <v>4.79006762986537</v>
+        <v>4.66118329641137</v>
       </c>
       <c r="D252" t="n">
-        <v>2.31378767536863</v>
+        <v>2.4902544933036</v>
       </c>
       <c r="E252" t="n">
-        <v>29.0568355216982</v>
+        <v>37.877512023322</v>
       </c>
       <c r="F252" t="n">
-        <v>42.5893364249374</v>
+        <v>72.238429731154</v>
       </c>
       <c r="G252" t="s">
         <v>70</v>
@@ -10909,7 +10909,7 @@
         <v>14</v>
       </c>
       <c r="K252" t="n">
-        <v>0.866</v>
+        <v>0.881</v>
       </c>
       <c r="L252" t="s">
         <v>15</v>
@@ -10923,19 +10923,19 @@
         <v>44166</v>
       </c>
       <c r="B253" t="n">
-        <v>10.3248737382636</v>
+        <v>10.3673543996669</v>
       </c>
       <c r="C253" t="n">
-        <v>3.32510994455969</v>
+        <v>3.4563913446456</v>
       </c>
       <c r="D253" t="n">
-        <v>1.05794970803218</v>
+        <v>1.82839214961885</v>
       </c>
       <c r="E253" t="n">
-        <v>24.5729013462207</v>
+        <v>33.0056937312996</v>
       </c>
       <c r="F253" t="n">
-        <v>36.8767308404507</v>
+        <v>63.820690080756</v>
       </c>
       <c r="G253" t="s">
         <v>70</v>
@@ -10950,7 +10950,7 @@
         <v>14</v>
       </c>
       <c r="K253" t="n">
-        <v>0.646</v>
+        <v>0.648</v>
       </c>
       <c r="L253" t="s">
         <v>15</v>
@@ -10964,19 +10964,19 @@
         <v>44197</v>
       </c>
       <c r="B254" t="n">
-        <v>26.0338676630422</v>
+        <v>25.7154721281317</v>
       </c>
       <c r="C254" t="n">
-        <v>10.7383043510384</v>
+        <v>7.91336705889863</v>
       </c>
       <c r="D254" t="n">
-        <v>6.14579544505426</v>
+        <v>3.35690993541026</v>
       </c>
       <c r="E254" t="n">
-        <v>55.7182241591018</v>
+        <v>89.9956618266285</v>
       </c>
       <c r="F254" t="n">
-        <v>80.6489216971119</v>
+        <v>169.777159670872</v>
       </c>
       <c r="G254" t="s">
         <v>70</v>
@@ -10991,7 +10991,7 @@
         <v>14</v>
       </c>
       <c r="K254" t="n">
-        <v>0.651</v>
+        <v>0.643</v>
       </c>
       <c r="L254" t="s">
         <v>15</v>
@@ -11005,19 +11005,19 @@
         <v>44228</v>
       </c>
       <c r="B255" t="n">
-        <v>19.1487258091164</v>
+        <v>18.6596194296991</v>
       </c>
       <c r="C255" t="n">
-        <v>7.12205137227019</v>
+        <v>5.20044720904859</v>
       </c>
       <c r="D255" t="n">
-        <v>3.65495460150561</v>
+        <v>2.55595545972884</v>
       </c>
       <c r="E255" t="n">
-        <v>43.5315999624819</v>
+        <v>72.7663756196927</v>
       </c>
       <c r="F255" t="n">
-        <v>64.5524900994735</v>
+        <v>138.748623800175</v>
       </c>
       <c r="G255" t="s">
         <v>70</v>
@@ -11032,7 +11032,7 @@
         <v>14</v>
       </c>
       <c r="K255" t="n">
-        <v>0.638</v>
+        <v>0.622</v>
       </c>
       <c r="L255" t="s">
         <v>15</v>
@@ -11046,19 +11046,19 @@
         <v>44256</v>
       </c>
       <c r="B256" t="n">
-        <v>16.2738600839784</v>
+        <v>16.0142217839584</v>
       </c>
       <c r="C256" t="n">
-        <v>5.57729192598637</v>
+        <v>4.42922066003556</v>
       </c>
       <c r="D256" t="n">
-        <v>2.57199025082019</v>
+        <v>2.06482895999439</v>
       </c>
       <c r="E256" t="n">
-        <v>38.690507554816</v>
+        <v>64.2903851459232</v>
       </c>
       <c r="F256" t="n">
-        <v>58.4060455806696</v>
+        <v>125.790520249848</v>
       </c>
       <c r="G256" t="s">
         <v>70</v>
@@ -11073,7 +11073,7 @@
         <v>14</v>
       </c>
       <c r="K256" t="n">
-        <v>0.452</v>
+        <v>0.445</v>
       </c>
       <c r="L256" t="s">
         <v>15</v>
@@ -11087,19 +11087,19 @@
         <v>44287</v>
       </c>
       <c r="B257" t="n">
-        <v>16.1061380387927</v>
+        <v>14.7709276383855</v>
       </c>
       <c r="C257" t="n">
-        <v>5.31768061996498</v>
+        <v>3.74342200837913</v>
       </c>
       <c r="D257" t="n">
-        <v>2.33796260917474</v>
+        <v>1.70844950603986</v>
       </c>
       <c r="E257" t="n">
-        <v>39.1825352280966</v>
+        <v>56.273760320899</v>
       </c>
       <c r="F257" t="n">
-        <v>59.7359904729674</v>
+        <v>130.794198859191</v>
       </c>
       <c r="G257" t="s">
         <v>70</v>
@@ -11108,13 +11108,13 @@
         <v>21</v>
       </c>
       <c r="I257" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J257" t="s">
         <v>14</v>
       </c>
       <c r="K257" t="n">
-        <v>0.767</v>
+        <v>0.704</v>
       </c>
       <c r="L257" t="s">
         <v>15</v>
@@ -11128,19 +11128,19 @@
         <v>44317</v>
       </c>
       <c r="B258" t="n">
-        <v>14.309307493733</v>
+        <v>15.4214577256529</v>
       </c>
       <c r="C258" t="n">
-        <v>4.36301470078818</v>
+        <v>3.57687019910654</v>
       </c>
       <c r="D258" t="n">
-        <v>1.63402879295741</v>
+        <v>1.48277960393386</v>
       </c>
       <c r="E258" t="n">
-        <v>36.2141269543499</v>
+        <v>67.7855476043245</v>
       </c>
       <c r="F258" t="n">
-        <v>56.0697847707661</v>
+        <v>148.493966743735</v>
       </c>
       <c r="G258" t="s">
         <v>70</v>
@@ -11149,13 +11149,13 @@
         <v>25</v>
       </c>
       <c r="I258" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="J258" t="s">
         <v>14</v>
       </c>
       <c r="K258" t="n">
-        <v>0.573</v>
+        <v>0.617</v>
       </c>
       <c r="L258" t="s">
         <v>15</v>
@@ -11169,19 +11169,19 @@
         <v>44348</v>
       </c>
       <c r="B259" t="n">
-        <v>15.4595344915785</v>
+        <v>14.9839824081058</v>
       </c>
       <c r="C259" t="n">
-        <v>4.70044189810686</v>
+        <v>3.17306557890104</v>
       </c>
       <c r="D259" t="n">
-        <v>1.81125811792128</v>
+        <v>1.3155515274046</v>
       </c>
       <c r="E259" t="n">
-        <v>39.4429962455593</v>
+        <v>63.1931305723598</v>
       </c>
       <c r="F259" t="n">
-        <v>61.3495869159171</v>
+        <v>165.128011990277</v>
       </c>
       <c r="G259" t="s">
         <v>70</v>
@@ -11196,7 +11196,7 @@
         <v>14</v>
       </c>
       <c r="K259" t="n">
-        <v>0.909</v>
+        <v>0.881</v>
       </c>
       <c r="L259" t="s">
         <v>15</v>
@@ -11210,19 +11210,19 @@
         <v>44378</v>
       </c>
       <c r="B260" t="n">
-        <v>13.5192592948058</v>
+        <v>13.9431854521815</v>
       </c>
       <c r="C260" t="n">
-        <v>3.74114808795575</v>
+        <v>2.73360680282215</v>
       </c>
       <c r="D260" t="n">
-        <v>0.862996789396804</v>
+        <v>1.13878861639731</v>
       </c>
       <c r="E260" t="n">
-        <v>35.979583319272</v>
+        <v>68.3540573420761</v>
       </c>
       <c r="F260" t="n">
-        <v>56.8663079756008</v>
+        <v>163.530198079203</v>
       </c>
       <c r="G260" t="s">
         <v>70</v>
@@ -11237,7 +11237,7 @@
         <v>17</v>
       </c>
       <c r="K260" t="n">
-        <v>1.229</v>
+        <v>1.267</v>
       </c>
       <c r="L260" t="s">
         <v>15</v>
@@ -11251,19 +11251,19 @@
         <v>44409</v>
       </c>
       <c r="B261" t="n">
-        <v>13.4682450711578</v>
+        <v>13.3921650710459</v>
       </c>
       <c r="C261" t="n">
-        <v>3.58865600880582</v>
+        <v>2.83538835838036</v>
       </c>
       <c r="D261" t="n">
-        <v>0.729198869169882</v>
+        <v>0.991424330358672</v>
       </c>
       <c r="E261" t="n">
-        <v>36.5815200315639</v>
+        <v>72.2418105807062</v>
       </c>
       <c r="F261" t="n">
-        <v>58.3156962407914</v>
+        <v>188.703442055005</v>
       </c>
       <c r="G261" t="s">
         <v>70</v>
@@ -11278,7 +11278,7 @@
         <v>17</v>
       </c>
       <c r="K261" t="n">
-        <v>1.683</v>
+        <v>1.673</v>
       </c>
       <c r="L261" t="s">
         <v>15</v>
@@ -11292,19 +11292,19 @@
         <v>44440</v>
       </c>
       <c r="B262" t="n">
-        <v>15.1552509191016</v>
+        <v>14.9123634944841</v>
       </c>
       <c r="C262" t="n">
-        <v>4.13509902705129</v>
+        <v>2.91921927732793</v>
       </c>
       <c r="D262" t="n">
-        <v>1.21480659348083</v>
+        <v>1.00470673759071</v>
       </c>
       <c r="E262" t="n">
-        <v>41.117165255787</v>
+        <v>81.0321213490509</v>
       </c>
       <c r="F262" t="n">
-        <v>65.6394144156715</v>
+        <v>206.516830389873</v>
       </c>
       <c r="G262" t="s">
         <v>70</v>
@@ -11319,7 +11319,7 @@
         <v>17</v>
       </c>
       <c r="K262" t="n">
-        <v>1.515</v>
+        <v>1.491</v>
       </c>
       <c r="L262" t="s">
         <v>15</v>
@@ -11333,19 +11333,19 @@
         <v>44470</v>
       </c>
       <c r="B263" t="n">
-        <v>13.8316138953696</v>
+        <v>13.1561644181341</v>
       </c>
       <c r="C263" t="n">
-        <v>3.48298444603847</v>
+        <v>2.31203551020176</v>
       </c>
       <c r="D263" t="n">
-        <v>0.636423754737862</v>
+        <v>0.776318604104399</v>
       </c>
       <c r="E263" t="n">
-        <v>38.840202044385</v>
+        <v>75.4477590291822</v>
       </c>
       <c r="F263" t="n">
-        <v>62.8220240155677</v>
+        <v>235.26228050817</v>
       </c>
       <c r="G263" t="s">
         <v>70</v>
@@ -11354,13 +11354,13 @@
         <v>12</v>
       </c>
       <c r="I263" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J263" t="s">
         <v>17</v>
       </c>
       <c r="K263" t="n">
-        <v>1.153</v>
+        <v>1.096</v>
       </c>
       <c r="L263" t="s">
         <v>15</v>
@@ -11374,19 +11374,19 @@
         <v>44501</v>
       </c>
       <c r="B264" t="n">
-        <v>12.9939364659813</v>
+        <v>13.7578930996478</v>
       </c>
       <c r="C264" t="n">
-        <v>3.0426028998733</v>
+        <v>2.09274205900055</v>
       </c>
       <c r="D264" t="n">
-        <v>0.502146300119774</v>
+        <v>0.721985789330001</v>
       </c>
       <c r="E264" t="n">
-        <v>37.5880533141534</v>
+        <v>80.8140924252257</v>
       </c>
       <c r="F264" t="n">
-        <v>61.4922457399557</v>
+        <v>231.411402408904</v>
       </c>
       <c r="G264" t="s">
         <v>70</v>
@@ -11395,13 +11395,13 @@
         <v>7</v>
       </c>
       <c r="I264" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J264" t="s">
         <v>17</v>
       </c>
       <c r="K264" t="n">
-        <v>1.855</v>
+        <v>1.964</v>
       </c>
       <c r="L264" t="s">
         <v>15</v>
@@ -11415,19 +11415,19 @@
         <v>44531</v>
       </c>
       <c r="B265" t="n">
-        <v>10.3248737382636</v>
+        <v>10.4874779829291</v>
       </c>
       <c r="C265" t="n">
-        <v>1.9148780062104</v>
+        <v>1.47963011135513</v>
       </c>
       <c r="D265" t="n">
-        <v>0.313361584587988</v>
+        <v>0.475053822821984</v>
       </c>
       <c r="E265" t="n">
-        <v>31.8200294494295</v>
+        <v>79.706829088736</v>
       </c>
       <c r="F265" t="n">
-        <v>53.1886272005374</v>
+        <v>235.605223375096</v>
       </c>
       <c r="G265" t="s">
         <v>70</v>
@@ -11442,7 +11442,7 @@
         <v>17</v>
       </c>
       <c r="K265" t="n">
-        <v>1.29</v>
+        <v>1.311</v>
       </c>
       <c r="L265" t="s">
         <v>15</v>
@@ -11456,19 +11456,19 @@
         <v>44562</v>
       </c>
       <c r="B266" t="n">
-        <v>26.0338676630422</v>
+        <v>25.5577608643023</v>
       </c>
       <c r="C266" t="n">
-        <v>7.78791967138843</v>
+        <v>3.46230562273426</v>
       </c>
       <c r="D266" t="n">
-        <v>3.31567917763305</v>
+        <v>1.15852286086865</v>
       </c>
       <c r="E266" t="n">
-        <v>69.5888343877755</v>
+        <v>184.08205810988</v>
       </c>
       <c r="F266" t="n">
-        <v>111.191711994238</v>
+        <v>795.591150271868</v>
       </c>
       <c r="G266" t="s">
         <v>70</v>
@@ -11483,7 +11483,7 @@
         <v>14</v>
       </c>
       <c r="K266" t="n">
-        <v>0.635</v>
+        <v>0.623</v>
       </c>
       <c r="L266" t="s">
         <v>15</v>
@@ -11497,19 +11497,19 @@
         <v>44593</v>
       </c>
       <c r="B267" t="n">
-        <v>19.1487258091164</v>
+        <v>18.4558353086767</v>
       </c>
       <c r="C267" t="n">
-        <v>4.98578577847768</v>
+        <v>2.42024589573799</v>
       </c>
       <c r="D267" t="n">
-        <v>1.58374391842972</v>
+        <v>0.59522269009602</v>
       </c>
       <c r="E267" t="n">
-        <v>54.5333063299614</v>
+        <v>148.587841077102</v>
       </c>
       <c r="F267" t="n">
-        <v>89.1963993307747</v>
+        <v>606.754315587769</v>
       </c>
       <c r="G267" t="s">
         <v>70</v>
@@ -11518,13 +11518,13 @@
         <v>18</v>
       </c>
       <c r="I267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J267" t="s">
         <v>17</v>
       </c>
       <c r="K267" t="n">
-        <v>1.064</v>
+        <v>1.025</v>
       </c>
       <c r="L267" t="s">
         <v>15</v>
@@ -11538,19 +11538,19 @@
         <v>44621</v>
       </c>
       <c r="B268" t="n">
-        <v>16.2738600839784</v>
+        <v>16.0358557612522</v>
       </c>
       <c r="C268" t="n">
-        <v>3.80393987903072</v>
+        <v>1.88509780220615</v>
       </c>
       <c r="D268" t="n">
-        <v>0.638371772404821</v>
+        <v>0.510371248699362</v>
       </c>
       <c r="E268" t="n">
-        <v>48.4323808661257</v>
+        <v>141.170380935534</v>
       </c>
       <c r="F268" t="n">
-        <v>80.5061420683186</v>
+        <v>487.399816126347</v>
       </c>
       <c r="G268" t="s">
         <v>70</v>
@@ -11565,7 +11565,7 @@
         <v>14</v>
       </c>
       <c r="K268" t="n">
-        <v>0.603</v>
+        <v>0.594</v>
       </c>
       <c r="L268" t="s">
         <v>15</v>
@@ -11579,19 +11579,19 @@
         <v>44652</v>
       </c>
       <c r="B269" t="n">
-        <v>16.1061380387927</v>
+        <v>14.4726320599796</v>
       </c>
       <c r="C269" t="n">
-        <v>3.62974032111983</v>
+        <v>1.47741774706592</v>
       </c>
       <c r="D269" t="n">
-        <v>0.571283012909242</v>
+        <v>0.416377700961287</v>
       </c>
       <c r="E269" t="n">
-        <v>48.8067267089671</v>
+        <v>132.052236151061</v>
       </c>
       <c r="F269" t="n">
-        <v>81.7339719250124</v>
+        <v>515.653204182173</v>
       </c>
       <c r="G269" t="s">
         <v>70</v>
@@ -11600,13 +11600,13 @@
         <v>40</v>
       </c>
       <c r="I269" t="n">
-        <v>-24</v>
+        <v>-26</v>
       </c>
       <c r="J269" t="s">
         <v>14</v>
       </c>
       <c r="K269" t="n">
-        <v>0.403</v>
+        <v>0.362</v>
       </c>
       <c r="L269" t="s">
         <v>15</v>
@@ -11620,19 +11620,19 @@
         <v>44682</v>
       </c>
       <c r="B270" t="n">
-        <v>14.309307493733</v>
+        <v>15.3878554655459</v>
       </c>
       <c r="C270" t="n">
-        <v>2.89467691711104</v>
+        <v>1.54457542365497</v>
       </c>
       <c r="D270" t="n">
-        <v>0.412790244456066</v>
+        <v>0.433823137209707</v>
       </c>
       <c r="E270" t="n">
-        <v>45.0377161033023</v>
+        <v>162.729727018319</v>
       </c>
       <c r="F270" t="n">
-        <v>76.4620132875297</v>
+        <v>590.682128781282</v>
       </c>
       <c r="G270" t="s">
         <v>70</v>
@@ -11641,13 +11641,13 @@
         <v>151</v>
       </c>
       <c r="I270" t="n">
-        <v>-137</v>
+        <v>-136</v>
       </c>
       <c r="J270" t="s">
         <v>14</v>
       </c>
       <c r="K270" t="n">
-        <v>0.095</v>
+        <v>0.102</v>
       </c>
       <c r="L270" t="s">
         <v>15</v>
@@ -11661,19 +11661,19 @@
         <v>44713</v>
       </c>
       <c r="B271" t="n">
-        <v>15.4595344915785</v>
+        <v>14.9989955879841</v>
       </c>
       <c r="C271" t="n">
-        <v>3.19144490989402</v>
+        <v>1.4936573206404</v>
       </c>
       <c r="D271" t="n">
-        <v>0.453833962849173</v>
+        <v>0.351402990516101</v>
       </c>
       <c r="E271" t="n">
-        <v>48.7180717063739</v>
+        <v>173.830723781491</v>
       </c>
       <c r="F271" t="n">
-        <v>82.8753399441762</v>
+        <v>684.391027839493</v>
       </c>
       <c r="G271" t="s">
         <v>70</v>
@@ -11688,7 +11688,7 @@
         <v>14</v>
       </c>
       <c r="K271" t="n">
-        <v>0.966</v>
+        <v>0.937</v>
       </c>
       <c r="L271" t="s">
         <v>15</v>
@@ -11702,19 +11702,19 @@
         <v>44743</v>
       </c>
       <c r="B272" t="n">
-        <v>13.5192592948058</v>
+        <v>13.6126345558937</v>
       </c>
       <c r="C272" t="n">
-        <v>2.4364077513997</v>
+        <v>1.2613352075685</v>
       </c>
       <c r="D272" t="n">
-        <v>0.335228863113846</v>
+        <v>0.292854024288708</v>
       </c>
       <c r="E272" t="n">
-        <v>44.4052388287541</v>
+        <v>163.096214647569</v>
       </c>
       <c r="F272" t="n">
-        <v>76.6449568081234</v>
+        <v>736.558534185377</v>
       </c>
       <c r="G272" t="s">
         <v>70</v>
@@ -11729,7 +11729,7 @@
         <v>14</v>
       </c>
       <c r="K272" t="n">
-        <v>0.644</v>
+        <v>0.648</v>
       </c>
       <c r="L272" t="s">
         <v>15</v>
@@ -11743,19 +11743,19 @@
         <v>44774</v>
       </c>
       <c r="B273" t="n">
-        <v>13.4682450711578</v>
+        <v>12.8158299783994</v>
       </c>
       <c r="C273" t="n">
-        <v>2.33124984188616</v>
+        <v>1.07702867532274</v>
       </c>
       <c r="D273" t="n">
-        <v>0.317358991839582</v>
+        <v>0.199836044169233</v>
       </c>
       <c r="E273" t="n">
-        <v>44.9607379086665</v>
+        <v>159.469939310427</v>
       </c>
       <c r="F273" t="n">
-        <v>78.1180532932102</v>
+        <v>1013.59514536337</v>
       </c>
       <c r="G273" t="s">
         <v>70</v>
@@ -11770,7 +11770,7 @@
         <v>14</v>
       </c>
       <c r="K273" t="n">
-        <v>0.518</v>
+        <v>0.493</v>
       </c>
       <c r="L273" t="s">
         <v>15</v>
@@ -11784,19 +11784,19 @@
         <v>44805</v>
       </c>
       <c r="B274" t="n">
-        <v>15.1552509191016</v>
+        <v>14.581430664495</v>
       </c>
       <c r="C274" t="n">
-        <v>2.80060731086076</v>
+        <v>1.05391318140569</v>
       </c>
       <c r="D274" t="n">
-        <v>0.369663280791825</v>
+        <v>0.243258500981378</v>
       </c>
       <c r="E274" t="n">
-        <v>50.1799080998587</v>
+        <v>190.992697681017</v>
       </c>
       <c r="F274" t="n">
-        <v>87.1048312246473</v>
+        <v>1205.53398625311</v>
       </c>
       <c r="G274" t="s">
         <v>70</v>
@@ -11811,7 +11811,7 @@
         <v>14</v>
       </c>
       <c r="K274" t="n">
-        <v>0.798</v>
+        <v>0.768</v>
       </c>
       <c r="L274" t="s">
         <v>15</v>
@@ -11825,19 +11825,19 @@
         <v>44835</v>
       </c>
       <c r="B275" t="n">
-        <v>13.8316138953696</v>
+        <v>13.2146631236977</v>
       </c>
       <c r="C275" t="n">
-        <v>2.28100908564532</v>
+        <v>0.848608410778722</v>
       </c>
       <c r="D275" t="n">
-        <v>0.301914461965714</v>
+        <v>0.152068579003333</v>
       </c>
       <c r="E275" t="n">
-        <v>47.3307805361369</v>
+        <v>179.119487615302</v>
       </c>
       <c r="F275" t="n">
-        <v>83.1258044629435</v>
+        <v>1494.24026738788</v>
       </c>
       <c r="G275" t="s">
         <v>70</v>
@@ -11846,13 +11846,13 @@
         <v>20</v>
       </c>
       <c r="I275" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="J275" t="s">
         <v>14</v>
       </c>
       <c r="K275" t="n">
-        <v>0.692</v>
+        <v>0.661</v>
       </c>
       <c r="L275" t="s">
         <v>15</v>
@@ -11866,19 +11866,19 @@
         <v>44866</v>
       </c>
       <c r="B276" t="n">
-        <v>12.9939364659813</v>
+        <v>13.67764271719</v>
       </c>
       <c r="C276" t="n">
-        <v>1.92444071689477</v>
+        <v>0.819602924475986</v>
       </c>
       <c r="D276" t="n">
-        <v>0.262808674444123</v>
+        <v>0.189317146537612</v>
       </c>
       <c r="E276" t="n">
-        <v>45.7095153761025</v>
+        <v>205.631936530553</v>
       </c>
       <c r="F276" t="n">
-        <v>81.0785242515949</v>
+        <v>1451.86742542326</v>
       </c>
       <c r="G276" t="s">
         <v>70</v>
@@ -11887,13 +11887,13 @@
         <v>11</v>
       </c>
       <c r="I276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J276" t="s">
         <v>17</v>
       </c>
       <c r="K276" t="n">
-        <v>1.181</v>
+        <v>1.243</v>
       </c>
       <c r="L276" t="s">
         <v>15</v>
@@ -11907,19 +11907,19 @@
         <v>44896</v>
       </c>
       <c r="B277" t="n">
-        <v>10.3248737382636</v>
+        <v>10.4822041420681</v>
       </c>
       <c r="C277" t="n">
-        <v>0.728388962014553</v>
+        <v>0.595201796558757</v>
       </c>
       <c r="D277" t="n">
-        <v>0.186174125635458</v>
+        <v>0.0874821222960065</v>
       </c>
       <c r="E277" t="n">
-        <v>38.7818061342285</v>
+        <v>142.315394624813</v>
       </c>
       <c r="F277" t="n">
-        <v>70.2255882059761</v>
+        <v>1226.38220338798</v>
       </c>
       <c r="G277" t="s">
         <v>70</v>
@@ -11934,7 +11934,7 @@
         <v>14</v>
       </c>
       <c r="K277" t="n">
-        <v>0.738</v>
+        <v>0.749</v>
       </c>
       <c r="L277" t="s">
         <v>15</v>
@@ -11948,19 +11948,19 @@
         <v>44927</v>
       </c>
       <c r="B278" t="n">
-        <v>26.0338676630422</v>
+        <v>25.0737505799513</v>
       </c>
       <c r="C278" t="n">
-        <v>5.87888264837927</v>
+        <v>1.19900832017182</v>
       </c>
       <c r="D278" t="n">
-        <v>1.64870075317364</v>
+        <v>0.200941741524088</v>
       </c>
       <c r="E278" t="n">
-        <v>82.7855281574696</v>
+        <v>492.822505834636</v>
       </c>
       <c r="F278" t="n">
-        <v>142.603776662251</v>
+        <v>3662.41894681397</v>
       </c>
       <c r="G278" t="s">
         <v>70</v>
@@ -11969,13 +11969,13 @@
         <v>44</v>
       </c>
       <c r="I278" t="n">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="J278" t="s">
         <v>14</v>
       </c>
       <c r="K278" t="n">
-        <v>0.592</v>
+        <v>0.57</v>
       </c>
       <c r="L278" t="s">
         <v>15</v>
@@ -11989,19 +11989,19 @@
         <v>44958</v>
       </c>
       <c r="B279" t="n">
-        <v>19.1487258091164</v>
+        <v>18.7597831883225</v>
       </c>
       <c r="C279" t="n">
-        <v>3.59417736661399</v>
+        <v>0.880066825548651</v>
       </c>
       <c r="D279" t="n">
-        <v>0.450973236647658</v>
+        <v>0.138710529088818</v>
       </c>
       <c r="E279" t="n">
-        <v>65.0960646747467</v>
+        <v>393.964784032011</v>
       </c>
       <c r="F279" t="n">
-        <v>114.761549095462</v>
+        <v>3030.77653742149</v>
       </c>
       <c r="G279" t="s">
         <v>70</v>
@@ -12016,7 +12016,7 @@
         <v>17</v>
       </c>
       <c r="K279" t="n">
-        <v>1.473</v>
+        <v>1.443</v>
       </c>
       <c r="L279" t="s">
         <v>15</v>
@@ -12030,19 +12030,19 @@
         <v>44986</v>
       </c>
       <c r="B280" t="n">
-        <v>16.2738600839784</v>
+        <v>16.3691665164094</v>
       </c>
       <c r="C280" t="n">
-        <v>2.63075626474855</v>
+        <v>0.769334790574536</v>
       </c>
       <c r="D280" t="n">
-        <v>0.315831499489344</v>
+        <v>0.107579711104007</v>
       </c>
       <c r="E280" t="n">
-        <v>57.8464802470417</v>
+        <v>334.092799576641</v>
       </c>
       <c r="F280" t="n">
-        <v>103.558352972991</v>
+        <v>4269.62529266399</v>
       </c>
       <c r="G280" t="s">
         <v>70</v>
@@ -12057,7 +12057,7 @@
         <v>17</v>
       </c>
       <c r="K280" t="n">
-        <v>1.627</v>
+        <v>1.636</v>
       </c>
       <c r="L280" t="s">
         <v>15</v>
@@ -12071,19 +12071,19 @@
         <v>45017</v>
       </c>
       <c r="B281" t="n">
-        <v>16.1061380387927</v>
+        <v>14.8794454174004</v>
       </c>
       <c r="C281" t="n">
-        <v>2.49902679829049</v>
+        <v>0.531707628204117</v>
       </c>
       <c r="D281" t="n">
-        <v>0.297555792925294</v>
+        <v>0.0798394817306968</v>
       </c>
       <c r="E281" t="n">
-        <v>58.1430765098339</v>
+        <v>326.85674327781</v>
       </c>
       <c r="F281" t="n">
-        <v>104.733079555231</v>
+        <v>3761.66951055887</v>
       </c>
       <c r="G281" t="s">
         <v>70</v>
@@ -12092,13 +12092,13 @@
         <v>17</v>
       </c>
       <c r="I281" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J281" t="s">
         <v>14</v>
       </c>
       <c r="K281" t="n">
-        <v>0.947</v>
+        <v>0.875</v>
       </c>
       <c r="L281" t="s">
         <v>15</v>
@@ -12112,19 +12112,19 @@
         <v>45047</v>
       </c>
       <c r="B282" t="n">
-        <v>14.309307493733</v>
+        <v>15.7146739543915</v>
       </c>
       <c r="C282" t="n">
-        <v>1.88161930643464</v>
+        <v>0.579835133914391</v>
       </c>
       <c r="D282" t="n">
-        <v>0.238719294079922</v>
+        <v>0.0906529571084597</v>
       </c>
       <c r="E282" t="n">
-        <v>53.6410606707893</v>
+        <v>383.869998002691</v>
       </c>
       <c r="F282" t="n">
-        <v>97.868191920386</v>
+        <v>4723.70491969531</v>
       </c>
       <c r="G282" t="s">
         <v>70</v>
@@ -12133,13 +12133,13 @@
         <v>14</v>
       </c>
       <c r="I282" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J282" t="s">
         <v>17</v>
       </c>
       <c r="K282" t="n">
-        <v>1.022</v>
+        <v>1.122</v>
       </c>
       <c r="L282" t="s">
         <v>15</v>
@@ -12153,19 +12153,19 @@
         <v>45078</v>
       </c>
       <c r="B283" t="n">
-        <v>15.4595344915785</v>
+        <v>15.366536420648</v>
       </c>
       <c r="C283" t="n">
-        <v>2.15253489824124</v>
+        <v>0.475278161206557</v>
       </c>
       <c r="D283" t="n">
-        <v>0.257698365281955</v>
+        <v>0.0751647447766687</v>
       </c>
       <c r="E283" t="n">
-        <v>57.7799819869045</v>
+        <v>387.199831564702</v>
       </c>
       <c r="F283" t="n">
-        <v>105.478850141462</v>
+        <v>5647.7450252801</v>
       </c>
       <c r="G283" t="s">
         <v>70</v>
@@ -12180,7 +12180,7 @@
         <v>17</v>
       </c>
       <c r="K283" t="n">
-        <v>1.717</v>
+        <v>1.707</v>
       </c>
       <c r="L283" t="s">
         <v>15</v>
@@ -12194,19 +12194,19 @@
         <v>45108</v>
       </c>
       <c r="B284" t="n">
-        <v>13.5192592948058</v>
+        <v>14.2147562517513</v>
       </c>
       <c r="C284" t="n">
-        <v>1.48360035836475</v>
+        <v>0.446993686745504</v>
       </c>
       <c r="D284" t="n">
-        <v>0.205384358487726</v>
+        <v>0.0583276026387536</v>
       </c>
       <c r="E284" t="n">
-        <v>52.6761893346717</v>
+        <v>411.787623037484</v>
       </c>
       <c r="F284" t="n">
-        <v>97.4933819636688</v>
+        <v>7010.71159278477</v>
       </c>
       <c r="G284" t="s">
         <v>70</v>
@@ -12221,7 +12221,7 @@
         <v>17</v>
       </c>
       <c r="K284" t="n">
-        <v>1.04</v>
+        <v>1.093</v>
       </c>
       <c r="L284" t="s">
         <v>15</v>
@@ -12235,19 +12235,19 @@
         <v>45139</v>
       </c>
       <c r="B285" t="n">
-        <v>13.4682450711578</v>
+        <v>13.576926692842</v>
       </c>
       <c r="C285" t="n">
-        <v>1.38957015636449</v>
+        <v>0.392346096890077</v>
       </c>
       <c r="D285" t="n">
-        <v>0.197535607154865</v>
+        <v>0.0510741756356447</v>
       </c>
       <c r="E285" t="n">
-        <v>53.2082322541549</v>
+        <v>371.480368141927</v>
       </c>
       <c r="F285" t="n">
-        <v>99.0207240805687</v>
+        <v>7297.29536609527</v>
       </c>
       <c r="G285" t="s">
         <v>70</v>
@@ -12256,13 +12256,13 @@
         <v>14</v>
       </c>
       <c r="I285" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J285" t="s">
         <v>14</v>
       </c>
       <c r="K285" t="n">
-        <v>0.962</v>
+        <v>0.97</v>
       </c>
       <c r="L285" t="s">
         <v>15</v>
@@ -12276,19 +12276,19 @@
         <v>45170</v>
       </c>
       <c r="B286" t="n">
-        <v>15.1552509191016</v>
+        <v>15.3150011202851</v>
       </c>
       <c r="C286" t="n">
-        <v>1.84485694945834</v>
+        <v>0.349491451719773</v>
       </c>
       <c r="D286" t="n">
-        <v>0.224422362622376</v>
+        <v>0.046633427159088</v>
       </c>
       <c r="E286" t="n">
-        <v>59.1081836970063</v>
+        <v>437.135678986357</v>
       </c>
       <c r="F286" t="n">
-        <v>109.746802683503</v>
+        <v>10725.8230281739</v>
       </c>
       <c r="G286" t="s">
         <v>70</v>
@@ -12303,7 +12303,7 @@
         <v>17</v>
       </c>
       <c r="K286" t="n">
-        <v>1.893</v>
+        <v>1.913</v>
       </c>
       <c r="L286" t="s">
         <v>15</v>
@@ -12317,19 +12317,19 @@
         <v>45200</v>
       </c>
       <c r="B287" t="n">
-        <v>13.8316138953696</v>
+        <v>13.4523121515823</v>
       </c>
       <c r="C287" t="n">
-        <v>1.36047960337837</v>
+        <v>0.347872194431714</v>
       </c>
       <c r="D287" t="n">
-        <v>0.191527009839817</v>
+        <v>0.03649728973959</v>
       </c>
       <c r="E287" t="n">
-        <v>55.7244916583357</v>
+        <v>436.869855907285</v>
       </c>
       <c r="F287" t="n">
-        <v>104.597852807693</v>
+        <v>9429.69547208453</v>
       </c>
       <c r="G287" t="s">
         <v>70</v>
@@ -12338,13 +12338,13 @@
         <v>5</v>
       </c>
       <c r="I287" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J287" t="s">
         <v>17</v>
       </c>
       <c r="K287" t="n">
-        <v>2.763</v>
+        <v>2.687</v>
       </c>
       <c r="L287" t="s">
         <v>15</v>
@@ -12358,19 +12358,19 @@
         <v>45231</v>
       </c>
       <c r="B288" t="n">
-        <v>12.9939364659813</v>
+        <v>14.1196079503037</v>
       </c>
       <c r="C288" t="n">
-        <v>0.834944743544822</v>
+        <v>0.303784127388724</v>
       </c>
       <c r="D288" t="n">
-        <v>0.17129793266395</v>
+        <v>0.034552209721203</v>
       </c>
       <c r="E288" t="n">
-        <v>53.761733393041</v>
+        <v>525.132414127292</v>
       </c>
       <c r="F288" t="n">
-        <v>101.832584482537</v>
+        <v>15288.5356010835</v>
       </c>
       <c r="G288" t="s">
         <v>70</v>
@@ -12379,13 +12379,13 @@
         <v>3</v>
       </c>
       <c r="I288" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J288" t="s">
         <v>17</v>
       </c>
       <c r="K288" t="n">
-        <v>4.32</v>
+        <v>4.694</v>
       </c>
       <c r="L288" t="s">
         <v>15</v>
@@ -12399,19 +12399,19 @@
         <v>45261</v>
       </c>
       <c r="B289" t="n">
-        <v>10.3248737382636</v>
+        <v>10.7405835176376</v>
       </c>
       <c r="C289" t="n">
-        <v>0.440202117606151</v>
+        <v>0.238651382253785</v>
       </c>
       <c r="D289" t="n">
-        <v>0.127474229147131</v>
+        <v>0.0205200701452755</v>
       </c>
       <c r="E289" t="n">
-        <v>45.7177753551244</v>
+        <v>431.92264238804</v>
       </c>
       <c r="F289" t="n">
-        <v>88.3581052488438</v>
+        <v>12274.6326159249</v>
       </c>
       <c r="G289" t="s">
         <v>70</v>
@@ -12420,13 +12420,13 @@
         <v>4</v>
       </c>
       <c r="I289" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J289" t="s">
         <v>17</v>
       </c>
       <c r="K289" t="n">
-        <v>2.577</v>
+        <v>2.681</v>
       </c>
       <c r="L289" t="s">
         <v>15</v>

--- a/Outcome/Appendix/figure_data/fig7.xlsx
+++ b/Outcome/Appendix/figure_data/fig7.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -226,9 +226,6 @@
   <si>
     <t xml:space="preserve">TBM</t>
   </si>
-  <si>
-    <t xml:space="preserve">Leprosy</t>
-  </si>
 </sst>
 </file>
 
@@ -283,8 +280,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M337" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:M337"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M289" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:M289"/>
   <tableColumns count="13">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="mean"/>
@@ -12435,1974 +12432,6 @@
         <v>64</v>
       </c>
     </row>
-    <row r="290">
-      <c r="A290" s="1" t="n">
-        <v>43831</v>
-      </c>
-      <c r="B290" t="n">
-        <v>1.35327868082698</v>
-      </c>
-      <c r="C290" t="n">
-        <v>0.373322054275106</v>
-      </c>
-      <c r="D290" t="n">
-        <v>0.212783825037333</v>
-      </c>
-      <c r="E290" t="n">
-        <v>4.62278802458875</v>
-      </c>
-      <c r="F290" t="n">
-        <v>9.13089241121516</v>
-      </c>
-      <c r="G290" t="s">
-        <v>71</v>
-      </c>
-      <c r="H290" t="n">
-        <v>11</v>
-      </c>
-      <c r="I290" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J290" t="s">
-        <v>14</v>
-      </c>
-      <c r="K290" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="L290" t="s">
-        <v>15</v>
-      </c>
-      <c r="M290" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="1" t="n">
-        <v>43862</v>
-      </c>
-      <c r="B291" t="n">
-        <v>1.09897275593117</v>
-      </c>
-      <c r="C291" t="n">
-        <v>0.296689868884206</v>
-      </c>
-      <c r="D291" t="n">
-        <v>0.148897984236092</v>
-      </c>
-      <c r="E291" t="n">
-        <v>3.78227284408564</v>
-      </c>
-      <c r="F291" t="n">
-        <v>7.39169326954061</v>
-      </c>
-      <c r="G291" t="s">
-        <v>71</v>
-      </c>
-      <c r="H291" t="n">
-        <v>3</v>
-      </c>
-      <c r="I291" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J291" t="s">
-        <v>14</v>
-      </c>
-      <c r="K291" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="L291" t="s">
-        <v>15</v>
-      </c>
-      <c r="M291" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="1" t="n">
-        <v>43891</v>
-      </c>
-      <c r="B292" t="n">
-        <v>0.866864956078264</v>
-      </c>
-      <c r="C292" t="n">
-        <v>0.214441686821767</v>
-      </c>
-      <c r="D292" t="n">
-        <v>0.104752100414645</v>
-      </c>
-      <c r="E292" t="n">
-        <v>3.49347576408465</v>
-      </c>
-      <c r="F292" t="n">
-        <v>5.86889752770439</v>
-      </c>
-      <c r="G292" t="s">
-        <v>71</v>
-      </c>
-      <c r="H292" t="n">
-        <v>3</v>
-      </c>
-      <c r="I292" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J292" t="s">
-        <v>14</v>
-      </c>
-      <c r="K292" t="n">
-        <v>0.291</v>
-      </c>
-      <c r="L292" t="s">
-        <v>15</v>
-      </c>
-      <c r="M292" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="1" t="n">
-        <v>43922</v>
-      </c>
-      <c r="B293" t="n">
-        <v>0.431755515709618</v>
-      </c>
-      <c r="C293" t="n">
-        <v>0.088096735418301</v>
-      </c>
-      <c r="D293" t="n">
-        <v>0.0436853532863958</v>
-      </c>
-      <c r="E293" t="n">
-        <v>1.72198162089537</v>
-      </c>
-      <c r="F293" t="n">
-        <v>3.27362164802682</v>
-      </c>
-      <c r="G293" t="s">
-        <v>71</v>
-      </c>
-      <c r="H293" t="n">
-        <v>5</v>
-      </c>
-      <c r="I293" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J293" t="s">
-        <v>14</v>
-      </c>
-      <c r="K293" t="n">
-        <v>0.088</v>
-      </c>
-      <c r="L293" t="s">
-        <v>15</v>
-      </c>
-      <c r="M293" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="1" t="n">
-        <v>43952</v>
-      </c>
-      <c r="B294" t="n">
-        <v>0.56311529544547</v>
-      </c>
-      <c r="C294" t="n">
-        <v>0.125025697076097</v>
-      </c>
-      <c r="D294" t="n">
-        <v>0.0497293888632115</v>
-      </c>
-      <c r="E294" t="n">
-        <v>2.55805489616996</v>
-      </c>
-      <c r="F294" t="n">
-        <v>5.1506161976529</v>
-      </c>
-      <c r="G294" t="s">
-        <v>71</v>
-      </c>
-      <c r="H294" t="n">
-        <v>4</v>
-      </c>
-      <c r="I294" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J294" t="s">
-        <v>14</v>
-      </c>
-      <c r="K294" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="L294" t="s">
-        <v>15</v>
-      </c>
-      <c r="M294" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="1" t="n">
-        <v>43983</v>
-      </c>
-      <c r="B295" t="n">
-        <v>0.459912890115576</v>
-      </c>
-      <c r="C295" t="n">
-        <v>0.0849223676140161</v>
-      </c>
-      <c r="D295" t="n">
-        <v>0.0332724956087245</v>
-      </c>
-      <c r="E295" t="n">
-        <v>2.03816636877504</v>
-      </c>
-      <c r="F295" t="n">
-        <v>4.40726539354129</v>
-      </c>
-      <c r="G295" t="s">
-        <v>71</v>
-      </c>
-      <c r="H295" t="n">
-        <v>3</v>
-      </c>
-      <c r="I295" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J295" t="s">
-        <v>14</v>
-      </c>
-      <c r="K295" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="L295" t="s">
-        <v>15</v>
-      </c>
-      <c r="M295" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="1" t="n">
-        <v>44013</v>
-      </c>
-      <c r="B296" t="n">
-        <v>0.207569423487199</v>
-      </c>
-      <c r="C296" t="n">
-        <v>0.0328574778578943</v>
-      </c>
-      <c r="D296" t="n">
-        <v>0.0100918290252098</v>
-      </c>
-      <c r="E296" t="n">
-        <v>1.05889023383847</v>
-      </c>
-      <c r="F296" t="n">
-        <v>2.35956578282061</v>
-      </c>
-      <c r="G296" t="s">
-        <v>71</v>
-      </c>
-      <c r="H296" t="n">
-        <v>3</v>
-      </c>
-      <c r="I296" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J296" t="s">
-        <v>14</v>
-      </c>
-      <c r="K296" t="n">
-        <v>0.072</v>
-      </c>
-      <c r="L296" t="s">
-        <v>15</v>
-      </c>
-      <c r="M296" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="1" t="n">
-        <v>44044</v>
-      </c>
-      <c r="B297" t="n">
-        <v>0.186326011437588</v>
-      </c>
-      <c r="C297" t="n">
-        <v>0.0283970765816598</v>
-      </c>
-      <c r="D297" t="n">
-        <v>0.00704015715021341</v>
-      </c>
-      <c r="E297" t="n">
-        <v>1.16501077921475</v>
-      </c>
-      <c r="F297" t="n">
-        <v>2.14668707493204</v>
-      </c>
-      <c r="G297" t="s">
-        <v>71</v>
-      </c>
-      <c r="H297" t="n">
-        <v>2</v>
-      </c>
-      <c r="I297" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J297" t="s">
-        <v>14</v>
-      </c>
-      <c r="K297" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="L297" t="s">
-        <v>15</v>
-      </c>
-      <c r="M297" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="1" t="n">
-        <v>44075</v>
-      </c>
-      <c r="B298" t="n">
-        <v>0.376482581268312</v>
-      </c>
-      <c r="C298" t="n">
-        <v>0.0492848257965322</v>
-      </c>
-      <c r="D298" t="n">
-        <v>0.0128003594161907</v>
-      </c>
-      <c r="E298" t="n">
-        <v>2.34267242838703</v>
-      </c>
-      <c r="F298" t="n">
-        <v>5.00895680220106</v>
-      </c>
-      <c r="G298" t="s">
-        <v>71</v>
-      </c>
-      <c r="H298" t="n">
-        <v>7</v>
-      </c>
-      <c r="I298" t="n">
-        <v>-7</v>
-      </c>
-      <c r="J298" t="s">
-        <v>14</v>
-      </c>
-      <c r="K298" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="L298" t="s">
-        <v>15</v>
-      </c>
-      <c r="M298" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="1" t="n">
-        <v>44105</v>
-      </c>
-      <c r="B299" t="n">
-        <v>0.262194740475969</v>
-      </c>
-      <c r="C299" t="n">
-        <v>0.029552414394094</v>
-      </c>
-      <c r="D299" t="n">
-        <v>0.00722277146870542</v>
-      </c>
-      <c r="E299" t="n">
-        <v>1.82161707506171</v>
-      </c>
-      <c r="F299" t="n">
-        <v>4.44723553616314</v>
-      </c>
-      <c r="G299" t="s">
-        <v>71</v>
-      </c>
-      <c r="H299" t="n">
-        <v>7</v>
-      </c>
-      <c r="I299" t="n">
-        <v>-7</v>
-      </c>
-      <c r="J299" t="s">
-        <v>14</v>
-      </c>
-      <c r="K299" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="L299" t="s">
-        <v>15</v>
-      </c>
-      <c r="M299" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="1" t="n">
-        <v>44136</v>
-      </c>
-      <c r="B300" t="n">
-        <v>0.0769400903727299</v>
-      </c>
-      <c r="C300" t="n">
-        <v>0.00762845785271064</v>
-      </c>
-      <c r="D300" t="n">
-        <v>0.00155896422002831</v>
-      </c>
-      <c r="E300" t="n">
-        <v>0.567471684380719</v>
-      </c>
-      <c r="F300" t="n">
-        <v>1.41685869686798</v>
-      </c>
-      <c r="G300" t="s">
-        <v>71</v>
-      </c>
-      <c r="H300" t="n">
-        <v>7</v>
-      </c>
-      <c r="I300" t="n">
-        <v>-7</v>
-      </c>
-      <c r="J300" t="s">
-        <v>14</v>
-      </c>
-      <c r="K300" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="L300" t="s">
-        <v>15</v>
-      </c>
-      <c r="M300" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="1" t="n">
-        <v>44166</v>
-      </c>
-      <c r="B301" t="n">
-        <v>0.232172312017793</v>
-      </c>
-      <c r="C301" t="n">
-        <v>0.021596746168259</v>
-      </c>
-      <c r="D301" t="n">
-        <v>0.00459025088381319</v>
-      </c>
-      <c r="E301" t="n">
-        <v>1.79946074758377</v>
-      </c>
-      <c r="F301" t="n">
-        <v>4.45641548859722</v>
-      </c>
-      <c r="G301" t="s">
-        <v>71</v>
-      </c>
-      <c r="H301" t="n">
-        <v>0</v>
-      </c>
-      <c r="I301" t="n">
-        <v>0</v>
-      </c>
-      <c r="J301" t="s">
-        <v>17</v>
-      </c>
-      <c r="K301" t="n">
-        <v>24.217</v>
-      </c>
-      <c r="L301" t="s">
-        <v>66</v>
-      </c>
-      <c r="M301" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="1" t="n">
-        <v>44197</v>
-      </c>
-      <c r="B302" t="n">
-        <v>0.375804008101439</v>
-      </c>
-      <c r="C302" t="n">
-        <v>0.0262302324601524</v>
-      </c>
-      <c r="D302" t="n">
-        <v>0.00558261863403421</v>
-      </c>
-      <c r="E302" t="n">
-        <v>3.98491373167497</v>
-      </c>
-      <c r="F302" t="n">
-        <v>9.18498133078387</v>
-      </c>
-      <c r="G302" t="s">
-        <v>71</v>
-      </c>
-      <c r="H302" t="n">
-        <v>5</v>
-      </c>
-      <c r="I302" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J302" t="s">
-        <v>14</v>
-      </c>
-      <c r="K302" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="L302" t="s">
-        <v>15</v>
-      </c>
-      <c r="M302" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="1" t="n">
-        <v>44228</v>
-      </c>
-      <c r="B303" t="n">
-        <v>0.292904690979184</v>
-      </c>
-      <c r="C303" t="n">
-        <v>0.019088823487204</v>
-      </c>
-      <c r="D303" t="n">
-        <v>0.00256391111098638</v>
-      </c>
-      <c r="E303" t="n">
-        <v>2.95569271508521</v>
-      </c>
-      <c r="F303" t="n">
-        <v>7.05646352769654</v>
-      </c>
-      <c r="G303" t="s">
-        <v>71</v>
-      </c>
-      <c r="H303" t="n">
-        <v>6</v>
-      </c>
-      <c r="I303" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J303" t="s">
-        <v>14</v>
-      </c>
-      <c r="K303" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L303" t="s">
-        <v>15</v>
-      </c>
-      <c r="M303" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="1" t="n">
-        <v>44256</v>
-      </c>
-      <c r="B304" t="n">
-        <v>0.246884180766159</v>
-      </c>
-      <c r="C304" t="n">
-        <v>0.0129491020614452</v>
-      </c>
-      <c r="D304" t="n">
-        <v>0.00227424835458766</v>
-      </c>
-      <c r="E304" t="n">
-        <v>2.75683254496035</v>
-      </c>
-      <c r="F304" t="n">
-        <v>7.35248451033318</v>
-      </c>
-      <c r="G304" t="s">
-        <v>71</v>
-      </c>
-      <c r="H304" t="n">
-        <v>9</v>
-      </c>
-      <c r="I304" t="n">
-        <v>-9</v>
-      </c>
-      <c r="J304" t="s">
-        <v>14</v>
-      </c>
-      <c r="K304" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="L304" t="s">
-        <v>15</v>
-      </c>
-      <c r="M304" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="1" t="n">
-        <v>44287</v>
-      </c>
-      <c r="B305" t="n">
-        <v>0.116793917045733</v>
-      </c>
-      <c r="C305" t="n">
-        <v>0.00579976157479039</v>
-      </c>
-      <c r="D305" t="n">
-        <v>0.000648142792359295</v>
-      </c>
-      <c r="E305" t="n">
-        <v>1.64525819150177</v>
-      </c>
-      <c r="F305" t="n">
-        <v>4.71092127361162</v>
-      </c>
-      <c r="G305" t="s">
-        <v>71</v>
-      </c>
-      <c r="H305" t="n">
-        <v>1</v>
-      </c>
-      <c r="I305" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J305" t="s">
-        <v>14</v>
-      </c>
-      <c r="K305" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="L305" t="s">
-        <v>15</v>
-      </c>
-      <c r="M305" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="1" t="n">
-        <v>44317</v>
-      </c>
-      <c r="B306" t="n">
-        <v>0.149403420899816</v>
-      </c>
-      <c r="C306" t="n">
-        <v>0.00623508827254805</v>
-      </c>
-      <c r="D306" t="n">
-        <v>0.000613629238500612</v>
-      </c>
-      <c r="E306" t="n">
-        <v>2.27249770589138</v>
-      </c>
-      <c r="F306" t="n">
-        <v>6.02783673641642</v>
-      </c>
-      <c r="G306" t="s">
-        <v>71</v>
-      </c>
-      <c r="H306" t="n">
-        <v>3</v>
-      </c>
-      <c r="I306" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J306" t="s">
-        <v>14</v>
-      </c>
-      <c r="K306" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="L306" t="s">
-        <v>15</v>
-      </c>
-      <c r="M306" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="1" t="n">
-        <v>44348</v>
-      </c>
-      <c r="B307" t="n">
-        <v>0.122974557951261</v>
-      </c>
-      <c r="C307" t="n">
-        <v>0.00438051076256206</v>
-      </c>
-      <c r="D307" t="n">
-        <v>0.000326100946977598</v>
-      </c>
-      <c r="E307" t="n">
-        <v>1.93773205433169</v>
-      </c>
-      <c r="F307" t="n">
-        <v>7.2671783970727</v>
-      </c>
-      <c r="G307" t="s">
-        <v>71</v>
-      </c>
-      <c r="H307" t="n">
-        <v>5</v>
-      </c>
-      <c r="I307" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J307" t="s">
-        <v>14</v>
-      </c>
-      <c r="K307" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="L307" t="s">
-        <v>15</v>
-      </c>
-      <c r="M307" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="1" t="n">
-        <v>44378</v>
-      </c>
-      <c r="B308" t="n">
-        <v>0.053579941472434</v>
-      </c>
-      <c r="C308" t="n">
-        <v>0.00166835960485581</v>
-      </c>
-      <c r="D308" t="n">
-        <v>0.000129597864668245</v>
-      </c>
-      <c r="E308" t="n">
-        <v>0.971502455611252</v>
-      </c>
-      <c r="F308" t="n">
-        <v>3.57827758427575</v>
-      </c>
-      <c r="G308" t="s">
-        <v>71</v>
-      </c>
-      <c r="H308" t="n">
-        <v>1</v>
-      </c>
-      <c r="I308" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J308" t="s">
-        <v>14</v>
-      </c>
-      <c r="K308" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="L308" t="s">
-        <v>15</v>
-      </c>
-      <c r="M308" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="1" t="n">
-        <v>44409</v>
-      </c>
-      <c r="B309" t="n">
-        <v>0.0519109600752612</v>
-      </c>
-      <c r="C309" t="n">
-        <v>0.00105081179622387</v>
-      </c>
-      <c r="D309" t="n">
-        <v>0.000115648484274022</v>
-      </c>
-      <c r="E309" t="n">
-        <v>0.988312320638165</v>
-      </c>
-      <c r="F309" t="n">
-        <v>3.8361528077566</v>
-      </c>
-      <c r="G309" t="s">
-        <v>71</v>
-      </c>
-      <c r="H309" t="n">
-        <v>1</v>
-      </c>
-      <c r="I309" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J309" t="s">
-        <v>14</v>
-      </c>
-      <c r="K309" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="L309" t="s">
-        <v>15</v>
-      </c>
-      <c r="M309" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="1" t="n">
-        <v>44440</v>
-      </c>
-      <c r="B310" t="n">
-        <v>0.105806802163293</v>
-      </c>
-      <c r="C310" t="n">
-        <v>0.00212186139132898</v>
-      </c>
-      <c r="D310" t="n">
-        <v>0.000188868851625275</v>
-      </c>
-      <c r="E310" t="n">
-        <v>2.4545513270766</v>
-      </c>
-      <c r="F310" t="n">
-        <v>7.22339172975483</v>
-      </c>
-      <c r="G310" t="s">
-        <v>71</v>
-      </c>
-      <c r="H310" t="n">
-        <v>3</v>
-      </c>
-      <c r="I310" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J310" t="s">
-        <v>14</v>
-      </c>
-      <c r="K310" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="L310" t="s">
-        <v>15</v>
-      </c>
-      <c r="M310" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="1" t="n">
-        <v>44470</v>
-      </c>
-      <c r="B311" t="n">
-        <v>0.0691652239606271</v>
-      </c>
-      <c r="C311" t="n">
-        <v>0.0013336675570609</v>
-      </c>
-      <c r="D311" t="n">
-        <v>0.000118843864946275</v>
-      </c>
-      <c r="E311" t="n">
-        <v>1.61350495358783</v>
-      </c>
-      <c r="F311" t="n">
-        <v>6.86778027461524</v>
-      </c>
-      <c r="G311" t="s">
-        <v>71</v>
-      </c>
-      <c r="H311" t="n">
-        <v>0</v>
-      </c>
-      <c r="I311" t="n">
-        <v>0</v>
-      </c>
-      <c r="J311" t="s">
-        <v>17</v>
-      </c>
-      <c r="K311" t="n">
-        <v>7.917</v>
-      </c>
-      <c r="L311" t="s">
-        <v>15</v>
-      </c>
-      <c r="M311" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="1" t="n">
-        <v>44501</v>
-      </c>
-      <c r="B312" t="n">
-        <v>0.0216401394628813</v>
-      </c>
-      <c r="C312" t="n">
-        <v>0.000420703858852283</v>
-      </c>
-      <c r="D312" t="n">
-        <v>0.0000176134505116936</v>
-      </c>
-      <c r="E312" t="n">
-        <v>0.624529311428782</v>
-      </c>
-      <c r="F312" t="n">
-        <v>2.29132916113469</v>
-      </c>
-      <c r="G312" t="s">
-        <v>71</v>
-      </c>
-      <c r="H312" t="n">
-        <v>2</v>
-      </c>
-      <c r="I312" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J312" t="s">
-        <v>14</v>
-      </c>
-      <c r="K312" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="L312" t="s">
-        <v>15</v>
-      </c>
-      <c r="M312" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="1" t="n">
-        <v>44531</v>
-      </c>
-      <c r="B313" t="n">
-        <v>0.0636724140865007</v>
-      </c>
-      <c r="C313" t="n">
-        <v>0.00109524712172</v>
-      </c>
-      <c r="D313" t="n">
-        <v>0.0000523712424918482</v>
-      </c>
-      <c r="E313" t="n">
-        <v>1.74670515905537</v>
-      </c>
-      <c r="F313" t="n">
-        <v>8.2322313285052</v>
-      </c>
-      <c r="G313" t="s">
-        <v>71</v>
-      </c>
-      <c r="H313" t="n">
-        <v>2</v>
-      </c>
-      <c r="I313" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J313" t="s">
-        <v>14</v>
-      </c>
-      <c r="K313" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="L313" t="s">
-        <v>15</v>
-      </c>
-      <c r="M313" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="1" t="n">
-        <v>44562</v>
-      </c>
-      <c r="B314" t="n">
-        <v>0.0998266786715496</v>
-      </c>
-      <c r="C314" t="n">
-        <v>0.00121570453228946</v>
-      </c>
-      <c r="D314" t="n">
-        <v>0.0000408596227783723</v>
-      </c>
-      <c r="E314" t="n">
-        <v>3.47737787477725</v>
-      </c>
-      <c r="F314" t="n">
-        <v>22.1910246852829</v>
-      </c>
-      <c r="G314" t="s">
-        <v>71</v>
-      </c>
-      <c r="H314" t="n">
-        <v>5</v>
-      </c>
-      <c r="I314" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J314" t="s">
-        <v>14</v>
-      </c>
-      <c r="K314" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="L314" t="s">
-        <v>15</v>
-      </c>
-      <c r="M314" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="1" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B315" t="n">
-        <v>0.0767992123891879</v>
-      </c>
-      <c r="C315" t="n">
-        <v>0.000715252300319803</v>
-      </c>
-      <c r="D315" t="n">
-        <v>0.0000220650483918941</v>
-      </c>
-      <c r="E315" t="n">
-        <v>2.90634449016081</v>
-      </c>
-      <c r="F315" t="n">
-        <v>14.3903498461747</v>
-      </c>
-      <c r="G315" t="s">
-        <v>71</v>
-      </c>
-      <c r="H315" t="n">
-        <v>3</v>
-      </c>
-      <c r="I315" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J315" t="s">
-        <v>14</v>
-      </c>
-      <c r="K315" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="L315" t="s">
-        <v>15</v>
-      </c>
-      <c r="M315" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="B316" t="n">
-        <v>0.06742931749915</v>
-      </c>
-      <c r="C316" t="n">
-        <v>0.000529628351942941</v>
-      </c>
-      <c r="D316" t="n">
-        <v>0.0000130476691552279</v>
-      </c>
-      <c r="E316" t="n">
-        <v>2.53443959148505</v>
-      </c>
-      <c r="F316" t="n">
-        <v>16.7188367785254</v>
-      </c>
-      <c r="G316" t="s">
-        <v>71</v>
-      </c>
-      <c r="H316" t="n">
-        <v>2</v>
-      </c>
-      <c r="I316" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J316" t="s">
-        <v>14</v>
-      </c>
-      <c r="K316" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="L316" t="s">
-        <v>15</v>
-      </c>
-      <c r="M316" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="1" t="n">
-        <v>44652</v>
-      </c>
-      <c r="B317" t="n">
-        <v>0.0312990105744972</v>
-      </c>
-      <c r="C317" t="n">
-        <v>0.000235900428692331</v>
-      </c>
-      <c r="D317" t="n">
-        <v>0.00000456439380667885</v>
-      </c>
-      <c r="E317" t="n">
-        <v>1.74419094737255</v>
-      </c>
-      <c r="F317" t="n">
-        <v>7.12749919302957</v>
-      </c>
-      <c r="G317" t="s">
-        <v>71</v>
-      </c>
-      <c r="H317" t="n">
-        <v>2</v>
-      </c>
-      <c r="I317" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J317" t="s">
-        <v>14</v>
-      </c>
-      <c r="K317" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="L317" t="s">
-        <v>15</v>
-      </c>
-      <c r="M317" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="1" t="n">
-        <v>44682</v>
-      </c>
-      <c r="B318" t="n">
-        <v>0.0416987786766469</v>
-      </c>
-      <c r="C318" t="n">
-        <v>0.000306401128678716</v>
-      </c>
-      <c r="D318" t="n">
-        <v>0.00000433331350817839</v>
-      </c>
-      <c r="E318" t="n">
-        <v>2.32717128359675</v>
-      </c>
-      <c r="F318" t="n">
-        <v>12.3239849245503</v>
-      </c>
-      <c r="G318" t="s">
-        <v>71</v>
-      </c>
-      <c r="H318" t="n">
-        <v>2</v>
-      </c>
-      <c r="I318" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J318" t="s">
-        <v>14</v>
-      </c>
-      <c r="K318" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="L318" t="s">
-        <v>15</v>
-      </c>
-      <c r="M318" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="1" t="n">
-        <v>44713</v>
-      </c>
-      <c r="B319" t="n">
-        <v>0.0348389002903633</v>
-      </c>
-      <c r="C319" t="n">
-        <v>0.000191431509768047</v>
-      </c>
-      <c r="D319" t="n">
-        <v>0.00000267196415595977</v>
-      </c>
-      <c r="E319" t="n">
-        <v>2.24499916265561</v>
-      </c>
-      <c r="F319" t="n">
-        <v>13.3910579762383</v>
-      </c>
-      <c r="G319" t="s">
-        <v>71</v>
-      </c>
-      <c r="H319" t="n">
-        <v>2</v>
-      </c>
-      <c r="I319" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J319" t="s">
-        <v>14</v>
-      </c>
-      <c r="K319" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="L319" t="s">
-        <v>15</v>
-      </c>
-      <c r="M319" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="1" t="n">
-        <v>44743</v>
-      </c>
-      <c r="B320" t="n">
-        <v>0.0146824206332797</v>
-      </c>
-      <c r="C320" t="n">
-        <v>0.000061261645702146</v>
-      </c>
-      <c r="D320" t="n">
-        <v>0.000000733790805172067</v>
-      </c>
-      <c r="E320" t="n">
-        <v>1.10805553990307</v>
-      </c>
-      <c r="F320" t="n">
-        <v>5.92176528593584</v>
-      </c>
-      <c r="G320" t="s">
-        <v>71</v>
-      </c>
-      <c r="H320" t="n">
-        <v>3</v>
-      </c>
-      <c r="I320" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J320" t="s">
-        <v>14</v>
-      </c>
-      <c r="K320" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="L320" t="s">
-        <v>15</v>
-      </c>
-      <c r="M320" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="1" t="n">
-        <v>44774</v>
-      </c>
-      <c r="B321" t="n">
-        <v>0.0131357558069229</v>
-      </c>
-      <c r="C321" t="n">
-        <v>0.0000548718559739392</v>
-      </c>
-      <c r="D321" t="n">
-        <v>0.000000625273838307736</v>
-      </c>
-      <c r="E321" t="n">
-        <v>1.0473452943938</v>
-      </c>
-      <c r="F321" t="n">
-        <v>7.01019330627675</v>
-      </c>
-      <c r="G321" t="s">
-        <v>71</v>
-      </c>
-      <c r="H321" t="n">
-        <v>2</v>
-      </c>
-      <c r="I321" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J321" t="s">
-        <v>14</v>
-      </c>
-      <c r="K321" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="L321" t="s">
-        <v>15</v>
-      </c>
-      <c r="M321" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="1" t="n">
-        <v>44805</v>
-      </c>
-      <c r="B322" t="n">
-        <v>0.028176803990143</v>
-      </c>
-      <c r="C322" t="n">
-        <v>0.0000904194670846897</v>
-      </c>
-      <c r="D322" t="n">
-        <v>0.000000907940024598905</v>
-      </c>
-      <c r="E322" t="n">
-        <v>2.51623274912453</v>
-      </c>
-      <c r="F322" t="n">
-        <v>22.8438476669787</v>
-      </c>
-      <c r="G322" t="s">
-        <v>71</v>
-      </c>
-      <c r="H322" t="n">
-        <v>5</v>
-      </c>
-      <c r="I322" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J322" t="s">
-        <v>14</v>
-      </c>
-      <c r="K322" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="L322" t="s">
-        <v>15</v>
-      </c>
-      <c r="M322" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="1" t="n">
-        <v>44835</v>
-      </c>
-      <c r="B323" t="n">
-        <v>0.019820002132454</v>
-      </c>
-      <c r="C323" t="n">
-        <v>0.0000567325505712796</v>
-      </c>
-      <c r="D323" t="n">
-        <v>0.000000312287577397552</v>
-      </c>
-      <c r="E323" t="n">
-        <v>1.78678372287731</v>
-      </c>
-      <c r="F323" t="n">
-        <v>20.1728972540389</v>
-      </c>
-      <c r="G323" t="s">
-        <v>71</v>
-      </c>
-      <c r="H323" t="n">
-        <v>2</v>
-      </c>
-      <c r="I323" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J323" t="s">
-        <v>14</v>
-      </c>
-      <c r="K323" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="L323" t="s">
-        <v>15</v>
-      </c>
-      <c r="M323" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="1" t="n">
-        <v>44866</v>
-      </c>
-      <c r="B324" t="n">
-        <v>0.00598592070216938</v>
-      </c>
-      <c r="C324" t="n">
-        <v>0.0000143460146703663</v>
-      </c>
-      <c r="D324" t="n">
-        <v>0.0000000472848706441462</v>
-      </c>
-      <c r="E324" t="n">
-        <v>0.807238628170726</v>
-      </c>
-      <c r="F324" t="n">
-        <v>7.1309712703106</v>
-      </c>
-      <c r="G324" t="s">
-        <v>71</v>
-      </c>
-      <c r="H324" t="n">
-        <v>4</v>
-      </c>
-      <c r="I324" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J324" t="s">
-        <v>14</v>
-      </c>
-      <c r="K324" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="L324" t="s">
-        <v>15</v>
-      </c>
-      <c r="M324" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="1" t="n">
-        <v>44896</v>
-      </c>
-      <c r="B325" t="n">
-        <v>0.0176085845950356</v>
-      </c>
-      <c r="C325" t="n">
-        <v>0.0000468988652112595</v>
-      </c>
-      <c r="D325" t="n">
-        <v>0.000000100139415077878</v>
-      </c>
-      <c r="E325" t="n">
-        <v>2.06812839227419</v>
-      </c>
-      <c r="F325" t="n">
-        <v>25.1392621260446</v>
-      </c>
-      <c r="G325" t="s">
-        <v>71</v>
-      </c>
-      <c r="H325" t="n">
-        <v>2</v>
-      </c>
-      <c r="I325" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J325" t="s">
-        <v>14</v>
-      </c>
-      <c r="K325" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="L325" t="s">
-        <v>15</v>
-      </c>
-      <c r="M325" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="1" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B326" t="n">
-        <v>0.0271053613770352</v>
-      </c>
-      <c r="C326" t="n">
-        <v>0.0000364497970422389</v>
-      </c>
-      <c r="D326" t="n">
-        <v>0.000000172228788835981</v>
-      </c>
-      <c r="E326" t="n">
-        <v>4.11372342858267</v>
-      </c>
-      <c r="F326" t="n">
-        <v>58.5750701818817</v>
-      </c>
-      <c r="G326" t="s">
-        <v>71</v>
-      </c>
-      <c r="H326" t="n">
-        <v>4</v>
-      </c>
-      <c r="I326" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J326" t="s">
-        <v>14</v>
-      </c>
-      <c r="K326" t="n">
-        <v>0.009</v>
-      </c>
-      <c r="L326" t="s">
-        <v>15</v>
-      </c>
-      <c r="M326" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="1" t="n">
-        <v>44958</v>
-      </c>
-      <c r="B327" t="n">
-        <v>0.0228456134884571</v>
-      </c>
-      <c r="C327" t="n">
-        <v>0.0000252837684196895</v>
-      </c>
-      <c r="D327" t="n">
-        <v>0.0000000666391703844524</v>
-      </c>
-      <c r="E327" t="n">
-        <v>3.65086988737032</v>
-      </c>
-      <c r="F327" t="n">
-        <v>66.9802168552141</v>
-      </c>
-      <c r="G327" t="s">
-        <v>71</v>
-      </c>
-      <c r="H327" t="n">
-        <v>4</v>
-      </c>
-      <c r="I327" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J327" t="s">
-        <v>14</v>
-      </c>
-      <c r="K327" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="L327" t="s">
-        <v>15</v>
-      </c>
-      <c r="M327" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="1" t="n">
-        <v>44986</v>
-      </c>
-      <c r="B328" t="n">
-        <v>0.0196954046647649</v>
-      </c>
-      <c r="C328" t="n">
-        <v>0.0000199760668466501</v>
-      </c>
-      <c r="D328" t="n">
-        <v>0.0000000249058404611133</v>
-      </c>
-      <c r="E328" t="n">
-        <v>4.3834675517599</v>
-      </c>
-      <c r="F328" t="n">
-        <v>73.1536040066311</v>
-      </c>
-      <c r="G328" t="s">
-        <v>71</v>
-      </c>
-      <c r="H328" t="n">
-        <v>8</v>
-      </c>
-      <c r="I328" t="n">
-        <v>-8</v>
-      </c>
-      <c r="J328" t="s">
-        <v>14</v>
-      </c>
-      <c r="K328" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="L328" t="s">
-        <v>15</v>
-      </c>
-      <c r="M328" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="1" t="n">
-        <v>45017</v>
-      </c>
-      <c r="B329" t="n">
-        <v>0.00895521585922002</v>
-      </c>
-      <c r="C329" t="n">
-        <v>0.0000080056727333548</v>
-      </c>
-      <c r="D329" t="n">
-        <v>0.0000000106277910336228</v>
-      </c>
-      <c r="E329" t="n">
-        <v>1.9271706328823</v>
-      </c>
-      <c r="F329" t="n">
-        <v>26.7405002751194</v>
-      </c>
-      <c r="G329" t="s">
-        <v>71</v>
-      </c>
-      <c r="H329" t="n">
-        <v>1</v>
-      </c>
-      <c r="I329" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J329" t="s">
-        <v>14</v>
-      </c>
-      <c r="K329" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="L329" t="s">
-        <v>15</v>
-      </c>
-      <c r="M329" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="1" t="n">
-        <v>45047</v>
-      </c>
-      <c r="B330" t="n">
-        <v>0.0117204823966676</v>
-      </c>
-      <c r="C330" t="n">
-        <v>0.0000094631359713465</v>
-      </c>
-      <c r="D330" t="n">
-        <v>0.00000000792443999773824</v>
-      </c>
-      <c r="E330" t="n">
-        <v>3.16412661722228</v>
-      </c>
-      <c r="F330" t="n">
-        <v>53.8158161667829</v>
-      </c>
-      <c r="G330" t="s">
-        <v>71</v>
-      </c>
-      <c r="H330" t="n">
-        <v>5</v>
-      </c>
-      <c r="I330" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J330" t="s">
-        <v>14</v>
-      </c>
-      <c r="K330" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="L330" t="s">
-        <v>15</v>
-      </c>
-      <c r="M330" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="1" t="n">
-        <v>45078</v>
-      </c>
-      <c r="B331" t="n">
-        <v>0.00986109418104859</v>
-      </c>
-      <c r="C331" t="n">
-        <v>0.00000792388140710542</v>
-      </c>
-      <c r="D331" t="n">
-        <v>0.00000000478547302147297</v>
-      </c>
-      <c r="E331" t="n">
-        <v>3.33129899655398</v>
-      </c>
-      <c r="F331" t="n">
-        <v>40.5841413432385</v>
-      </c>
-      <c r="G331" t="s">
-        <v>71</v>
-      </c>
-      <c r="H331" t="n">
-        <v>0</v>
-      </c>
-      <c r="I331" t="n">
-        <v>0</v>
-      </c>
-      <c r="J331" t="s">
-        <v>17</v>
-      </c>
-      <c r="K331" t="n">
-        <v>1.986</v>
-      </c>
-      <c r="L331" t="s">
-        <v>15</v>
-      </c>
-      <c r="M331" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="1" t="n">
-        <v>45108</v>
-      </c>
-      <c r="B332" t="n">
-        <v>0.0043874761982722</v>
-      </c>
-      <c r="C332" t="n">
-        <v>0.00000190226387761683</v>
-      </c>
-      <c r="D332" t="n">
-        <v>0.00000000147214414621319</v>
-      </c>
-      <c r="E332" t="n">
-        <v>1.59016419358805</v>
-      </c>
-      <c r="F332" t="n">
-        <v>28.9025394893388</v>
-      </c>
-      <c r="G332" t="s">
-        <v>71</v>
-      </c>
-      <c r="H332" t="n">
-        <v>0</v>
-      </c>
-      <c r="I332" t="n">
-        <v>0</v>
-      </c>
-      <c r="J332" t="s">
-        <v>17</v>
-      </c>
-      <c r="K332" t="n">
-        <v>1.439</v>
-      </c>
-      <c r="L332" t="s">
-        <v>15</v>
-      </c>
-      <c r="M332" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="1" t="n">
-        <v>45139</v>
-      </c>
-      <c r="B333" t="n">
-        <v>0.00406923909199524</v>
-      </c>
-      <c r="C333" t="n">
-        <v>0.00000167751958642733</v>
-      </c>
-      <c r="D333" t="n">
-        <v>0.00000000118745128988795</v>
-      </c>
-      <c r="E333" t="n">
-        <v>1.50366327623125</v>
-      </c>
-      <c r="F333" t="n">
-        <v>40.6925375169476</v>
-      </c>
-      <c r="G333" t="s">
-        <v>71</v>
-      </c>
-      <c r="H333" t="n">
-        <v>2</v>
-      </c>
-      <c r="I333" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J333" t="s">
-        <v>14</v>
-      </c>
-      <c r="K333" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="L333" t="s">
-        <v>15</v>
-      </c>
-      <c r="M333" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="1" t="n">
-        <v>45170</v>
-      </c>
-      <c r="B334" t="n">
-        <v>0.00866712511081053</v>
-      </c>
-      <c r="C334" t="n">
-        <v>0.00000251214279195247</v>
-      </c>
-      <c r="D334" t="n">
-        <v>0.0000000016503970905535</v>
-      </c>
-      <c r="E334" t="n">
-        <v>4.13509972673125</v>
-      </c>
-      <c r="F334" t="n">
-        <v>97.5868079101488</v>
-      </c>
-      <c r="G334" t="s">
-        <v>71</v>
-      </c>
-      <c r="H334" t="n">
-        <v>4</v>
-      </c>
-      <c r="I334" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J334" t="s">
-        <v>14</v>
-      </c>
-      <c r="K334" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="L334" t="s">
-        <v>15</v>
-      </c>
-      <c r="M334" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="1" t="n">
-        <v>45200</v>
-      </c>
-      <c r="B335" t="n">
-        <v>0.0058281380220087</v>
-      </c>
-      <c r="C335" t="n">
-        <v>0.00000173365046140912</v>
-      </c>
-      <c r="D335" t="n">
-        <v>0.000000000672515562658808</v>
-      </c>
-      <c r="E335" t="n">
-        <v>3.03551494035618</v>
-      </c>
-      <c r="F335" t="n">
-        <v>68.6549988895899</v>
-      </c>
-      <c r="G335" t="s">
-        <v>71</v>
-      </c>
-      <c r="H335" t="n">
-        <v>4</v>
-      </c>
-      <c r="I335" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J335" t="s">
-        <v>14</v>
-      </c>
-      <c r="K335" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="L335" t="s">
-        <v>15</v>
-      </c>
-      <c r="M335" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="1" t="n">
-        <v>45231</v>
-      </c>
-      <c r="B336" t="n">
-        <v>0.00177868970737232</v>
-      </c>
-      <c r="C336" t="n">
-        <v>0.00000041307950736658</v>
-      </c>
-      <c r="D336" t="n">
-        <v>0.000000000142098698870733</v>
-      </c>
-      <c r="E336" t="n">
-        <v>1.12507220427223</v>
-      </c>
-      <c r="F336" t="n">
-        <v>35.1080709675802</v>
-      </c>
-      <c r="G336" t="s">
-        <v>71</v>
-      </c>
-      <c r="H336" t="n">
-        <v>3</v>
-      </c>
-      <c r="I336" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J336" t="s">
-        <v>14</v>
-      </c>
-      <c r="K336" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="L336" t="s">
-        <v>15</v>
-      </c>
-      <c r="M336" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="1" t="n">
-        <v>45261</v>
-      </c>
-      <c r="B337" t="n">
-        <v>0.00515763143699397</v>
-      </c>
-      <c r="C337" t="n">
-        <v>0.000000806473051855981</v>
-      </c>
-      <c r="D337" t="n">
-        <v>0.00000000022443250952633</v>
-      </c>
-      <c r="E337" t="n">
-        <v>3.9735108940454</v>
-      </c>
-      <c r="F337" t="n">
-        <v>82.428973686923</v>
-      </c>
-      <c r="G337" t="s">
-        <v>71</v>
-      </c>
-      <c r="H337" t="n">
-        <v>2</v>
-      </c>
-      <c r="I337" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J337" t="s">
-        <v>14</v>
-      </c>
-      <c r="K337" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="L337" t="s">
-        <v>15</v>
-      </c>
-      <c r="M337" t="s">
-        <v>64</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
